--- a/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
+++ b/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
@@ -449,7 +449,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Del maestro sin ficha: quedan activos, sin descripción ni foto</v>
+        <v>Del maestro sin ficha: quedan FUERA del catálogo</v>
       </c>
       <c r="B7">
         <v>12</v>
@@ -476,7 +476,7 @@
         <v>Productos nuevos</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -484,7 +484,7 @@
         <v>Productos retirados</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -492,7 +492,7 @@
         <v>Precios actualizados con el Excel</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -628,7 +628,7 @@
         <v>Falta la ficha</v>
       </c>
       <c r="B32" t="str">
-        <v>los 12 códigos que entraron sin Word</v>
+        <v>los 12 códigos del maestro que no tienen Word</v>
       </c>
     </row>
     <row r="33">
@@ -8582,7 +8582,7 @@
         <v>24999</v>
       </c>
       <c r="O122" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P122" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -8633,7 +8633,7 @@
         <v>950</v>
       </c>
       <c r="O123" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P123" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -8841,7 +8841,7 @@
         <v>14500</v>
       </c>
       <c r="O127" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P127" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -8892,7 +8892,7 @@
         <v>15500</v>
       </c>
       <c r="O128" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P128" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -8943,7 +8943,7 @@
         <v>9300</v>
       </c>
       <c r="O129" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P129" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -8994,7 +8994,7 @@
         <v>9500</v>
       </c>
       <c r="O130" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P130" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -9045,7 +9045,7 @@
         <v>9150</v>
       </c>
       <c r="O131" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P131" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -9096,7 +9096,7 @@
         <v>4500</v>
       </c>
       <c r="O132" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P132" t="str">
         <v>El maestro lo marca en rojo: «No hay ningun archivo con ese codigo»</v>
@@ -9146,7 +9146,7 @@
         <v>11150</v>
       </c>
       <c r="O133" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="P133" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
@@ -9162,7 +9162,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E36"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -9202,7 +9202,7 @@
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="3">
@@ -9219,7 +9219,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="4">
@@ -9236,7 +9236,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="5">
@@ -9253,7 +9253,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="6">
@@ -9270,7 +9270,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="7">
@@ -9287,7 +9287,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="8">
@@ -9304,24 +9304,24 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Producto nuevo</v>
+        <v>Precio actualizado</v>
       </c>
       <c r="B9" t="str">
-        <v>LAVA060</v>
+        <v>CALM18</v>
       </c>
       <c r="C9" t="str">
-        <v>LAVADORA INDUSTRIAL</v>
+        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 1.8 LITROS CALENTAMIENTO ELECTRICO</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>2250.00</v>
       </c>
       <c r="E9" t="str">
-        <v>Figura en el maestro v2 y no existía en el CRM</v>
+        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
       </c>
     </row>
     <row r="10">
@@ -9329,13 +9329,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B10" t="str">
-        <v>CALM18</v>
+        <v>CALM231</v>
       </c>
       <c r="C10" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 1.8 LITROS CALENTAMIENTO ELECTRICO</v>
+        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 2.3 LITROS CALENTAMIENTO ELECTRICO</v>
       </c>
       <c r="D10" t="str">
-        <v>2250.00</v>
+        <v>2350.00</v>
       </c>
       <c r="E10" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9346,13 +9346,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B11" t="str">
-        <v>CALM231</v>
+        <v>CALM4</v>
       </c>
       <c r="C11" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 2.3 LITROS CALENTAMIENTO ELECTRICO</v>
+        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 4 LITROS CALENTAMIENTO ELECTRICO</v>
       </c>
       <c r="D11" t="str">
-        <v>2350.00</v>
+        <v>2500.00</v>
       </c>
       <c r="E11" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9363,13 +9363,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B12" t="str">
-        <v>CALM4</v>
+        <v>CO401A</v>
       </c>
       <c r="C12" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 4 LITROS CALENTAMIENTO ELECTRICO</v>
+        <v>COCHE UTILITARIO DE PLASTICO MOD. HM-401 Azul</v>
       </c>
       <c r="D12" t="str">
-        <v>2500.00</v>
+        <v>1050.00</v>
       </c>
       <c r="E12" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9380,13 +9380,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B13" t="str">
-        <v>CO401A</v>
+        <v>CO402A</v>
       </c>
       <c r="C13" t="str">
-        <v>COCHE UTILITARIO DE PLASTICO MOD. HM-401 Azul</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Azul</v>
       </c>
       <c r="D13" t="str">
-        <v>1050.00</v>
+        <v>999.00</v>
       </c>
       <c r="E13" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9397,10 +9397,10 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B14" t="str">
-        <v>CO402A</v>
+        <v>CO402B</v>
       </c>
       <c r="C14" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Azul</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Blanco</v>
       </c>
       <c r="D14" t="str">
         <v>999.00</v>
@@ -9414,10 +9414,10 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B15" t="str">
-        <v>CO402B</v>
+        <v>CO402G</v>
       </c>
       <c r="C15" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Blanco</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Gris</v>
       </c>
       <c r="D15" t="str">
         <v>999.00</v>
@@ -9431,13 +9431,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B16" t="str">
-        <v>CO402G</v>
+        <v>CO408A</v>
       </c>
       <c r="C16" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Gris</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Azul</v>
       </c>
       <c r="D16" t="str">
-        <v>999.00</v>
+        <v>899.00</v>
       </c>
       <c r="E16" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9448,10 +9448,10 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B17" t="str">
-        <v>CO408A</v>
+        <v>CO408B</v>
       </c>
       <c r="C17" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Azul</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Blanco</v>
       </c>
       <c r="D17" t="str">
         <v>899.00</v>
@@ -9465,13 +9465,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B18" t="str">
-        <v>CO408B</v>
+        <v>LAV040</v>
       </c>
       <c r="C18" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Blanco</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D18" t="str">
-        <v>899.00</v>
+        <v>14500.00</v>
       </c>
       <c r="E18" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9482,13 +9482,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B19" t="str">
-        <v>LAV040</v>
+        <v>LAV060</v>
       </c>
       <c r="C19" t="str">
         <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D19" t="str">
-        <v>14500.00</v>
+        <v>16500.00</v>
       </c>
       <c r="E19" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9499,13 +9499,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B20" t="str">
-        <v>LAV060</v>
+        <v>SECU752</v>
       </c>
       <c r="C20" t="str">
-        <v>LAVADORA INDUSTRIAL</v>
+        <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D20" t="str">
-        <v>16500.00</v>
+        <v>11950.00</v>
       </c>
       <c r="E20" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9516,13 +9516,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B21" t="str">
-        <v>LAVA060</v>
+        <v>SECU755</v>
       </c>
       <c r="C21" t="str">
-        <v>LAVADORA INDUSTRIAL</v>
+        <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D21" t="str">
-        <v>15500.00</v>
+        <v>9900.00</v>
       </c>
       <c r="E21" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9530,36 +9530,36 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Precio actualizado</v>
+        <v>Retirado del catálogo</v>
       </c>
       <c r="B22" t="str">
-        <v>SECU752</v>
+        <v>1SECU1701</v>
       </c>
       <c r="C22" t="str">
         <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D22" t="str">
-        <v>11950.00</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Precio actualizado</v>
+        <v>Retirado del catálogo</v>
       </c>
       <c r="B23" t="str">
-        <v>SECU755</v>
+        <v>CALM23</v>
       </c>
       <c r="C23" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>CALDERÍN CON PLANCHA</v>
       </c>
       <c r="D23" t="str">
-        <v>9900.00</v>
+        <v/>
       </c>
       <c r="E23" t="str">
-        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="24">
@@ -9576,7 +9576,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Su equipo pasó a estar codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
+        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
       </c>
     </row>
     <row r="25">
@@ -9593,7 +9593,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Su equipo pasó a estar codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
+        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
       </c>
     </row>
     <row r="26">
@@ -9610,7 +9610,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Su equipo pasó a estar codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
+        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
       </c>
     </row>
     <row r="27">
@@ -9618,16 +9618,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B27" t="str">
-        <v>SECU75E</v>
+        <v>LAV135S</v>
       </c>
       <c r="C27" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUST. FLOT. SOFTWASH</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="28">
@@ -9635,16 +9635,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B28" t="str">
-        <v>SECU75E2</v>
+        <v>LAVA060</v>
       </c>
       <c r="C28" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="29">
@@ -9652,7 +9652,7 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B29" t="str">
-        <v>SECU75E3</v>
+        <v>SEC75E</v>
       </c>
       <c r="C29" t="str">
         <v>SECADORA INDUSTRIAL</v>
@@ -9661,12 +9661,131 @@
         <v/>
       </c>
       <c r="E29" t="str">
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B30" t="str">
+        <v>SEC75E2</v>
+      </c>
+      <c r="C30" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B31" t="str">
+        <v>SEC75E3</v>
+      </c>
+      <c r="C31" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SECNSEN</v>
+      </c>
+      <c r="C32" t="str">
+        <v>SECADORA SEMI INDUSTRIAL APILABLE ELÉCTRICA</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B33" t="str">
+        <v>SECU754</v>
+      </c>
+      <c r="C33" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B34" t="str">
+        <v>SECU75E</v>
+      </c>
+      <c r="C34" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SECU75E2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B36" t="str">
+        <v>SECU75E3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
         <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9726,7 +9845,7 @@
         <v>UNIMAC</v>
       </c>
       <c r="D2" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E2" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -9755,7 +9874,7 @@
         <v>SIMI MONDIAL</v>
       </c>
       <c r="D3" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E3" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -9871,7 +9990,7 @@
         <v>PRIMUS</v>
       </c>
       <c r="D7" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E7" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -9900,7 +10019,7 @@
         <v>UNIMAC</v>
       </c>
       <c r="D8" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E8" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -9929,7 +10048,7 @@
         <v>UNIMAC</v>
       </c>
       <c r="D9" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E9" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -9958,7 +10077,7 @@
         <v>UNIMAC</v>
       </c>
       <c r="D10" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E10" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -9987,7 +10106,7 @@
         <v>UNIMAC</v>
       </c>
       <c r="D11" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E11" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>
@@ -10016,7 +10135,7 @@
         <v>PRIMUS</v>
       </c>
       <c r="D12" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E12" t="str">
         <v>El maestro lo marca en rojo: «No hay ningun archivo con ese codigo»</v>
@@ -10045,7 +10164,7 @@
         <v>UNIMAC</v>
       </c>
       <c r="D13" t="str">
-        <v>activo</v>
+        <v>retirado</v>
       </c>
       <c r="E13" t="str">
         <v>El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»</v>

--- a/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
+++ b/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
@@ -4605,8 +4605,9 @@
       <c r="D46" t="str">
         <v>LG</v>
       </c>
-      <c r="E46" t="str">
-        <v>GIANT C MAX(CWG27MDCRS)</v>
+      <c r="E46" t="str" xml:space="preserve">
+        <v xml:space="preserve">GIANT C MAX
+(CWG27MDCRS)</v>
       </c>
       <c r="F46" t="str">
         <v>Cargada con su ficha</v>
@@ -4660,8 +4661,9 @@
       <c r="D47" t="str">
         <v>LG</v>
       </c>
-      <c r="E47" t="str">
-        <v>GIANT C MAX(CWG27MSCRS)</v>
+      <c r="E47" t="str" xml:space="preserve">
+        <v xml:space="preserve">GIANT C MAX
+(CWG27MSCRS)</v>
       </c>
       <c r="F47" t="str">
         <v>Cargada con su ficha</v>
@@ -4766,8 +4768,9 @@
       <c r="D49" t="str">
         <v>LG</v>
       </c>
-      <c r="E49" t="str">
-        <v>TITAN MAXCWT29MDCRS</v>
+      <c r="E49" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITAN MAX
+CWT29MDCRS</v>
       </c>
       <c r="F49" t="str">
         <v>Cargada con su ficha</v>
@@ -4821,8 +4824,9 @@
       <c r="D50" t="str">
         <v>LG</v>
       </c>
-      <c r="E50" t="str">
-        <v>TITAN MAXCWT29MSORS</v>
+      <c r="E50" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITAN MAX
+CWT29MSORS</v>
       </c>
       <c r="F50" t="str">
         <v>Cargada con su ficha</v>
@@ -5239,8 +5243,10 @@
       <c r="D58" t="str">
         <v>LG</v>
       </c>
-      <c r="E58" t="str">
-        <v>GIANT C MAX(CWG27MDCRSCDG27MUCPS)</v>
+      <c r="E58" t="str" xml:space="preserve">
+        <v xml:space="preserve">GIANT C MAX
+(CWG27MDCRS
+CDG27MUCPS)</v>
       </c>
       <c r="F58" t="str">
         <v>Cargada con su ficha</v>
@@ -5292,8 +5298,9 @@
       <c r="D59" t="str">
         <v>LG</v>
       </c>
-      <c r="E59" t="str">
-        <v>TITAN MAXTITAN LIGHT</v>
+      <c r="E59" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITAN MAX
+TITAN LIGHT</v>
       </c>
       <c r="F59" t="str">
         <v>Cargada con su ficha</v>
@@ -5314,7 +5321,7 @@
         <v>no</v>
       </c>
       <c r="L59">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -7016,8 +7023,9 @@
       <c r="D92" t="str">
         <v>LG</v>
       </c>
-      <c r="E92" t="str">
-        <v>GIANT C MAX(CDG27MUCPS)</v>
+      <c r="E92" t="str" xml:space="preserve">
+        <v xml:space="preserve">GIANT C MAX
+(CDG27MUCPS)</v>
       </c>
       <c r="F92" t="str">
         <v>Cargada con su ficha</v>
@@ -7068,8 +7076,9 @@
       <c r="D93" t="str">
         <v>LG</v>
       </c>
-      <c r="E93" t="str">
-        <v>GIANT C MAX(CDG27MSCPS)</v>
+      <c r="E93" t="str" xml:space="preserve">
+        <v xml:space="preserve">GIANT C MAX
+(CDG27MSCPS)</v>
       </c>
       <c r="F93" t="str">
         <v>Cargada con su ficha</v>
@@ -7173,8 +7182,9 @@
       <c r="D95" t="str">
         <v>LG</v>
       </c>
-      <c r="E95" t="str">
-        <v>TITAN LIGHTCDT29MUCPS</v>
+      <c r="E95" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITAN LIGHT
+CDT29MUCPS</v>
       </c>
       <c r="F95" t="str">
         <v>Cargada con su ficha</v>

--- a/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
+++ b/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
@@ -436,7 +436,7 @@
         <v>Códigos en el maestro de Lesly</v>
       </c>
       <c r="B5">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         <v>Cargados con su ficha (descripción + fotos del Word)</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -476,7 +476,7 @@
         <v>Productos nuevos</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -492,12 +492,12 @@
         <v>Precios actualizados con el Excel</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CALIDAD DE LAS 120 FICHAS CARGADAS</v>
+        <v>CALIDAD DE LAS 121 FICHAS CARGADAS</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -524,7 +524,7 @@
         <v>Sin vista de complemento (panel o botonera)</v>
       </c>
       <c r="B18">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -548,7 +548,7 @@
         <v>Códigos que comparten la foto del equipo con otro</v>
       </c>
       <c r="B21">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -572,7 +572,7 @@
         <v>Tabla de cabecera incompleta</v>
       </c>
       <c r="B24">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
@@ -696,7 +696,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="58.83203125" customWidth="1"/>
@@ -1373,7 +1373,7 @@
         <v>LAV280</v>
       </c>
       <c r="B40" t="str">
-        <v>LAVADORA INDUST. FLOT. MOD. FX280, FUERZA 400G, CONTROL X, PANEL FRONTAL INOX., PANEL LATERAL GRIS, CILINDRO INOX., CALENTAMIENTO BOILER FED, CAP.: 28KG, Q (220/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIDIGA, MOD. RX280, CAP: 28 KG, FUERZA 100G, CONTROL X + , PANEL SUPERIOR, FRONTAL LATERAL INOXIDABLE, CIL. INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, P(220V/60HZ/3PH)</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>LAV350</v>
+        <v>LAV2801</v>
       </c>
       <c r="B41" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: RX350, FUERZA: 200G, CONTROL X,CAP 35KG, P. FRONTAL, LATERIAL INOX., BOILER FED + PREP. PARA VAPOR, CILINDRO INOX., X(220V/60HZ/1PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIDIGA, MOD. RX280, CAP: 28 KG, FUERZA 100G, CONTROL X + , PANEL SUPERIOR, FRONTAL LATERAL INOXIDABLE, CIL. INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, P(380V/60HZ/3PH)</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>LAV3501</v>
+        <v>LAV350</v>
       </c>
       <c r="B42" t="str">
-        <v>LAVADORA IND. RIGIDA MOD.RX350, CONTROL X +, FUERZA:100G, CAP.: 35KG, BOILER FED + PREPARADO VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX, CILNDRO INOX., P (380V/60/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: RX350, FUERZA: 200G, CONTROL X,CAP 35KG, P. FRONTAL, LATERIAL INOX., BOILER FED + PREP. PARA VAPOR, CILINDRO INOX., X(220V/60HZ/1PH)</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>LAVG080</v>
+        <v>LAV3501</v>
       </c>
       <c r="B43" t="str">
-        <v>LAVADORA INDUSTRIAL RÍGIDA, MOD: UCG080, FUERZA: 200G, CONTROL M9, PANEL LATERAL,FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, CAP: 36 KG, (220V/60HZ/1-3PH)</v>
+        <v>LAVADORA IND. RIGIDA MOD.RX350, CONTROL X +, FUERZA:100G, CAP.: 35KG, BOILER FED + PREPARADO VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX, CILNDRO INOX., P (380V/60/3PH)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>LAVG50</v>
+        <v>LAVG080</v>
       </c>
       <c r="B44" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP50, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 50 KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RÍGIDA, MOD: UCG080, FUERZA: 200G, CONTROL M9, PANEL LATERAL,FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, CAP: 36 KG, (220V/60HZ/1-3PH)</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LAVG70</v>
+        <v>LAVG50</v>
       </c>
       <c r="B45" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP70, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 70 KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP50, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 50 KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>LAVGIA13</v>
+        <v>LAVG70</v>
       </c>
       <c r="B46" t="str">
-        <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX APILABLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MDCRS</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP70, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 70 KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>LAVGIA132</v>
+        <v>LAVGIA13</v>
       </c>
       <c r="B47" t="str">
-        <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX SINGLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MSCRS</v>
+        <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX APILABLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MDCRS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>LAVGP100</v>
+        <v>LAVGIA132</v>
       </c>
       <c r="B48" t="str">
-        <v>LAVADORA IND. EXTRACTORA SAILSTAR MOD.GP100 CAP.100KG C/CALENTAMIENTO A VAPOR 220V/60HZ/3PH</v>
+        <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX SINGLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MSCRS</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>LAVMA17</v>
+        <v>LAVGP100</v>
       </c>
       <c r="B49" t="str">
-        <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX APILABLE, CAP:17KG, 220/60/1PH, COD:CWT29MDCRS</v>
+        <v>LAVADORA IND. EXTRACTORA SAILSTAR MOD.GP100 CAP.100KG C/CALENTAMIENTO A VAPOR 220V/60HZ/3PH</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LAVMA172</v>
+        <v>LAVMA17</v>
       </c>
       <c r="B50" t="str">
-        <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX SINGLE, CAP:17KG, 220/60/1PH, COD.: CWT29MSORS</v>
+        <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX APILABLE, CAP:17KG, 220/60/1PH, COD:CWT29MDCRS</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1557,44 +1557,44 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>LAVP15</v>
+        <v>LAVMA172</v>
       </c>
       <c r="B51" t="str">
-        <v>LAVADORA AL SECO SAILSTAR MOD: P15 C/CALENTAMIENTO ELECTRICO CAP: 8KG 220/1/3P/60HZ S: 130918</v>
+        <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX SINGLE, CAP:17KG, 220/60/1PH, COD.: CWT29MSORS</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>falta</v>
       </c>
       <c r="E51" t="str">
-        <v>falta</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LAVS17</v>
+        <v>LAVP15</v>
       </c>
       <c r="B52" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA AL SECO SAILSTAR MOD: P15 C/CALENTAMIENTO ELECTRICO CAP: 8KG 220/1/3P/60HZ S: 130918</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
         <v>falta</v>
-      </c>
-      <c r="E52" t="str">
-        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>LAVS17E</v>
+        <v>LAVS17</v>
       </c>
       <c r="B53" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>LAVS23</v>
+        <v>LAVS17E</v>
       </c>
       <c r="B54" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1625,10 +1625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>LAVS23E</v>
+        <v>LAVS23</v>
       </c>
       <c r="B55" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>LAVS40</v>
+        <v>LAVS23E</v>
       </c>
       <c r="B56" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS40, CALENTAMIENTO A VAPOR, PANEL FRONTAL Y CILINDRO INOXIDABLE, 300G, CAP.: 40KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>LAVT080</v>
+        <v>LAVS40</v>
       </c>
       <c r="B57" t="str">
-        <v>LAVADORA IND. RIGIDA MOD:UCT080 CAP: 36 KG, FUERZA 100G OPL, CONTROL M9, CILINDRO INOX, PREPARADO A VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., (220V/60HZ/1-3PH), 15 AMP</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS40, CALENTAMIENTO A VAPOR, PANEL FRONTAL Y CILINDRO INOXIDABLE, 300G, CAP.: 40KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>LAVUC100</v>
+        <v>LAVT080</v>
       </c>
       <c r="B58" t="str">
-        <v>LAV.IND,RIG,MOD.UC100,OPL,200G,M9,X,220V/60HZ/1-3PH,CAP.45KG,PAN.ACER.CILN.STAND.PREP.VAP.</v>
+        <v>LAVADORA IND. RIGIDA MOD:UCT080 CAP: 36 KG, FUERZA 100G OPL, CONTROL M9, CILINDRO INOX, PREPARADO A VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., (220V/60HZ/1-3PH), 15 AMP</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LAVUW045</v>
+        <v>LAVUC100</v>
       </c>
       <c r="B59" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, X (220V/60HZ/1-3 PH)</v>
+        <v>LAV.IND,RIG,MOD.UC100,OPL,200G,M9,X,220V/60HZ/1-3PH,CAP.45KG,PAN.ACER.CILN.STAND.PREP.VAP.</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>LAVUY2802</v>
+        <v>LAVUW045</v>
       </c>
       <c r="B60" t="str">
-        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY280, FUERZA 450G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO BOILER FED + PREPARADO PARA VAPOR, CAP.: 28KG, X(220V/60HZ/1PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, X (220V/60HZ/1-3 PH)</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>LAVUY4502</v>
+        <v>LAVUY2802</v>
       </c>
       <c r="B61" t="str">
-        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY450, FUERZA 360G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO DIRECTO CON VAPOR, CAP.: 45 KG, Q(220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY280, FUERZA 450G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO BOILER FED + PREPARADO PARA VAPOR, CAP.: 28KG, X(220V/60HZ/1PH)</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>LAVW045</v>
+        <v>LAVUY4502</v>
       </c>
       <c r="B62" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, P (380V/60HZ/3 PH)</v>
+        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY450, FUERZA 360G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO DIRECTO CON VAPOR, CAP.: 45 KG, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>LAVW065</v>
+        <v>LAVW045</v>
       </c>
       <c r="B63" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UWT065, FUERZA: 400 G, CONTROL UNILINC TOUCH, CAP. 29.5 KG, SIS. OPL, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., C/ DOSIFICADOR MANUAL, C/ OTISPRAY, (220V/60HZ/1-3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, P (380V/60HZ/3 PH)</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>LAVW085</v>
+        <v>LAVW065</v>
       </c>
       <c r="B64" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA MOD: UW085N, 200G, CONTROL: M30, CAP:38.5 KG, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL, CILINDRO INOX, S / DOSIFICADOR MANUAL, SIN OTISPRAY, (220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UWT065, FUERZA: 400 G, CONTROL UNILINC TOUCH, CAP. 29.5 KG, SIS. OPL, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., C/ DOSIFICADOR MANUAL, C/ OTISPRAY, (220V/60HZ/1-3PH)</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>LAVW0851</v>
+        <v>LAVW085</v>
       </c>
       <c r="B65" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (380V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA MOD: UW085N, 200G, CONTROL: M30, CAP:38.5 KG, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL, CILINDRO INOX, S / DOSIFICADOR MANUAL, SIN OTISPRAY, (220V/60HZ/3PH)</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>LAVW0852</v>
+        <v>LAVW0851</v>
       </c>
       <c r="B66" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (380V/60HZ/3PH)</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1829,10 +1829,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>LAVW105</v>
+        <v>LAVW0852</v>
       </c>
       <c r="B67" t="str">
-        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (220V/60HZ/3PH)</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>LAVW1051</v>
+        <v>LAVW105</v>
       </c>
       <c r="B68" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD:UWT105, FUERZA 300G, CAP: 47.6KG, OPL, CONTROL: UNILINC TOUCH, PANEL LATERAL, FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(220V/60HZ/3PH)</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LAVW1301</v>
+        <v>LAVW1051</v>
       </c>
       <c r="B69" t="str">
-        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD:UWT105, FUERZA 300G, CAP: 47.6KG, OPL, CONTROL: UNILINC TOUCH, PANEL LATERAL, FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>LAVW1302</v>
+        <v>LAVW1301</v>
       </c>
       <c r="B70" t="str">
-        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL: UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, Q(220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1897,33 +1897,33 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>MEFENI1</v>
+        <v>LAVW1302</v>
       </c>
       <c r="B71" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE CON TERMOSTATO, SIDI MONDIAL MOD FENIX, 220/1/60HZ S:</v>
+        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL: UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
         <v>falta</v>
       </c>
-      <c r="D71" t="str">
-        <v/>
-      </c>
       <c r="E71" t="str">
-        <v>falta</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>MEVA2</v>
+        <v>MEFENI1</v>
       </c>
       <c r="B72" t="str">
-        <v>MESA VAPORIZADORA SIN CALDERO EFALMV2000</v>
+        <v>MESA DE PLANCHADO ASPIRANTE CON TERMOSTATO, SIDI MONDIAL MOD FENIX, 220/1/60HZ S:</v>
       </c>
       <c r="C72" t="str">
         <v>falta</v>
       </c>
       <c r="D72" t="str">
-        <v>falta</v>
+        <v/>
       </c>
       <c r="E72" t="str">
         <v>falta</v>
@@ -1931,16 +1931,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>PRE702U</v>
+        <v>MEVA2</v>
       </c>
       <c r="B73" t="str">
-        <v>PRENSA MANUAL SIDI MONDIAL MOD: ST-702/U, VAPOR EXTERNO PARA PLATO, ASPIRANTE INCORP. 220V/60HZ/ 1PH S: 284236</v>
+        <v>MESA VAPORIZADORA SIN CALDERO EFALMV2000</v>
       </c>
       <c r="C73" t="str">
         <v>falta</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>falta</v>
       </c>
       <c r="E73" t="str">
         <v>falta</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>PRN750U</v>
+        <v>PRE702U</v>
       </c>
       <c r="B74" t="str">
-        <v>PRENSA NEUMATICA ASPIR. 2 PULSAD. SIDI MONDIAL MOD: CT-750/U, VAPOR EXTERNO PARA PLATO 220V/60HZ/1PH S: 284237</v>
+        <v>PRENSA MANUAL SIDI MONDIAL MOD: ST-702/U, VAPOR EXTERNO PARA PLATO, ASPIRANTE INCORP. 220V/60HZ/ 1PH S: 284236</v>
       </c>
       <c r="C74" t="str">
         <v>falta</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>PRPE01</v>
+        <v>PRN750U</v>
       </c>
       <c r="B75" t="str">
-        <v>PRENSA DE PLANCHADO ELECTRICA (MESA) CON CALENTAMIENTO A VAPOR MOD.PCV 220V/60HZ/1PH</v>
+        <v>PRENSA NEUMATICA ASPIR. 2 PULSAD. SIDI MONDIAL MOD: CT-750/U, VAPOR EXTERNO PARA PLATO 220V/60HZ/1PH S: 284237</v>
       </c>
       <c r="C75" t="str">
         <v>falta</v>
@@ -1982,13 +1982,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SECEF60</v>
+        <v>PRPE01</v>
       </c>
       <c r="B76" t="str">
-        <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS60 ,CAP. 60 KG, 5HP, 220V/60HZ/TRIFASICO</v>
+        <v>PRENSA DE PLANCHADO ELECTRICA (MESA) CON CALENTAMIENTO A VAPOR MOD.PCV 220V/60HZ/1PH</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>falta</v>
       </c>
       <c r="D76" t="str">
         <v/>
@@ -1999,27 +1999,27 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SECU200</v>
+        <v>SECEF60</v>
       </c>
       <c r="B77" t="str">
-        <v>SECADORA INDUSTRIAL, MOD.: UT200L, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP. 90 KG, GAS GLP, C/ OPTIDRY, Q(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS60 ,CAP. 60 KG, 5HP, 220V/60HZ/TRIFASICO</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
         <v>falta</v>
-      </c>
-      <c r="E77" t="str">
-        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SECU2001</v>
+        <v>SECU200</v>
       </c>
       <c r="B78" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT200N, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP: 90KG, GAS NATURAL, C/ OPTIDRY , Q (220V/60HZ/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD.: UT200L, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP. 90 KG, GAS GLP, C/ OPTIDRY, Q(220V/60HZ/1-3PH)</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -2031,9 +2031,26 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SECU2001</v>
+      </c>
+      <c r="B79" t="str">
+        <v>SECADORA INDUSTRIAL, MOD: UT200N, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP: 90KG, GAS NATURAL, C/ OPTIDRY , Q (220V/60HZ/3PH)</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>falta</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E79"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2211,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P134"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="58.83203125" customWidth="1"/>
@@ -4001,7 +4018,7 @@
         <v>57</v>
       </c>
       <c r="M34" t="str">
-        <v>LAV2402, LAV280</v>
+        <v>LAV2402, LAV280, LAV2801</v>
       </c>
       <c r="N34">
         <v>14500</v>
@@ -4011,7 +4028,7 @@
       </c>
       <c r="P34" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
-Usa la misma foto de equipo que LAV2402, LAV280
+Usa la misma foto de equipo que LAV2402, LAV280, LAV2801
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
@@ -4262,7 +4279,7 @@
         <v>52</v>
       </c>
       <c r="M39" t="str">
-        <v>LAV1355, LAV280</v>
+        <v>LAV1355, LAV280, LAV2801</v>
       </c>
       <c r="N39">
         <v>14350</v>
@@ -4272,7 +4289,7 @@
       </c>
       <c r="P39" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
-Usa la misma foto de equipo que LAV1355, LAV280
+Usa la misma foto de equipo que LAV1355, LAV280, LAV2801
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
@@ -4281,7 +4298,7 @@
         <v>LAV280</v>
       </c>
       <c r="B40" t="str">
-        <v>LAVADORA INDUST. FLOT. MOD. FX280, FUERZA 400G, CONTROL X, PANEL FRONTAL INOX., PANEL LATERAL GRIS, CILINDRO INOX., CALENTAMIENTO BOILER FED, CAP.: 28KG, Q (220/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIDIGA, MOD. RX280, CAP: 28 KG, FUERZA 100G, CONTROL X + , PANEL SUPERIOR, FRONTAL LATERAL INOXIDABLE, CIL. INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, P(220V/60HZ/3PH)</v>
       </c>
       <c r="C40" t="str">
         <v>PRIMUS</v>
@@ -4314,26 +4331,26 @@
         <v>52</v>
       </c>
       <c r="M40" t="str">
-        <v>LAV1355, LAV2402</v>
+        <v>LAV1355, LAV2402, LAV2801</v>
       </c>
       <c r="N40">
-        <v>22500</v>
+        <v>14900</v>
       </c>
       <c r="O40" t="str">
         <v>activo</v>
       </c>
       <c r="P40" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
-Usa la misma foto de equipo que LAV1355, LAV2402
+Usa la misma foto de equipo que LAV1355, LAV2402, LAV2801
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41" t="str">
-        <v>LAV350</v>
+        <v>LAV2801</v>
       </c>
       <c r="B41" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: RX350, FUERZA: 200G, CONTROL X,CAP 35KG, P. FRONTAL, LATERIAL INOX., BOILER FED + PREP. PARA VAPOR, CILINDRO INOX., X(220V/60HZ/1PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIDIGA, MOD. RX280, CAP: 28 KG, FUERZA 100G, CONTROL X + , PANEL SUPERIOR, FRONTAL LATERAL INOXIDABLE, CIL. INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, P(380V/60HZ/3PH)</v>
       </c>
       <c r="C41" t="str">
         <v>PRIMUS</v>
@@ -4342,49 +4359,50 @@
         <v>PRIMUS</v>
       </c>
       <c r="E41" t="str">
-        <v>RX 350</v>
+        <v>RX280</v>
       </c>
       <c r="F41" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G41" t="str">
-        <v>LAV350-LAVADORA RX350-XCONTROL-200G-INOX-220V-1PH.docx</v>
+        <v>LAV2801-LAVADORA RX280-X CONTROL PLUS-100G-INOX-380V-3PH.docx</v>
       </c>
       <c r="H41" t="str">
-        <v>sí · 637×841 px · 300 ppp</v>
+        <v>sí · 637×895 px · 300 ppp</v>
       </c>
       <c r="I41">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="J41" t="str">
-        <v>sí · 301 ppp</v>
+        <v>sí · 299 ppp</v>
       </c>
       <c r="K41" t="str">
         <v>no</v>
       </c>
       <c r="L41">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>LAV1355, LAV2402, LAV280</v>
       </c>
       <c r="N41">
-        <v>19900</v>
+        <v>15200</v>
       </c>
       <c r="O41" t="str">
         <v>activo</v>
       </c>
       <c r="P41" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
+Usa la misma foto de equipo que LAV1355, LAV2402, LAV280
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>LAV3501</v>
+        <v>LAV350</v>
       </c>
       <c r="B42" t="str">
-        <v>LAVADORA IND. RIGIDA MOD.RX350, CONTROL X +, FUERZA:100G, CAP.: 35KG, BOILER FED + PREPARADO VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX, CILNDRO INOX., P (380V/60/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: RX350, FUERZA: 200G, CONTROL X,CAP 35KG, P. FRONTAL, LATERIAL INOX., BOILER FED + PREP. PARA VAPOR, CILINDRO INOX., X(220V/60HZ/1PH)</v>
       </c>
       <c r="C42" t="str">
         <v>PRIMUS</v>
@@ -4399,13 +4417,13 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G42" t="str">
-        <v>LAV3501-LAVADORA RX350-XCONTROL-100G-INOX-380V-3PH.docx</v>
+        <v>LAV350-LAVADORA RX350-XCONTROL-200G-INOX-220V-1PH.docx</v>
       </c>
       <c r="H42" t="str">
-        <v>sí · 640×910 px · 301 ppp</v>
+        <v>sí · 637×841 px · 300 ppp</v>
       </c>
       <c r="I42">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="J42" t="str">
         <v>sí · 301 ppp</v>
@@ -4417,68 +4435,119 @@
         <v>53</v>
       </c>
       <c r="M42" t="str">
-        <v>LAV2401</v>
+        <v/>
       </c>
       <c r="N42">
-        <v>21500</v>
+        <v>19900</v>
       </c>
       <c r="O42" t="str">
         <v>activo</v>
       </c>
       <c r="P42" t="str" xml:space="preserve">
+        <v xml:space="preserve">No trae vista de complemento (panel o botonera)
+La tabla de cabecera no dice: calentamiento</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>LAV3501</v>
+      </c>
+      <c r="B43" t="str">
+        <v>LAVADORA IND. RIGIDA MOD.RX350, CONTROL X +, FUERZA:100G, CAP.: 35KG, BOILER FED + PREPARADO VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX, CILNDRO INOX., P (380V/60/3PH)</v>
+      </c>
+      <c r="C43" t="str">
+        <v>PRIMUS</v>
+      </c>
+      <c r="D43" t="str">
+        <v>PRIMUS</v>
+      </c>
+      <c r="E43" t="str">
+        <v>RX 350</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Cargada con su ficha</v>
+      </c>
+      <c r="G43" t="str">
+        <v>LAV3501-LAVADORA RX350-XCONTROL-100G-INOX-380V-3PH.docx</v>
+      </c>
+      <c r="H43" t="str">
+        <v>sí · 640×910 px · 301 ppp</v>
+      </c>
+      <c r="I43">
+        <v>136</v>
+      </c>
+      <c r="J43" t="str">
+        <v>sí · 301 ppp</v>
+      </c>
+      <c r="K43" t="str">
+        <v>no</v>
+      </c>
+      <c r="L43">
+        <v>53</v>
+      </c>
+      <c r="M43" t="str">
+        <v>LAV2401</v>
+      </c>
+      <c r="N43">
+        <v>21500</v>
+      </c>
+      <c r="O43" t="str">
+        <v>activo</v>
+      </c>
+      <c r="P43" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (136 ppp al tamaño impreso; se amplió a 301)
 Usa la misma foto de equipo que LAV2401
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
         <v>LAVG080</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B44" t="str">
         <v>LAVADORA INDUSTRIAL RÍGIDA, MOD: UCG080, FUERZA: 200G, CONTROL M9, PANEL LATERAL,FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, CAP: 36 KG, (220V/60HZ/1-3PH)</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C44" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D44" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E43" t="str">
+      <c r="E44" t="str">
         <v>UCG080</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F44" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G43" t="str">
+      <c r="G44" t="str">
         <v>LAVG080-LAVADORA UCG080-M9-INOX-100G-220V.docx</v>
       </c>
-      <c r="H43" t="str">
+      <c r="H44" t="str">
         <v>sí · 636×892 px · 299 ppp</v>
       </c>
-      <c r="I43">
+      <c r="I44">
         <v>140</v>
       </c>
-      <c r="J43" t="str">
+      <c r="J44" t="str">
         <v>NO</v>
       </c>
-      <c r="K43" t="str">
+      <c r="K44" t="str">
         <v>sí · 287 ppp</v>
       </c>
-      <c r="L43">
+      <c r="L44">
         <v>41</v>
       </c>
-      <c r="M43" t="str">
+      <c r="M44" t="str">
         <v>LAVT080, LAVUC100</v>
       </c>
-      <c r="N43">
+      <c r="N44">
         <v>21900</v>
       </c>
-      <c r="O43" t="str">
+      <c r="O44" t="str">
         <v>activo</v>
       </c>
-      <c r="P43" t="str" xml:space="preserve">
+      <c r="P44" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVT080, LAVUC100
@@ -4486,160 +4555,160 @@
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44" t="str">
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
         <v>LAVG50</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B45" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP50, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 50 KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C45" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D45" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E44" t="str">
+      <c r="E45" t="str">
         <v>GP50</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F45" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G44" t="str">
+      <c r="G45" t="str">
         <v>LAVG50-Lavadora GP 50 KG V1 PROGRAMADOR DIGITAL.doc</v>
       </c>
-      <c r="H44" t="str">
+      <c r="H45" t="str">
         <v>sí · 637×712 px · 300 ppp</v>
       </c>
-      <c r="I44">
+      <c r="I45">
         <v>140</v>
       </c>
-      <c r="J44" t="str">
+      <c r="J45" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K44" t="str">
+      <c r="K45" t="str">
         <v>no</v>
       </c>
-      <c r="L44">
+      <c r="L45">
         <v>49</v>
       </c>
-      <c r="M44" t="str">
+      <c r="M45" t="str">
         <v>LAVG70, LAVGP100</v>
       </c>
-      <c r="N44">
+      <c r="N45">
         <v>39500</v>
       </c>
-      <c r="O44" t="str">
+      <c r="O45" t="str">
         <v>activo</v>
       </c>
-      <c r="P44" t="str" xml:space="preserve">
+      <c r="P45" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 300)
 Usa la misma foto de equipo que LAVG70, LAVGP100
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45" t="str">
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
         <v>LAVG70</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B46" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP70, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 70 KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C46" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D46" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E46" t="str">
         <v>GP70</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F46" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G45" t="str">
+      <c r="G46" t="str">
         <v>LAVG70-Lavadora GP 70 KG V1 PROGRAMADOR DIGITAL.doc</v>
       </c>
-      <c r="H45" t="str">
+      <c r="H46" t="str">
         <v>sí · 637×712 px · 300 ppp</v>
       </c>
-      <c r="I45">
+      <c r="I46">
         <v>140</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J46" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K45" t="str">
+      <c r="K46" t="str">
         <v>no</v>
       </c>
-      <c r="L45">
+      <c r="L46">
         <v>48</v>
       </c>
-      <c r="M45" t="str">
+      <c r="M46" t="str">
         <v>LAVG50, LAVGP100</v>
       </c>
-      <c r="N45">
+      <c r="N46">
         <v>45500</v>
       </c>
-      <c r="O45" t="str">
+      <c r="O46" t="str">
         <v>activo</v>
       </c>
-      <c r="P45" t="str" xml:space="preserve">
+      <c r="P46" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 300)
 Usa la misma foto de equipo que LAVG50, LAVGP100
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46" t="str">
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
         <v>LAVGIA13</v>
       </c>
-      <c r="B46" t="str">
+      <c r="B47" t="str">
         <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX APILABLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MDCRS</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C47" t="str">
         <v>LG</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D47" t="str">
         <v>LG</v>
       </c>
-      <c r="E46" t="str" xml:space="preserve">
+      <c r="E47" t="str" xml:space="preserve">
         <v xml:space="preserve">GIANT C MAX
 (CWG27MDCRS)</v>
       </c>
-      <c r="F46" t="str">
+      <c r="F47" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G46" t="str">
+      <c r="G47" t="str">
         <v>LAVGIA13-Lavadora Giant C Max 13 kg OPL Apilable.doc</v>
       </c>
-      <c r="H46" t="str">
+      <c r="H47" t="str">
         <v>sí · 637×890 px · 300 ppp</v>
       </c>
-      <c r="I46">
+      <c r="I47">
         <v>140</v>
       </c>
-      <c r="J46" t="str">
+      <c r="J47" t="str">
         <v>NO</v>
       </c>
-      <c r="K46" t="str">
+      <c r="K47" t="str">
         <v>no</v>
       </c>
-      <c r="L46">
+      <c r="L47">
         <v>29</v>
       </c>
-      <c r="M46" t="str">
+      <c r="M47" t="str">
         <v>LAVMA17</v>
       </c>
-      <c r="N46">
+      <c r="N47">
         <v>2250</v>
       </c>
-      <c r="O46" t="str">
+      <c r="O47" t="str">
         <v>activo</v>
       </c>
-      <c r="P46" t="str" xml:space="preserve">
+      <c r="P47" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 300)
@@ -4648,161 +4717,161 @@
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47" t="str">
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
         <v>LAVGIA132</v>
       </c>
-      <c r="B47" t="str">
+      <c r="B48" t="str">
         <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX SINGLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MSCRS</v>
       </c>
-      <c r="C47" t="str">
+      <c r="C48" t="str">
         <v>LG</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D48" t="str">
         <v>LG</v>
       </c>
-      <c r="E47" t="str" xml:space="preserve">
+      <c r="E48" t="str" xml:space="preserve">
         <v xml:space="preserve">GIANT C MAX
 (CWG27MSCRS)</v>
       </c>
-      <c r="F47" t="str">
+      <c r="F48" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G47" t="str">
+      <c r="G48" t="str">
         <v>LAVGIA132-Lavadora Giant C Max 13 kg OPL.doc</v>
       </c>
-      <c r="H47" t="str">
+      <c r="H48" t="str">
         <v>sí · 502×703 px · 236 ppp</v>
       </c>
-      <c r="I47">
+      <c r="I48">
         <v>285</v>
       </c>
-      <c r="J47" t="str">
+      <c r="J48" t="str">
         <v>NO</v>
       </c>
-      <c r="K47" t="str">
+      <c r="K48" t="str">
         <v>no</v>
       </c>
-      <c r="L47">
+      <c r="L48">
         <v>29</v>
       </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
-      <c r="N47">
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48">
         <v>2250</v>
       </c>
-      <c r="O47" t="str">
+      <c r="O48" t="str">
         <v>activo</v>
       </c>
-      <c r="P47" t="str" xml:space="preserve">
+      <c r="P48" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Trae 1 imagen(es) de más: en la cotización solo entran el logo, el equipo y una vista de complemento
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48" t="str">
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
         <v>LAVGP100</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B49" t="str">
         <v>LAVADORA IND. EXTRACTORA SAILSTAR MOD.GP100 CAP.100KG C/CALENTAMIENTO A VAPOR 220V/60HZ/3PH</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C49" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D49" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E48" t="str">
+      <c r="E49" t="str">
         <v>GP100</v>
       </c>
-      <c r="F48" t="str">
+      <c r="F49" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G48" t="str">
+      <c r="G49" t="str">
         <v>LAVGP100-Lavadora GP 100 KG V1 PROGRAMADOR DIGITAL.doc</v>
       </c>
-      <c r="H48" t="str">
+      <c r="H49" t="str">
         <v>sí · 637×712 px · 300 ppp</v>
       </c>
-      <c r="I48">
+      <c r="I49">
         <v>140</v>
       </c>
-      <c r="J48" t="str">
+      <c r="J49" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K48" t="str">
+      <c r="K49" t="str">
         <v>no</v>
       </c>
-      <c r="L48">
+      <c r="L49">
         <v>49</v>
       </c>
-      <c r="M48" t="str">
+      <c r="M49" t="str">
         <v>LAVG50, LAVG70</v>
       </c>
-      <c r="N48">
+      <c r="N49">
         <v>72500</v>
       </c>
-      <c r="O48" t="str">
+      <c r="O49" t="str">
         <v>activo</v>
       </c>
-      <c r="P48" t="str" xml:space="preserve">
+      <c r="P49" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 300)
 Usa la misma foto de equipo que LAVG50, LAVG70
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49" t="str">
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
         <v>LAVMA17</v>
       </c>
-      <c r="B49" t="str">
+      <c r="B50" t="str">
         <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX APILABLE, CAP:17KG, 220/60/1PH, COD:CWT29MDCRS</v>
       </c>
-      <c r="C49" t="str">
+      <c r="C50" t="str">
         <v>LG</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D50" t="str">
         <v>LG</v>
       </c>
-      <c r="E49" t="str" xml:space="preserve">
+      <c r="E50" t="str" xml:space="preserve">
         <v xml:space="preserve">TITAN MAX
 CWT29MDCRS</v>
       </c>
-      <c r="F49" t="str">
+      <c r="F50" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G49" t="str">
+      <c r="G50" t="str">
         <v>LAVMA17-Lavadora Titan Max 17 kg -Apilable.doc</v>
       </c>
-      <c r="H49" t="str">
+      <c r="H50" t="str">
         <v>sí · 637×890 px · 300 ppp</v>
       </c>
-      <c r="I49">
+      <c r="I50">
         <v>140</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J50" t="str">
         <v>NO</v>
       </c>
-      <c r="K49" t="str">
+      <c r="K50" t="str">
         <v>no</v>
       </c>
-      <c r="L49">
+      <c r="L50">
         <v>29</v>
       </c>
-      <c r="M49" t="str">
+      <c r="M50" t="str">
         <v>LAVGIA13</v>
       </c>
-      <c r="N49">
+      <c r="N50">
         <v>3999</v>
       </c>
-      <c r="O49" t="str">
+      <c r="O50" t="str">
         <v>activo</v>
       </c>
-      <c r="P49" t="str" xml:space="preserve">
+      <c r="P50" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 300)
@@ -4811,54 +4880,54 @@
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50" t="str">
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
         <v>LAVMA172</v>
       </c>
-      <c r="B50" t="str">
+      <c r="B51" t="str">
         <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX SINGLE, CAP:17KG, 220/60/1PH, COD.: CWT29MSORS</v>
       </c>
-      <c r="C50" t="str">
+      <c r="C51" t="str">
         <v>LG</v>
       </c>
-      <c r="D50" t="str">
+      <c r="D51" t="str">
         <v>LG</v>
       </c>
-      <c r="E50" t="str" xml:space="preserve">
+      <c r="E51" t="str" xml:space="preserve">
         <v xml:space="preserve">TITAN MAX
 CWT29MSORS</v>
       </c>
-      <c r="F50" t="str">
+      <c r="F51" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G51" t="str">
         <v>LAVMA172-Lavadora Titan Max 17 kg.doc</v>
       </c>
-      <c r="H50" t="str">
+      <c r="H51" t="str">
         <v>sí · 636×956 px · 299 ppp</v>
       </c>
-      <c r="I50">
+      <c r="I51">
         <v>144</v>
       </c>
-      <c r="J50" t="str">
+      <c r="J51" t="str">
         <v>NO</v>
       </c>
-      <c r="K50" t="str">
+      <c r="K51" t="str">
         <v>no</v>
       </c>
-      <c r="L50">
+      <c r="L51">
         <v>29</v>
       </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-      <c r="N50">
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51">
         <v>3950</v>
       </c>
-      <c r="O50" t="str">
+      <c r="O51" t="str">
         <v>activo</v>
       </c>
-      <c r="P50" t="str" xml:space="preserve">
+      <c r="P51" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (144 ppp al tamaño impreso; se amplió a 299)
@@ -4866,363 +4935,363 @@
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="51" xml:space="preserve">
-      <c r="A51" t="str">
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
         <v>LAVP15</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B52" t="str">
         <v>LAVADORA AL SECO SAILSTAR MOD: P15 C/CALENTAMIENTO ELECTRICO CAP: 8KG 220/1/3P/60HZ S: 130918</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C52" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D52" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E52" t="str">
         <v>P15</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F52" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G52" t="str">
         <v>LAVP15-Seco P15 8-10 kg.doc</v>
       </c>
-      <c r="H51" t="str">
+      <c r="H52" t="str">
         <v>sí · 550×621 px · 259 ppp</v>
       </c>
-      <c r="I51">
+      <c r="I52">
         <v>235</v>
       </c>
-      <c r="J51" t="str">
+      <c r="J52" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K51" t="str">
+      <c r="K52" t="str">
         <v>no</v>
       </c>
-      <c r="L51">
+      <c r="L52">
         <v>23</v>
       </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51">
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52">
         <v>21500</v>
       </c>
-      <c r="O51" t="str">
+      <c r="O52" t="str">
         <v>activo</v>
       </c>
-      <c r="P51" t="str" xml:space="preserve">
+      <c r="P52" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 La tabla de cabecera no dice: panel</v>
       </c>
     </row>
-    <row r="52" xml:space="preserve">
-      <c r="A52" t="str">
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
         <v>LAVS17</v>
       </c>
-      <c r="B52" t="str">
+      <c r="B53" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C52" t="str">
+      <c r="C53" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D52" t="str">
+      <c r="D53" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E52" t="str">
+      <c r="E53" t="str">
         <v>SS17</v>
       </c>
-      <c r="F52" t="str">
+      <c r="F53" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G52" t="str">
+      <c r="G53" t="str">
         <v>LAVS17-Lavadora Centrifuga SS17 17 kg_Panel multifuncion vapor.doc</v>
       </c>
-      <c r="H52" t="str">
+      <c r="H53" t="str">
         <v>sí · 639×894 px · 301 ppp</v>
       </c>
-      <c r="I52">
+      <c r="I53">
         <v>187</v>
       </c>
-      <c r="J52" t="str">
+      <c r="J53" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K52" t="str">
+      <c r="K53" t="str">
         <v>no</v>
       </c>
-      <c r="L52">
+      <c r="L53">
         <v>49</v>
       </c>
-      <c r="M52" t="str">
+      <c r="M53" t="str">
         <v>LAVS17E</v>
       </c>
-      <c r="N52">
+      <c r="N53">
         <v>11900</v>
       </c>
-      <c r="O52" t="str">
+      <c r="O53" t="str">
         <v>activo</v>
       </c>
-      <c r="P52" t="str" xml:space="preserve">
+      <c r="P53" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que LAVS17E
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53" t="str">
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
         <v>LAVS17E</v>
       </c>
-      <c r="B53" t="str">
+      <c r="B54" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C53" t="str">
+      <c r="C54" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D53" t="str">
+      <c r="D54" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E53" t="str">
+      <c r="E54" t="str">
         <v>SS17 E</v>
       </c>
-      <c r="F53" t="str">
+      <c r="F54" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G53" t="str">
+      <c r="G54" t="str">
         <v>LAVS17E-Lavadora Centrifuga SS17E 17 kg_Panel multifuncion electrico.doc</v>
       </c>
-      <c r="H53" t="str">
+      <c r="H54" t="str">
         <v>sí · 639×894 px · 301 ppp</v>
       </c>
-      <c r="I53">
+      <c r="I54">
         <v>187</v>
       </c>
-      <c r="J53" t="str">
+      <c r="J54" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K53" t="str">
+      <c r="K54" t="str">
         <v>no</v>
       </c>
-      <c r="L53">
+      <c r="L54">
         <v>50</v>
       </c>
-      <c r="M53" t="str">
+      <c r="M54" t="str">
         <v>LAVS17</v>
       </c>
-      <c r="N53">
+      <c r="N54">
         <v>12900</v>
       </c>
-      <c r="O53" t="str">
+      <c r="O54" t="str">
         <v>activo</v>
       </c>
-      <c r="P53" t="str" xml:space="preserve">
+      <c r="P54" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que LAVS17
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54" t="str">
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
         <v>LAVS23</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B55" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C54" t="str">
+      <c r="C55" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D54" t="str">
+      <c r="D55" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E54" t="str">
+      <c r="E55" t="str">
         <v>SS23</v>
       </c>
-      <c r="F54" t="str">
+      <c r="F55" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G54" t="str">
+      <c r="G55" t="str">
         <v>LAVS23-Lavadora Centrifuga SS23 23 kg_Panel multifuncion vapor.doc</v>
       </c>
-      <c r="H54" t="str">
+      <c r="H55" t="str">
         <v>sí · 638×893 px · 300 ppp</v>
       </c>
-      <c r="I54">
+      <c r="I55">
         <v>163</v>
       </c>
-      <c r="J54" t="str">
+      <c r="J55" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K54" t="str">
+      <c r="K55" t="str">
         <v>no</v>
       </c>
-      <c r="L54">
+      <c r="L55">
         <v>49</v>
       </c>
-      <c r="M54" t="str">
+      <c r="M55" t="str">
         <v>LAVS23E</v>
       </c>
-      <c r="N54">
+      <c r="N55">
         <v>13500</v>
       </c>
-      <c r="O54" t="str">
+      <c r="O55" t="str">
         <v>activo</v>
       </c>
-      <c r="P54" t="str" xml:space="preserve">
+      <c r="P55" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que LAVS23E
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="55" xml:space="preserve">
-      <c r="A55" t="str">
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
         <v>LAVS23E</v>
       </c>
-      <c r="B55" t="str">
+      <c r="B56" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C55" t="str">
+      <c r="C56" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D55" t="str">
+      <c r="D56" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E55" t="str">
+      <c r="E56" t="str">
         <v>SS23E</v>
       </c>
-      <c r="F55" t="str">
+      <c r="F56" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G56" t="str">
         <v>LAVS23E-Lavadora Centrifuga SS23E 23 kg_Panel multifuncion electrico.doc</v>
       </c>
-      <c r="H55" t="str">
+      <c r="H56" t="str">
         <v>sí · 638×893 px · 300 ppp</v>
       </c>
-      <c r="I55">
+      <c r="I56">
         <v>178</v>
       </c>
-      <c r="J55" t="str">
+      <c r="J56" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K55" t="str">
+      <c r="K56" t="str">
         <v>no</v>
       </c>
-      <c r="L55">
+      <c r="L56">
         <v>50</v>
       </c>
-      <c r="M55" t="str">
+      <c r="M56" t="str">
         <v>LAVS23</v>
       </c>
-      <c r="N55">
+      <c r="N56">
         <v>14900</v>
       </c>
-      <c r="O55" t="str">
+      <c r="O56" t="str">
         <v>activo</v>
       </c>
-      <c r="P55" t="str" xml:space="preserve">
+      <c r="P56" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que LAVS23
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="56" xml:space="preserve">
-      <c r="A56" t="str">
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
         <v>LAVS40</v>
       </c>
-      <c r="B56" t="str">
+      <c r="B57" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS40, CALENTAMIENTO A VAPOR, PANEL FRONTAL Y CILINDRO INOXIDABLE, 300G, CAP.: 40KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C56" t="str">
+      <c r="C57" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D56" t="str">
+      <c r="D57" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E56" t="str">
+      <c r="E57" t="str">
         <v>SS40</v>
       </c>
-      <c r="F56" t="str">
+      <c r="F57" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G56" t="str">
+      <c r="G57" t="str">
         <v>LAVS40-Lavador Centrifuga SS40 40 kg_ Panel multifuncion vapor.DOC</v>
       </c>
-      <c r="H56" t="str">
+      <c r="H57" t="str">
         <v>sí · 448×555 px · 211 ppp</v>
       </c>
-      <c r="I56">
+      <c r="I57">
         <v>210</v>
       </c>
-      <c r="J56" t="str">
+      <c r="J57" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K56" t="str">
+      <c r="K57" t="str">
         <v>no</v>
       </c>
-      <c r="L56">
+      <c r="L57">
         <v>44</v>
       </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-      <c r="N56">
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57">
         <v>19500</v>
       </c>
-      <c r="O56" t="str">
+      <c r="O57" t="str">
         <v>activo</v>
       </c>
-      <c r="P56" t="str" xml:space="preserve">
+      <c r="P57" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57" t="str">
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
         <v>LAVT080</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B58" t="str">
         <v>LAVADORA IND. RIGIDA MOD:UCT080 CAP: 36 KG, FUERZA 100G OPL, CONTROL M9, CILINDRO INOX, PREPARADO A VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., (220V/60HZ/1-3PH), 15 AMP</v>
       </c>
-      <c r="C57" t="str">
+      <c r="C58" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D57" t="str">
+      <c r="D58" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E58" t="str">
         <v>UCT080</v>
       </c>
-      <c r="F57" t="str">
+      <c r="F58" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G57" t="str">
+      <c r="G58" t="str">
         <v>LAVT080-LAVADORA UCT080-M9-INOX-100G-220V.docx</v>
       </c>
-      <c r="H57" t="str">
+      <c r="H58" t="str">
         <v>sí · 636×892 px · 299 ppp</v>
       </c>
-      <c r="I57">
+      <c r="I58">
         <v>140</v>
       </c>
-      <c r="J57" t="str">
+      <c r="J58" t="str">
         <v>NO</v>
       </c>
-      <c r="K57" t="str">
+      <c r="K58" t="str">
         <v>sí · 287 ppp</v>
       </c>
-      <c r="L57">
+      <c r="L58">
         <v>41</v>
       </c>
-      <c r="M57" t="str">
+      <c r="M58" t="str">
         <v>LAVG080, LAVUC100</v>
       </c>
-      <c r="N57">
+      <c r="N58">
         <v>23900</v>
       </c>
-      <c r="O57" t="str">
+      <c r="O58" t="str">
         <v>activo</v>
       </c>
-      <c r="P57" t="str" xml:space="preserve">
+      <c r="P58" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVG080, LAVUC100
@@ -5230,379 +5299,327 @@
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str">
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
         <v>LAVTGIA13</v>
       </c>
-      <c r="B58" t="str">
+      <c r="B59" t="str">
         <v>LAVADORA SECADORA SEMI INDUSTRIAL TORRE A GAS GIANT C MAX 13 -10.2 KG 220/60HZ/1PH</v>
       </c>
-      <c r="C58" t="str">
+      <c r="C59" t="str">
         <v>LG</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D59" t="str">
         <v>LG</v>
       </c>
-      <c r="E58" t="str" xml:space="preserve">
+      <c r="E59" t="str" xml:space="preserve">
         <v xml:space="preserve">GIANT C MAX
 (CWG27MDCRS
 CDG27MUCPS)</v>
       </c>
-      <c r="F58" t="str">
+      <c r="F59" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G59" t="str">
         <v>LAVTGIA13-LavadoraSecadora giant c max 13-10.2 kg  OPL A GAS.docx</v>
       </c>
-      <c r="H58" t="str">
+      <c r="H59" t="str">
         <v>sí · 421×1132 px · 300 ppp</v>
       </c>
-      <c r="I58">
+      <c r="I59">
         <v>140</v>
       </c>
-      <c r="J58" t="str">
+      <c r="J59" t="str">
         <v>NO</v>
       </c>
-      <c r="K58" t="str">
+      <c r="K59" t="str">
         <v>no</v>
       </c>
-      <c r="L58">
+      <c r="L59">
         <v>48</v>
       </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58">
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59">
         <v>4450</v>
       </c>
-      <c r="O58" t="str">
+      <c r="O59" t="str">
         <v>activo</v>
       </c>
-      <c r="P58" t="str" xml:space="preserve">
+      <c r="P59" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 300)
 Trae 1 imagen(es) de más: en la cotización solo entran el logo, el equipo y una vista de complemento</v>
       </c>
     </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59" t="str">
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
         <v>LAVTMAX17</v>
       </c>
-      <c r="B59" t="str">
+      <c r="B60" t="str">
         <v>LAVADORA SECADORA SEMI INDUSTRIAL TORRE A GAS TITAN MAX MAX 17 -15 KG 220/60HZ/1PH</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C60" t="str">
         <v>LG</v>
       </c>
-      <c r="D59" t="str">
+      <c r="D60" t="str">
         <v>LG</v>
       </c>
-      <c r="E59" t="str" xml:space="preserve">
+      <c r="E60" t="str" xml:space="preserve">
         <v xml:space="preserve">TITAN MAX
 TITAN LIGHT</v>
       </c>
-      <c r="F59" t="str">
+      <c r="F60" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G59" t="str">
+      <c r="G60" t="str">
         <v>LAVTMAX17-LavadoraSecadora Titan  max 17-15 kg  OPL A GAS.docx</v>
       </c>
-      <c r="H59" t="str">
+      <c r="H60" t="str">
         <v>sí · 423×1136 px · 301 ppp</v>
       </c>
-      <c r="I59">
+      <c r="I60">
         <v>96</v>
       </c>
-      <c r="J59" t="str">
+      <c r="J60" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K59" t="str">
+      <c r="K60" t="str">
         <v>no</v>
       </c>
-      <c r="L59">
+      <c r="L60">
         <v>48</v>
       </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-      <c r="N59">
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60">
         <v>8590</v>
       </c>
-      <c r="O59" t="str">
+      <c r="O60" t="str">
         <v>activo</v>
       </c>
-      <c r="P59" t="str" xml:space="preserve">
+      <c r="P60" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (96 ppp al tamaño impreso; se amplió a 301)</v>
       </c>
     </row>
-    <row r="60" xml:space="preserve">
-      <c r="A60" t="str">
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str">
         <v>LAVUC100</v>
       </c>
-      <c r="B60" t="str">
+      <c r="B61" t="str">
         <v>LAV.IND,RIG,MOD.UC100,OPL,200G,M9,X,220V/60HZ/1-3PH,CAP.45KG,PAN.ACER.CILN.STAND.PREP.VAP.</v>
       </c>
-      <c r="C60" t="str">
+      <c r="C61" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D60" t="str">
+      <c r="D61" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E61" t="str">
         <v>UCT100</v>
       </c>
-      <c r="F60" t="str">
+      <c r="F61" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G60" t="str">
+      <c r="G61" t="str">
         <v>LAVUC100-LAVADORA UCT100-M9-INOX-200G-220V.docx</v>
       </c>
-      <c r="H60" t="str">
+      <c r="H61" t="str">
         <v>sí · 636×892 px · 299 ppp</v>
       </c>
-      <c r="I60">
+      <c r="I61">
         <v>140</v>
       </c>
-      <c r="J60" t="str">
+      <c r="J61" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K60" t="str">
+      <c r="K61" t="str">
         <v>sí · 223 ppp</v>
       </c>
-      <c r="L60">
+      <c r="L61">
         <v>41</v>
       </c>
-      <c r="M60" t="str">
+      <c r="M61" t="str">
         <v>LAVG080, LAVT080</v>
       </c>
-      <c r="N60">
+      <c r="N61">
         <v>29500</v>
       </c>
-      <c r="O60" t="str">
+      <c r="O61" t="str">
         <v>activo</v>
       </c>
-      <c r="P60" t="str" xml:space="preserve">
+      <c r="P61" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (140 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVG080, LAVT080
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61" t="str">
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
         <v>LAVUS030</v>
       </c>
-      <c r="B61" t="str">
+      <c r="B62" t="str">
         <v>LAVADORA - SECADORA INDUSTRIAL, MOD. UST030, UNILIC TOUCH, PANEL FRONTAL, LATERAL y CILINDRO INOXIDABLE, DOBLE ROTACION, GAS NATURAL, CAP.: 2*14 KG, X(220V/60HZ/3PH)</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C62" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D62" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E62" t="str">
         <v>UST030</v>
       </c>
-      <c r="F61" t="str">
+      <c r="F62" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G62" t="str">
         <v>LAVUS030-LAVADORA SECADORA APILABLE UST030-UNILINC TOUCH-INOX-GN-220V.docx</v>
       </c>
-      <c r="H61" t="str">
+      <c r="H62" t="str">
         <v>sí · 573×1130 px · 299 ppp</v>
       </c>
-      <c r="I61">
+      <c r="I62">
         <v>127</v>
       </c>
-      <c r="J61" t="str">
+      <c r="J62" t="str">
         <v>sí · 240 ppp</v>
       </c>
-      <c r="K61" t="str">
+      <c r="K62" t="str">
         <v>no</v>
       </c>
-      <c r="L61">
+      <c r="L62">
         <v>104</v>
       </c>
-      <c r="M61" t="str">
+      <c r="M62" t="str">
         <v>LAVUS050</v>
       </c>
-      <c r="N61">
+      <c r="N62">
         <v>16900</v>
       </c>
-      <c r="O61" t="str">
+      <c r="O62" t="str">
         <v>activo</v>
       </c>
-      <c r="P61" t="str" xml:space="preserve">
+      <c r="P62" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (127 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVUS050</v>
       </c>
     </row>
-    <row r="62" xml:space="preserve">
-      <c r="A62" t="str">
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str">
         <v>LAVUS050</v>
       </c>
-      <c r="B62" t="str">
+      <c r="B63" t="str">
         <v>LAVADORA - SECADORA INDUSTRIAL, MOD. UST050, UNILIC TOUCH, PANEL FRONTAL, LATERAL y CILINDRO INOXIDABLE, DOBLE ROTACION, GAS NATURAL, CAP.: 2*23 KG, X(220V/60HZ/3PH)</v>
       </c>
-      <c r="C62" t="str">
+      <c r="C63" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D62" t="str">
+      <c r="D63" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E62" t="str">
+      <c r="E63" t="str">
         <v>UST050</v>
       </c>
-      <c r="F62" t="str">
+      <c r="F63" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G63" t="str">
         <v>LAVUS050-LAVADORA SECADORA APILABLE UST050-UNILINC TOUCH-INOX-GN-220V.docx</v>
       </c>
-      <c r="H62" t="str">
+      <c r="H63" t="str">
         <v>sí · 573×1130 px · 299 ppp</v>
       </c>
-      <c r="I62">
+      <c r="I63">
         <v>127</v>
       </c>
-      <c r="J62" t="str">
+      <c r="J63" t="str">
         <v>sí · 240 ppp</v>
       </c>
-      <c r="K62" t="str">
+      <c r="K63" t="str">
         <v>no</v>
       </c>
-      <c r="L62">
+      <c r="L63">
         <v>103</v>
       </c>
-      <c r="M62" t="str">
+      <c r="M63" t="str">
         <v>LAVUS030</v>
       </c>
-      <c r="N62">
+      <c r="N63">
         <v>21500</v>
       </c>
-      <c r="O62" t="str">
+      <c r="O63" t="str">
         <v>activo</v>
       </c>
-      <c r="P62" t="str" xml:space="preserve">
+      <c r="P63" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (127 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVUS030</v>
       </c>
     </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63" t="str">
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
         <v>LAVUW045</v>
       </c>
-      <c r="B63" t="str">
+      <c r="B64" t="str">
         <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, X (220V/60HZ/1-3 PH)</v>
       </c>
-      <c r="C63" t="str">
+      <c r="C64" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D63" t="str">
+      <c r="D64" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E64" t="str">
         <v>UWT045</v>
       </c>
-      <c r="F63" t="str">
+      <c r="F64" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G63" t="str">
+      <c r="G64" t="str">
         <v>LAVUW045-LAVADORA UW045-UNILINC TOUCH-INOX-400G-OPTISPRAY-220V.docx</v>
       </c>
-      <c r="H63" t="str">
+      <c r="H64" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I63">
+      <c r="I64">
         <v>91</v>
       </c>
-      <c r="J63" t="str">
+      <c r="J64" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K63" t="str">
+      <c r="K64" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L63">
+      <c r="L64">
         <v>52</v>
       </c>
-      <c r="M63" t="str">
+      <c r="M64" t="str">
         <v>LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302</v>
       </c>
-      <c r="N63">
+      <c r="N64">
         <v>20500</v>
       </c>
-      <c r="O63" t="str">
+      <c r="O64" t="str">
         <v>activo</v>
       </c>
-      <c r="P63" t="str" xml:space="preserve">
+      <c r="P64" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64" t="str">
-        <v>LAVUY2802</v>
-      </c>
-      <c r="B64" t="str">
-        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY280, FUERZA 450G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO BOILER FED + PREPARADO PARA VAPOR, CAP.: 28KG, X(220V/60HZ/1PH)</v>
-      </c>
-      <c r="C64" t="str">
-        <v>PRIMUS</v>
-      </c>
-      <c r="D64" t="str">
-        <v>UNIMAC</v>
-      </c>
-      <c r="E64" t="str">
-        <v>UY240</v>
-      </c>
-      <c r="F64" t="str">
-        <v>Cargada con su ficha</v>
-      </c>
-      <c r="G64" t="str">
-        <v>LAVUY2802LAVADORA UY240 - UNILIC TOUCH-450G-INOX-220V.docx</v>
-      </c>
-      <c r="H64" t="str">
-        <v>sí · 637×883 px · 300 ppp</v>
-      </c>
-      <c r="I64">
-        <v>178</v>
-      </c>
-      <c r="J64" t="str">
-        <v>sí · 299 ppp</v>
-      </c>
-      <c r="K64" t="str">
-        <v>no</v>
-      </c>
-      <c r="L64">
-        <v>53</v>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64">
-        <v>23000</v>
-      </c>
-      <c r="O64" t="str">
-        <v>activo</v>
-      </c>
-      <c r="P64" t="str" xml:space="preserve">
-        <v xml:space="preserve">No trae vista de complemento (panel o botonera)
-La tabla de cabecera no dice: calentamiento
-El maestro dice marca PRIMUS y la ficha dice UNIMAC</v>
-      </c>
-    </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
-        <v>LAVUY4502</v>
+        <v>LAVUY2802</v>
       </c>
       <c r="B65" t="str">
-        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY450, FUERZA 360G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO DIRECTO CON VAPOR, CAP.: 45 KG, Q(220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY280, FUERZA 450G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO BOILER FED + PREPARADO PARA VAPOR, CAP.: 28KG, X(220V/60HZ/1PH)</v>
       </c>
       <c r="C65" t="str">
         <v>PRIMUS</v>
@@ -5611,34 +5628,34 @@
         <v>UNIMAC</v>
       </c>
       <c r="E65" t="str">
-        <v>UY450</v>
+        <v>UY240</v>
       </c>
       <c r="F65" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G65" t="str">
-        <v>LAVUY4502-LAVADORA UY450-UNILINC TOUCH-360G-INOX-220V.docx</v>
+        <v>LAVUY2802LAVADORA UY240 - UNILIC TOUCH-450G-INOX-220V.docx</v>
       </c>
       <c r="H65" t="str">
-        <v>sí · 505×639 px · 238 ppp</v>
+        <v>sí · 637×883 px · 300 ppp</v>
       </c>
       <c r="I65">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="J65" t="str">
-        <v>sí · 300 ppp</v>
+        <v>sí · 299 ppp</v>
       </c>
       <c r="K65" t="str">
         <v>no</v>
       </c>
       <c r="L65">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M65" t="str">
         <v/>
       </c>
       <c r="N65">
-        <v>31500</v>
+        <v>23000</v>
       </c>
       <c r="O65" t="str">
         <v>activo</v>
@@ -5651,677 +5668,729 @@
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
-        <v>LAVW045</v>
+        <v>LAVUY4502</v>
       </c>
       <c r="B66" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, P (380V/60HZ/3 PH)</v>
+        <v>LAVADORA INDUSTRIAL FLOT., MOD. UY450, FUERZA 360G, UNILINC TOUCH, PANEL FRONTAL Y LATERAL INOX., CILINDRO INOX., CALENTAMIENTO DIRECTO CON VAPOR, CAP.: 45 KG, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="C66" t="str">
-        <v>UNIMAC</v>
+        <v>PRIMUS</v>
       </c>
       <c r="D66" t="str">
         <v>UNIMAC</v>
       </c>
       <c r="E66" t="str">
-        <v>UWT045</v>
+        <v>UY450</v>
       </c>
       <c r="F66" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G66" t="str">
-        <v>LAVW045-LAVADORA UW045-UNILINC TOUCH-INOX-400G-OPTISPRAY-380V.docx</v>
+        <v>LAVUY4502-LAVADORA UY450-UNILINC TOUCH-360G-INOX-220V.docx</v>
       </c>
       <c r="H66" t="str">
-        <v>sí · 612×1041 px · 288 ppp</v>
+        <v>sí · 505×639 px · 238 ppp</v>
       </c>
       <c r="I66">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="J66" t="str">
-        <v>sí · 260 ppp</v>
+        <v>sí · 300 ppp</v>
       </c>
       <c r="K66" t="str">
-        <v>sí · 250 ppp</v>
+        <v>no</v>
       </c>
       <c r="L66">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M66" t="str">
-        <v>LAVUW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302</v>
+        <v/>
       </c>
       <c r="N66">
-        <v>21500</v>
+        <v>31500</v>
       </c>
       <c r="O66" t="str">
         <v>activo</v>
       </c>
       <c r="P66" t="str" xml:space="preserve">
+        <v xml:space="preserve">No trae vista de complemento (panel o botonera)
+La tabla de cabecera no dice: calentamiento
+El maestro dice marca PRIMUS y la ficha dice UNIMAC</v>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>LAVW045</v>
+      </c>
+      <c r="B67" t="str">
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, P (380V/60HZ/3 PH)</v>
+      </c>
+      <c r="C67" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="D67" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="E67" t="str">
+        <v>UWT045</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Cargada con su ficha</v>
+      </c>
+      <c r="G67" t="str">
+        <v>LAVW045-LAVADORA UW045-UNILINC TOUCH-INOX-400G-OPTISPRAY-380V.docx</v>
+      </c>
+      <c r="H67" t="str">
+        <v>sí · 612×1041 px · 288 ppp</v>
+      </c>
+      <c r="I67">
+        <v>91</v>
+      </c>
+      <c r="J67" t="str">
+        <v>sí · 260 ppp</v>
+      </c>
+      <c r="K67" t="str">
+        <v>sí · 250 ppp</v>
+      </c>
+      <c r="L67">
+        <v>52</v>
+      </c>
+      <c r="M67" t="str">
+        <v>LAVUW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302</v>
+      </c>
+      <c r="N67">
+        <v>21500</v>
+      </c>
+      <c r="O67" t="str">
+        <v>activo</v>
+      </c>
+      <c r="P67" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67" t="str">
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
         <v>LAVW065</v>
       </c>
-      <c r="B67" t="str">
+      <c r="B68" t="str">
         <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UWT065, FUERZA: 400 G, CONTROL UNILINC TOUCH, CAP. 29.5 KG, SIS. OPL, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., C/ DOSIFICADOR MANUAL, C/ OTISPRAY, (220V/60HZ/1-3PH)</v>
       </c>
-      <c r="C67" t="str">
+      <c r="C68" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D67" t="str">
+      <c r="D68" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E67" t="str">
+      <c r="E68" t="str">
         <v>UWT065</v>
       </c>
-      <c r="F67" t="str">
+      <c r="F68" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G67" t="str">
+      <c r="G68" t="str">
         <v>LAVW065-LAVADORA UW065-UNILINC TOUCH-INOX-400G-OPTISPRAY-220V.docx</v>
       </c>
-      <c r="H67" t="str">
+      <c r="H68" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I67">
+      <c r="I68">
         <v>91</v>
       </c>
-      <c r="J67" t="str">
+      <c r="J68" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K67" t="str">
+      <c r="K68" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L67">
+      <c r="L68">
         <v>52</v>
       </c>
-      <c r="M67" t="str">
+      <c r="M68" t="str">
         <v>LAVUW045, LAVW045, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302</v>
       </c>
-      <c r="N67">
+      <c r="N68">
         <v>22900</v>
       </c>
-      <c r="O67" t="str">
+      <c r="O68" t="str">
         <v>activo</v>
       </c>
-      <c r="P67" t="str" xml:space="preserve">
+      <c r="P68" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68" t="str">
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
         <v>LAVW085</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B69" t="str">
         <v>LAVADORA INDUSTRIAL RIGIDA MOD: UW085N, 200G, CONTROL: M30, CAP:38.5 KG, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL, CILINDRO INOX, S / DOSIFICADOR MANUAL, SIN OTISPRAY, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C68" t="str">
+      <c r="C69" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D68" t="str">
+      <c r="D69" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E69" t="str">
         <v>UW085</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F69" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G69" t="str">
         <v>LAVW085-LAVADORA UW085-M30-INOX-200G-220V.docx</v>
       </c>
-      <c r="H68" t="str">
+      <c r="H69" t="str">
         <v>sí · 582×939 px · 274 ppp</v>
       </c>
-      <c r="I68">
+      <c r="I69">
         <v>82</v>
       </c>
-      <c r="J68" t="str">
+      <c r="J69" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K68" t="str">
+      <c r="K69" t="str">
         <v>sí · 237 ppp</v>
       </c>
-      <c r="L68">
+      <c r="L69">
         <v>41</v>
       </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68">
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69">
         <v>27500</v>
       </c>
-      <c r="O68" t="str">
+      <c r="O69" t="str">
         <v>activo</v>
       </c>
-      <c r="P68" t="str" xml:space="preserve">
+      <c r="P69" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (82 ppp al tamaño impreso; se amplió a 274)
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69" t="str">
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
         <v>LAVW0851</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B70" t="str">
         <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (380V/60HZ/3PH)</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C70" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D69" t="str">
+      <c r="D70" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E69" t="str">
+      <c r="E70" t="str">
         <v>UWT085</v>
       </c>
-      <c r="F69" t="str">
+      <c r="F70" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G69" t="str">
+      <c r="G70" t="str">
         <v>LAVW0851-LAVADORA UW085-UNILINC TOUCH-INOX-300G-OPTISPRAY-380V.docx</v>
       </c>
-      <c r="H69" t="str">
+      <c r="H70" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I69">
+      <c r="I70">
         <v>91</v>
       </c>
-      <c r="J69" t="str">
+      <c r="J70" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K69" t="str">
+      <c r="K70" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L69">
+      <c r="L70">
         <v>52</v>
       </c>
-      <c r="M69" t="str">
+      <c r="M70" t="str">
         <v>LAVUW045, LAVW045, LAVW065, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302</v>
       </c>
-      <c r="N69">
+      <c r="N70">
         <v>28900</v>
       </c>
-      <c r="O69" t="str">
+      <c r="O70" t="str">
         <v>activo</v>
       </c>
-      <c r="P69" t="str" xml:space="preserve">
+      <c r="P70" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW065, LAVW0852, LAVW105, LAVW1051, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="70" xml:space="preserve">
-      <c r="A70" t="str">
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
         <v>LAVW0852</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B71" t="str">
         <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C71" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D71" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E71" t="str">
         <v>UWT085</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F71" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G71" t="str">
         <v>LAVW0852-LAVADORA UW085-UNILINC TOUCH-INOX-300G-OPTISPRAY-220V.docx</v>
       </c>
-      <c r="H70" t="str">
+      <c r="H71" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I70">
+      <c r="I71">
         <v>91</v>
       </c>
-      <c r="J70" t="str">
+      <c r="J71" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K70" t="str">
+      <c r="K71" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L70">
+      <c r="L71">
         <v>52</v>
       </c>
-      <c r="M70" t="str">
+      <c r="M71" t="str">
         <v>LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW105, LAVW1051, LAVW1301, LAVW1302</v>
       </c>
-      <c r="N70">
+      <c r="N71">
         <v>28150</v>
       </c>
-      <c r="O70" t="str">
+      <c r="O71" t="str">
         <v>activo</v>
       </c>
-      <c r="P70" t="str" xml:space="preserve">
+      <c r="P71" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW105, LAVW1051, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71" t="str">
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str">
         <v>LAVW105</v>
       </c>
-      <c r="B71" t="str">
+      <c r="B72" t="str">
         <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(220V/60HZ/3PH)</v>
       </c>
-      <c r="C71" t="str">
+      <c r="C72" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D72" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E72" t="str">
         <v>UWT105</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F72" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G72" t="str">
         <v>LAVW105-LAVADORA UW105-UNILINC TOUCH-INOX-300G-OPTISPRAY-220V.docx</v>
       </c>
-      <c r="H71" t="str">
+      <c r="H72" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I71">
+      <c r="I72">
         <v>91</v>
       </c>
-      <c r="J71" t="str">
+      <c r="J72" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K71" t="str">
+      <c r="K72" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L71">
+      <c r="L72">
         <v>53</v>
       </c>
-      <c r="M71" t="str">
+      <c r="M72" t="str">
         <v>LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW1051, LAVW1301, LAVW1302</v>
       </c>
-      <c r="N71">
+      <c r="N72">
         <v>31950</v>
       </c>
-      <c r="O71" t="str">
+      <c r="O72" t="str">
         <v>activo</v>
       </c>
-      <c r="P71" t="str" xml:space="preserve">
+      <c r="P72" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW1051, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="72" xml:space="preserve">
-      <c r="A72" t="str">
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
         <v>LAVW1051</v>
       </c>
-      <c r="B72" t="str">
+      <c r="B73" t="str">
         <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD:UWT105, FUERZA 300G, CAP: 47.6KG, OPL, CONTROL: UNILINC TOUCH, PANEL LATERAL, FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
       </c>
-      <c r="C72" t="str">
+      <c r="C73" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D72" t="str">
+      <c r="D73" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E72" t="str">
+      <c r="E73" t="str">
         <v>UWT105</v>
       </c>
-      <c r="F72" t="str">
+      <c r="F73" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G73" t="str">
         <v>LAVW1051-LAVADORA UW105-UNILINC TOUCH-INOX-300G-OPTISPRAY-380V.docx</v>
       </c>
-      <c r="H72" t="str">
+      <c r="H73" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I72">
+      <c r="I73">
         <v>91</v>
       </c>
-      <c r="J72" t="str">
+      <c r="J73" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K72" t="str">
+      <c r="K73" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L72">
+      <c r="L73">
         <v>53</v>
       </c>
-      <c r="M72" t="str">
+      <c r="M73" t="str">
         <v>LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1301, LAVW1302</v>
       </c>
-      <c r="N72">
+      <c r="N73">
         <v>31500</v>
       </c>
-      <c r="O72" t="str">
+      <c r="O73" t="str">
         <v>activo</v>
       </c>
-      <c r="P72" t="str" xml:space="preserve">
+      <c r="P73" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1301, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73" t="str">
+    <row r="74" xml:space="preserve">
+      <c r="A74" t="str">
         <v>LAVW1301</v>
       </c>
-      <c r="B73" t="str">
+      <c r="B74" t="str">
         <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
       </c>
-      <c r="C73" t="str">
+      <c r="C74" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D73" t="str">
+      <c r="D74" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E73" t="str">
+      <c r="E74" t="str">
         <v>UW130</v>
       </c>
-      <c r="F73" t="str">
+      <c r="F74" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G74" t="str">
         <v>LAVW1301-LAVADORA UW130-UNILINC TOUCH-INOX-300G-OPTISPRAY-380V.docx</v>
       </c>
-      <c r="H73" t="str">
+      <c r="H74" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I73">
+      <c r="I74">
         <v>91</v>
       </c>
-      <c r="J73" t="str">
+      <c r="J74" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K73" t="str">
+      <c r="K74" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L73">
+      <c r="L74">
         <v>52</v>
       </c>
-      <c r="M73" t="str">
+      <c r="M74" t="str">
         <v>LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1302</v>
       </c>
-      <c r="N73">
+      <c r="N74">
         <v>38500</v>
       </c>
-      <c r="O73" t="str">
+      <c r="O74" t="str">
         <v>activo</v>
       </c>
-      <c r="P73" t="str" xml:space="preserve">
+      <c r="P74" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1302
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="74" xml:space="preserve">
-      <c r="A74" t="str">
+    <row r="75" xml:space="preserve">
+      <c r="A75" t="str">
         <v>LAVW1302</v>
       </c>
-      <c r="B74" t="str">
+      <c r="B75" t="str">
         <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL: UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, Q(220V/60HZ/3PH)</v>
       </c>
-      <c r="C74" t="str">
+      <c r="C75" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D75" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E75" t="str">
         <v>UW130</v>
       </c>
-      <c r="F74" t="str">
+      <c r="F75" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G74" t="str">
+      <c r="G75" t="str">
         <v>LAVW1302-LAVADORA UW130-UNILINC TOUCH-INOX-300G-OPTISPRAY-220V.docx</v>
       </c>
-      <c r="H74" t="str">
+      <c r="H75" t="str">
         <v>sí · 612×1041 px · 288 ppp</v>
       </c>
-      <c r="I74">
+      <c r="I75">
         <v>91</v>
       </c>
-      <c r="J74" t="str">
+      <c r="J75" t="str">
         <v>sí · 260 ppp</v>
       </c>
-      <c r="K74" t="str">
+      <c r="K75" t="str">
         <v>sí · 250 ppp</v>
       </c>
-      <c r="L74">
+      <c r="L75">
         <v>52</v>
       </c>
-      <c r="M74" t="str">
+      <c r="M75" t="str">
         <v>LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301</v>
       </c>
-      <c r="N74">
+      <c r="N75">
         <v>37500</v>
       </c>
-      <c r="O74" t="str">
+      <c r="O75" t="str">
         <v>activo</v>
       </c>
-      <c r="P74" t="str" xml:space="preserve">
+      <c r="P75" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (91 ppp al tamaño impreso; se amplió a 288)
 Usa la misma foto de equipo que LAVUW045, LAVW045, LAVW065, LAVW0851, LAVW0852, LAVW105, LAVW1051, LAVW1301
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="75" xml:space="preserve">
-      <c r="A75" t="str">
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str">
         <v>LAVW17</v>
       </c>
-      <c r="B75" t="str">
+      <c r="B76" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: WET 17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, CONTROL: TOUCH, CON SEÑALES DE ALIMENTACIÓN, 300G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C75" t="str">
+      <c r="C76" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D75" t="str">
+      <c r="D76" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E75" t="str">
+      <c r="E76" t="str">
         <v>WET SS17</v>
       </c>
-      <c r="F75" t="str">
+      <c r="F76" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G76" t="str">
         <v>LAVW17-Lavador Centrifuga SS17 WET 17 kg_ Panel Tocuh vapor.DOC</v>
       </c>
-      <c r="H75" t="str">
+      <c r="H76" t="str">
         <v>sí · 636×750 px · 299 ppp</v>
       </c>
-      <c r="I75">
+      <c r="I76">
         <v>105</v>
       </c>
-      <c r="J75" t="str">
+      <c r="J76" t="str">
         <v>NO</v>
       </c>
-      <c r="K75" t="str">
+      <c r="K76" t="str">
         <v>no</v>
       </c>
-      <c r="L75">
+      <c r="L76">
         <v>57</v>
       </c>
-      <c r="M75" t="str">
+      <c r="M76" t="str">
         <v>LAVW23</v>
       </c>
-      <c r="N75">
+      <c r="N76">
         <v>12900</v>
       </c>
-      <c r="O75" t="str">
+      <c r="O76" t="str">
         <v>activo</v>
       </c>
-      <c r="P75" t="str" xml:space="preserve">
+      <c r="P76" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (105 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVW23</v>
       </c>
     </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76" t="str">
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
         <v>LAVW23</v>
       </c>
-      <c r="B76" t="str">
+      <c r="B77" t="str">
         <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: WET 23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, CONTROL: TOUCH, CON SEÑALES DE ALIMENTACIÓN, 300G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
-      <c r="C76" t="str">
+      <c r="C77" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D76" t="str">
+      <c r="D77" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E76" t="str">
+      <c r="E77" t="str">
         <v>WET SS23</v>
       </c>
-      <c r="F76" t="str">
+      <c r="F77" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G76" t="str">
+      <c r="G77" t="str">
         <v>LAVW23-Lavador Centrifuga SS23 WET 23 kg_ Panel Tocuh vapor.DOC</v>
       </c>
-      <c r="H76" t="str">
+      <c r="H77" t="str">
         <v>sí · 636×750 px · 299 ppp</v>
       </c>
-      <c r="I76">
+      <c r="I77">
         <v>105</v>
       </c>
-      <c r="J76" t="str">
+      <c r="J77" t="str">
         <v>NO</v>
       </c>
-      <c r="K76" t="str">
+      <c r="K77" t="str">
         <v>no</v>
       </c>
-      <c r="L76">
+      <c r="L77">
         <v>57</v>
       </c>
-      <c r="M76" t="str">
+      <c r="M77" t="str">
         <v>LAVW17</v>
       </c>
-      <c r="N76">
+      <c r="N77">
         <v>14900</v>
       </c>
-      <c r="O76" t="str">
+      <c r="O77" t="str">
         <v>activo</v>
       </c>
-      <c r="P76" t="str" xml:space="preserve">
+      <c r="P77" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (105 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que LAVW17</v>
       </c>
     </row>
-    <row r="77" xml:space="preserve">
-      <c r="A77" t="str">
+    <row r="78" xml:space="preserve">
+      <c r="A78" t="str">
         <v>MEFENI1</v>
       </c>
-      <c r="B77" t="str">
+      <c r="B78" t="str">
         <v>MESA DE PLANCHADO ASPIRANTE CON TERMOSTATO, SIDI MONDIAL MOD FENIX, 220/1/60HZ S:</v>
       </c>
-      <c r="C77" t="str">
+      <c r="C78" t="str">
         <v>SIMI MONDIAL</v>
       </c>
-      <c r="D77" t="str">
+      <c r="D78" t="str">
         <v>SIDI MONDIAL (Italia)</v>
       </c>
-      <c r="E77" t="str">
+      <c r="E78" t="str">
         <v>FENIX</v>
       </c>
-      <c r="F77" t="str">
+      <c r="F78" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G77" t="str">
+      <c r="G78" t="str">
         <v>MEFENI1-Mesa de planchado Mod Fenix.doc</v>
       </c>
-      <c r="H77" t="str">
+      <c r="H78" t="str">
         <v>sí · 1808×1287 px · 850 ppp</v>
       </c>
-      <c r="I77">
+      <c r="I78">
         <v>1116</v>
       </c>
-      <c r="J77" t="str">
+      <c r="J78" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K77" t="str">
+      <c r="K78" t="str">
         <v>no</v>
       </c>
-      <c r="L77">
+      <c r="L78">
         <v>10</v>
       </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
-      <c r="N77">
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78">
         <v>1400</v>
       </c>
-      <c r="O77" t="str">
+      <c r="O78" t="str">
         <v>activo</v>
       </c>
-      <c r="P77" t="str" xml:space="preserve">
+      <c r="P78" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Descripción muy corta (10 líneas; la media de las fichas es 50)
 La tabla de cabecera no dice: capacidad, panel
 El maestro dice marca SIMI MONDIAL y la ficha dice SIDI MONDIAL (Italia)</v>
       </c>
     </row>
-    <row r="78" xml:space="preserve">
-      <c r="A78" t="str">
+    <row r="79" xml:space="preserve">
+      <c r="A79" t="str">
         <v>MEVA2</v>
       </c>
-      <c r="B78" t="str">
+      <c r="B79" t="str">
         <v>MESA VAPORIZADORA SIN CALDERO EFALMV2000</v>
       </c>
-      <c r="C78" t="str">
+      <c r="C79" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="D78" t="str">
+      <c r="D79" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="E78" t="str">
+      <c r="E79" t="str">
         <v>EFALMV2000</v>
       </c>
-      <c r="F78" t="str">
+      <c r="F79" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G79" t="str">
         <v>MEVA2-Mesa Vaporizadora Efamein EFALMV2000.doc</v>
       </c>
-      <c r="H78" t="str">
+      <c r="H79" t="str">
         <v>sí · 636×419 px · 299 ppp</v>
       </c>
-      <c r="I78">
+      <c r="I79">
         <v>127</v>
       </c>
-      <c r="J78" t="str">
+      <c r="J79" t="str">
         <v>NO</v>
       </c>
-      <c r="K78" t="str">
+      <c r="K79" t="str">
         <v>no</v>
       </c>
-      <c r="L78">
+      <c r="L79">
         <v>6</v>
       </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78">
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79">
         <v>8500</v>
       </c>
-      <c r="O78" t="str">
+      <c r="O79" t="str">
         <v>activo</v>
       </c>
-      <c r="P78" t="str" xml:space="preserve">
+      <c r="P79" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (127 ppp al tamaño impreso; se amplió a 299)
@@ -6329,53 +6398,53 @@
 La tabla de cabecera no dice: capacidad, calentamiento, panel</v>
       </c>
     </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79" t="str">
+    <row r="80" xml:space="preserve">
+      <c r="A80" t="str">
         <v>PRE702U</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B80" t="str">
         <v>PRENSA MANUAL SIDI MONDIAL MOD: ST-702/U, VAPOR EXTERNO PARA PLATO, ASPIRANTE INCORP. 220V/60HZ/ 1PH S: 284236</v>
       </c>
-      <c r="C79" t="str">
+      <c r="C80" t="str">
         <v>SIMI MONDIAL</v>
       </c>
-      <c r="D79" t="str">
+      <c r="D80" t="str">
         <v>SIDI MONDIAL (Italia)</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E80" t="str">
         <v>ST-702/U</v>
       </c>
-      <c r="F79" t="str">
+      <c r="F80" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G80" t="str">
         <v>PRE702U-PRENSA DE PLANCHADO-ST-702.U 220V.doc</v>
       </c>
-      <c r="H79" t="str">
+      <c r="H80" t="str">
         <v>sí · 639×801 px · 301 ppp</v>
       </c>
-      <c r="I79">
+      <c r="I80">
         <v>133</v>
       </c>
-      <c r="J79" t="str">
+      <c r="J80" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K79" t="str">
+      <c r="K80" t="str">
         <v>no</v>
       </c>
-      <c r="L79">
+      <c r="L80">
         <v>15</v>
       </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79">
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80">
         <v>12999</v>
       </c>
-      <c r="O79" t="str">
+      <c r="O80" t="str">
         <v>activo</v>
       </c>
-      <c r="P79" t="str" xml:space="preserve">
+      <c r="P80" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (133 ppp al tamaño impreso; se amplió a 301)
 Descripción muy corta (15 líneas; la media de las fichas es 50)
@@ -6383,106 +6452,106 @@
 El maestro dice marca SIMI MONDIAL y la ficha dice SIDI MONDIAL (Italia)</v>
       </c>
     </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80" t="str">
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str">
         <v>PRN750U</v>
       </c>
-      <c r="B80" t="str">
+      <c r="B81" t="str">
         <v>PRENSA NEUMATICA ASPIR. 2 PULSAD. SIDI MONDIAL MOD: CT-750/U, VAPOR EXTERNO PARA PLATO 220V/60HZ/1PH S: 284237</v>
       </c>
-      <c r="C80" t="str">
+      <c r="C81" t="str">
         <v>SIMI MONDIAL</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D81" t="str">
         <v>SIDI MONDIAL (Italia)</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E81" t="str">
         <v>CT-750/U</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F81" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G81" t="str">
         <v>PRN750U-PRENSA DE PLANCHADO-CT-750.U 220V.doc</v>
       </c>
-      <c r="H80" t="str">
+      <c r="H81" t="str">
         <v>sí · 637×712 px · 300 ppp</v>
       </c>
-      <c r="I80">
+      <c r="I81">
         <v>152</v>
       </c>
-      <c r="J80" t="str">
+      <c r="J81" t="str">
         <v>sí · 299 ppp</v>
       </c>
-      <c r="K80" t="str">
+      <c r="K81" t="str">
         <v>no</v>
       </c>
-      <c r="L80">
+      <c r="L81">
         <v>19</v>
       </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
-      <c r="N80">
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81">
         <v>14999</v>
       </c>
-      <c r="O80" t="str">
+      <c r="O81" t="str">
         <v>activo</v>
       </c>
-      <c r="P80" t="str" xml:space="preserve">
+      <c r="P81" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Descripción muy corta (19 líneas; la media de las fichas es 50)
 La tabla de cabecera no dice: capacidad, panel
 El maestro dice marca SIMI MONDIAL y la ficha dice SIDI MONDIAL (Italia)</v>
       </c>
     </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81" t="str">
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str">
         <v>PRPE01</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B82" t="str">
         <v>PRENSA DE PLANCHADO ELECTRICA (MESA) CON CALENTAMIENTO A VAPOR MOD.PCV 220V/60HZ/1PH</v>
       </c>
-      <c r="C81" t="str">
+      <c r="C82" t="str">
         <v>BLANCA PRESS</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D82" t="str">
         <v>BLANCA PRESS</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E82" t="str">
         <v>PCV</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F82" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G82" t="str">
         <v>PRPE01-Prensa de planchado electrico Mod. PCV.doc</v>
       </c>
-      <c r="H81" t="str">
+      <c r="H82" t="str">
         <v>sí · 639×523 px · 301 ppp</v>
       </c>
-      <c r="I81">
+      <c r="I82">
         <v>106</v>
       </c>
-      <c r="J81" t="str">
+      <c r="J82" t="str">
         <v>NO</v>
       </c>
-      <c r="K81" t="str">
+      <c r="K82" t="str">
         <v>no</v>
       </c>
-      <c r="L81">
+      <c r="L82">
         <v>4</v>
       </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
-      <c r="N81">
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82">
         <v>2200</v>
       </c>
-      <c r="O81" t="str">
+      <c r="O82" t="str">
         <v>activo</v>
       </c>
-      <c r="P81" t="str" xml:space="preserve">
+      <c r="P82" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (106 ppp al tamaño impreso; se amplió a 301)
@@ -6490,627 +6559,627 @@
 La tabla de cabecera no dice: capacidad, panel</v>
       </c>
     </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82" t="str">
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str">
         <v>SECA120</v>
       </c>
-      <c r="B82" t="str">
+      <c r="B83" t="str">
         <v>SECADORA INDUSTRIAL, MOD.: ADG-120I, CAP.: 54KG, DOBLE ROTACION, PANEL FRONTAL Y CILINDRO INOX., GAS GLP, (220/60HZ/3PH)</v>
       </c>
-      <c r="C82" t="str">
+      <c r="C83" t="str">
         <v>ADC</v>
       </c>
-      <c r="D82" t="str">
+      <c r="D83" t="str">
         <v>ADC</v>
       </c>
-      <c r="E82" t="str">
+      <c r="E83" t="str">
         <v>ADG-120i</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F83" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G83" t="str">
         <v>SECA120-Secadora ADG-120i 54 kg_A gas Trifasico.docx</v>
       </c>
-      <c r="H82" t="str">
+      <c r="H83" t="str">
         <v>sí · 594×1133 px · 300 ppp</v>
       </c>
-      <c r="I82">
+      <c r="I83">
         <v>130</v>
       </c>
-      <c r="J82" t="str">
+      <c r="J83" t="str">
         <v>NO</v>
       </c>
-      <c r="K82" t="str">
+      <c r="K83" t="str">
         <v>no</v>
       </c>
-      <c r="L82">
+      <c r="L83">
         <v>50</v>
       </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
-      <c r="N82">
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83">
         <v>21500</v>
       </c>
-      <c r="O82" t="str">
+      <c r="O83" t="str">
         <v>activo</v>
       </c>
-      <c r="P82" t="str" xml:space="preserve">
+      <c r="P83" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (130 ppp al tamaño impreso; se amplió a 300)</v>
       </c>
     </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83" t="str">
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str">
         <v>SECA758</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B84" t="str">
         <v>SECADORA INDUSTRIAL, MOD.: ADG-758V, SISTEMA OPL, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, GAS GLP, CAP.: 34 KG, (220V/60HZ/1PH)</v>
       </c>
-      <c r="C83" t="str">
+      <c r="C84" t="str">
         <v>ADC</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D84" t="str">
         <v>ADC</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E84" t="str">
         <v>ADG-758V</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F84" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G84" t="str">
         <v>SECA758-Secadora ADG-758V 34 kg_A gas.docx</v>
       </c>
-      <c r="H83" t="str">
+      <c r="H84" t="str">
         <v>sí · 614×1133 px · 300 ppp</v>
       </c>
-      <c r="I83">
+      <c r="I84">
         <v>123</v>
       </c>
-      <c r="J83" t="str">
+      <c r="J84" t="str">
         <v>NO</v>
       </c>
-      <c r="K83" t="str">
+      <c r="K84" t="str">
         <v>no</v>
       </c>
-      <c r="L83">
+      <c r="L84">
         <v>43</v>
       </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
-      <c r="N83">
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84">
         <v>8999</v>
       </c>
-      <c r="O83" t="str">
+      <c r="O84" t="str">
         <v>activo</v>
       </c>
-      <c r="P83" t="str" xml:space="preserve">
+      <c r="P84" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (123 ppp al tamaño impreso; se amplió a 300)</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="str">
+    <row r="85">
+      <c r="A85" t="str">
         <v>SECD24</v>
       </c>
-      <c r="B84" t="str">
+      <c r="B85" t="str">
         <v>SECADORA INDUSTRIAL, MOD. DX24, CONTROL: MICROPROCESSOR , DOBLE ROTACION, CILINDRO GALVANIZADO, PANEL FRONTAL y LATERAL ACERO GRIS, CAP. 24KG, A GAS NATURAL, X(220V/60HZ/1-3PH)</v>
       </c>
-      <c r="C84" t="str">
+      <c r="C85" t="str">
         <v>PRIMUS</v>
       </c>
-      <c r="D84" t="str">
+      <c r="D85" t="str">
         <v>PRIMUS</v>
       </c>
-      <c r="E84" t="str">
+      <c r="E85" t="str">
         <v>DX 24</v>
-      </c>
-      <c r="F84" t="str">
-        <v>Cargada con su ficha</v>
-      </c>
-      <c r="G84" t="str">
-        <v>SECD24. SECADORA DX 24 OPL MICROPROCESOR - C. GALVANIZADO - CAP. 24 KG - GAS NATURAL - 220V.60HZ.1-3.PH.docx</v>
-      </c>
-      <c r="H84" t="str">
-        <v>sí · 638×1020 px · 300 ppp</v>
-      </c>
-      <c r="I84">
-        <v>177</v>
-      </c>
-      <c r="J84" t="str">
-        <v>sí · 300 ppp</v>
-      </c>
-      <c r="K84" t="str">
-        <v>no</v>
-      </c>
-      <c r="L84">
-        <v>53</v>
-      </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
-      <c r="N84">
-        <v>7500</v>
-      </c>
-      <c r="O84" t="str">
-        <v>activo</v>
-      </c>
-      <c r="P84" t="str">
-        <v>No trae vista de complemento (panel o botonera)</v>
-      </c>
-    </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85" t="str">
-        <v>SECEF60</v>
-      </c>
-      <c r="B85" t="str">
-        <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS60 ,CAP. 60 KG, 5HP, 220V/60HZ/TRIFASICO</v>
-      </c>
-      <c r="C85" t="str">
-        <v>EFAMEIN</v>
-      </c>
-      <c r="D85" t="str">
-        <v>EFAMEIN</v>
-      </c>
-      <c r="E85" t="str">
-        <v>EFAS 60</v>
       </c>
       <c r="F85" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G85" t="str">
-        <v>SECEF60-Secadora  Industrial a vapor Efamein Modelo Efas60 220v trifasico.doc</v>
+        <v>SECD24. SECADORA DX 24 OPL MICROPROCESOR - C. GALVANIZADO - CAP. 24 KG - GAS NATURAL - 220V.60HZ.1-3.PH.docx</v>
       </c>
       <c r="H85" t="str">
-        <v>sí · 570×909 px · 268 ppp</v>
+        <v>sí · 638×1020 px · 300 ppp</v>
       </c>
       <c r="I85">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="J85" t="str">
-        <v>NO</v>
+        <v>sí · 300 ppp</v>
       </c>
       <c r="K85" t="str">
         <v>no</v>
       </c>
       <c r="L85">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M85" t="str">
         <v/>
       </c>
       <c r="N85">
-        <v>16999</v>
+        <v>7500</v>
       </c>
       <c r="O85" t="str">
         <v>activo</v>
       </c>
-      <c r="P85" t="str" xml:space="preserve">
+      <c r="P85" t="str">
+        <v>No trae vista de complemento (panel o botonera)</v>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
+        <v>SECEF60</v>
+      </c>
+      <c r="B86" t="str">
+        <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS60 ,CAP. 60 KG, 5HP, 220V/60HZ/TRIFASICO</v>
+      </c>
+      <c r="C86" t="str">
+        <v>EFAMEIN</v>
+      </c>
+      <c r="D86" t="str">
+        <v>EFAMEIN</v>
+      </c>
+      <c r="E86" t="str">
+        <v>EFAS 60</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Cargada con su ficha</v>
+      </c>
+      <c r="G86" t="str">
+        <v>SECEF60-Secadora  Industrial a vapor Efamein Modelo Efas60 220v trifasico.doc</v>
+      </c>
+      <c r="H86" t="str">
+        <v>sí · 570×909 px · 268 ppp</v>
+      </c>
+      <c r="I86">
+        <v>83</v>
+      </c>
+      <c r="J86" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K86" t="str">
+        <v>no</v>
+      </c>
+      <c r="L86">
+        <v>50</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86">
+        <v>16999</v>
+      </c>
+      <c r="O86" t="str">
+        <v>activo</v>
+      </c>
+      <c r="P86" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (83 ppp al tamaño impreso; se amplió a 268)
 La tabla de cabecera no dice: panel</v>
       </c>
     </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86" t="str">
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str">
         <v>SECEFG125</v>
       </c>
-      <c r="B86" t="str">
+      <c r="B87" t="str">
         <v>SECADORA INDUSTRIAL A GAS EFAMEIN MODELO EFAS125, CAP. 125 KG, 10 HP, 220V/60HZ/TRIFASICO</v>
       </c>
-      <c r="C86" t="str">
+      <c r="C87" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="D86" t="str">
+      <c r="D87" t="str">
         <v>Efamein</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E87" t="str">
         <v>EFAS125</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F87" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G87" t="str">
         <v>SECEFG125-Secadora  Industrial a gas Efamein Modelo Efas125 220v trifasico.doc</v>
       </c>
-      <c r="H86" t="str">
+      <c r="H87" t="str">
         <v>sí · 510×750 px · 240 ppp</v>
       </c>
-      <c r="I86">
+      <c r="I87">
         <v>95</v>
       </c>
-      <c r="J86" t="str">
+      <c r="J87" t="str">
         <v>NO</v>
       </c>
-      <c r="K86" t="str">
+      <c r="K87" t="str">
         <v>no</v>
       </c>
-      <c r="L86">
+      <c r="L87">
         <v>48</v>
       </c>
-      <c r="M86" t="str">
+      <c r="M87" t="str">
         <v>SECEFV125</v>
       </c>
-      <c r="N86">
+      <c r="N87">
         <v>37500</v>
       </c>
-      <c r="O86" t="str">
+      <c r="O87" t="str">
         <v>activo</v>
       </c>
-      <c r="P86" t="str" xml:space="preserve">
+      <c r="P87" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (95 ppp al tamaño impreso; se amplió a 240)
 Usa la misma foto de equipo que SECEFV125</v>
       </c>
     </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87" t="str">
+    <row r="88" xml:space="preserve">
+      <c r="A88" t="str">
         <v>SECEFV125</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B88" t="str">
         <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS125, CAP. 125 KG, 10 HP, 220V/60HZ/TRIFASICO</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C88" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D88" t="str">
         <v>Efamein</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E88" t="str">
         <v>EFAS125</v>
       </c>
-      <c r="F87" t="str">
+      <c r="F88" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G87" t="str">
+      <c r="G88" t="str">
         <v>SECEFV125-Secadora  Industrial a vapor Efamein Modelo Efas125 220v trifasico.doc</v>
       </c>
-      <c r="H87" t="str">
+      <c r="H88" t="str">
         <v>sí · 510×750 px · 240 ppp</v>
       </c>
-      <c r="I87">
+      <c r="I88">
         <v>95</v>
       </c>
-      <c r="J87" t="str">
+      <c r="J88" t="str">
         <v>NO</v>
       </c>
-      <c r="K87" t="str">
+      <c r="K88" t="str">
         <v>no</v>
       </c>
-      <c r="L87">
+      <c r="L88">
         <v>52</v>
       </c>
-      <c r="M87" t="str">
+      <c r="M88" t="str">
         <v>SECEFG125</v>
       </c>
-      <c r="N87">
+      <c r="N88">
         <v>39500</v>
       </c>
-      <c r="O87" t="str">
+      <c r="O88" t="str">
         <v>activo</v>
       </c>
-      <c r="P87" t="str" xml:space="preserve">
+      <c r="P88" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (95 ppp al tamaño impreso; se amplió a 240)
 Usa la misma foto de equipo que SECEFG125</v>
       </c>
     </row>
-    <row r="88" xml:space="preserve">
-      <c r="A88" t="str">
+    <row r="89" xml:space="preserve">
+      <c r="A89" t="str">
         <v>SECEGI10</v>
       </c>
-      <c r="B88" t="str">
+      <c r="B89" t="str">
         <v>SECADORA SEMI INDUSTRIAL MARCA LG ELECTRICO GIANT C 10.2 KG, 220/60/1PH</v>
       </c>
-      <c r="C88" t="str">
+      <c r="C89" t="str">
         <v>LG</v>
       </c>
-      <c r="D88" t="str">
+      <c r="D89" t="str">
         <v>LG</v>
       </c>
-      <c r="E88" t="str">
+      <c r="E89" t="str">
         <v>GIANT C</v>
       </c>
-      <c r="F88" t="str">
+      <c r="F89" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G88" t="str">
+      <c r="G89" t="str">
         <v>SECEGI10-Secadora Giant C Gas 10.2 kg_ELECTRICO.doc</v>
       </c>
-      <c r="H88" t="str">
+      <c r="H89" t="str">
         <v>sí · 636×958 px · 299 ppp</v>
       </c>
-      <c r="I88">
+      <c r="I89">
         <v>132</v>
       </c>
-      <c r="J88" t="str">
+      <c r="J89" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K88" t="str">
+      <c r="K89" t="str">
         <v>no</v>
       </c>
-      <c r="L88">
+      <c r="L89">
         <v>19</v>
       </c>
-      <c r="M88" t="str">
+      <c r="M89" t="str">
         <v>SECPL102, SEPLU10</v>
       </c>
-      <c r="N88">
+      <c r="N89">
         <v>2100</v>
       </c>
-      <c r="O88" t="str">
+      <c r="O89" t="str">
         <v>activo</v>
       </c>
-      <c r="P88" t="str" xml:space="preserve">
+      <c r="P89" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (132 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que SECPL102, SEPLU10
 Descripción muy corta (19 líneas; la media de las fichas es 50)</v>
       </c>
     </row>
-    <row r="89" xml:space="preserve">
-      <c r="A89" t="str">
+    <row r="90" xml:space="preserve">
+      <c r="A90" t="str">
         <v>SECFDEE</v>
       </c>
-      <c r="B89" t="str">
+      <c r="B90" t="str">
         <v>SECADORA SEMI INDUSTRIAL PRIMUS, MOD:FDEE5BG8543MW01, CAP: 10.5 KG, CONTROL FRONTAL, (220V/60HZ/1PH),TAMBOR GALVANIZADO, CONTROL HEC ELECTRONIC, CALENTAMIENTO: ELÉCTRICO, 4600W 45° MANDO</v>
       </c>
-      <c r="C89" t="str">
+      <c r="C90" t="str">
         <v>PRIMUS</v>
       </c>
-      <c r="D89" t="str">
+      <c r="D90" t="str">
         <v>PRIMUS</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E90" t="str">
         <v>FDE</v>
       </c>
-      <c r="F89" t="str">
+      <c r="F90" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G90" t="str">
         <v>SECFDEE-SECADORA ELECTRICA FDE SEMI INDUSTRIAL 10.2 KG.docx</v>
       </c>
-      <c r="H89" t="str">
+      <c r="H90" t="str">
         <v>sí · 487×643 px · 229 ppp</v>
       </c>
-      <c r="I89">
+      <c r="I90">
         <v>220</v>
       </c>
-      <c r="J89" t="str">
+      <c r="J90" t="str">
         <v>NO</v>
       </c>
-      <c r="K89" t="str">
+      <c r="K90" t="str">
         <v>no</v>
       </c>
-      <c r="L89">
+      <c r="L90">
         <v>23</v>
       </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
-      <c r="N89">
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90">
         <v>2150</v>
       </c>
-      <c r="O89" t="str">
+      <c r="O90" t="str">
         <v>activo</v>
       </c>
-      <c r="P89" t="str" xml:space="preserve">
+      <c r="P90" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)</v>
       </c>
     </row>
-    <row r="90" xml:space="preserve">
-      <c r="A90" t="str">
+    <row r="91" xml:space="preserve">
+      <c r="A91" t="str">
         <v>SECG501</v>
       </c>
-      <c r="B90" t="str">
+      <c r="B91" t="str">
         <v>SECADORA INDUSTRIAL, MOD: UG050, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, CILINDRO GALV., CAP 25KG, H (380V/60Hz/3PH)</v>
       </c>
-      <c r="C90" t="str">
+      <c r="C91" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D90" t="str">
+      <c r="D91" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E90" t="str">
+      <c r="E91" t="str">
         <v>UG050</v>
       </c>
-      <c r="F90" t="str">
+      <c r="F91" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G90" t="str">
+      <c r="G91" t="str">
         <v>SECG501. SECADORA UG050 - DUAL DIGITAL - GALVANIZADO - ELÉCTRICO - 380V-60Hz-3Ph.docx</v>
       </c>
-      <c r="H90" t="str">
+      <c r="H91" t="str">
         <v>sí · 463×703 px · 218 ppp</v>
       </c>
-      <c r="I90">
+      <c r="I91">
         <v>222</v>
       </c>
-      <c r="J90" t="str">
+      <c r="J91" t="str">
         <v>sí · 208 ppp</v>
       </c>
-      <c r="K90" t="str">
+      <c r="K91" t="str">
         <v>no</v>
       </c>
-      <c r="L90">
+      <c r="L91">
         <v>51</v>
       </c>
-      <c r="M90" t="str">
-        <v/>
-      </c>
-      <c r="N90">
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91">
         <v>7850</v>
       </c>
-      <c r="O90" t="str">
+      <c r="O91" t="str">
         <v>activo</v>
       </c>
-      <c r="P90" t="str" xml:space="preserve">
+      <c r="P91" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Trae 1 imagen(es) de más: en la cotización solo entran el logo, el equipo y una vista de complemento</v>
       </c>
     </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91" t="str">
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str">
         <v>SECGDZ20</v>
       </c>
-      <c r="B91" t="str">
+      <c r="B92" t="str">
         <v>SECADORA ELECTRICA SAILSTAR, MOD.: GDZ-20E, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO, CAP:20KG, (220/60/3PH)</v>
       </c>
-      <c r="C91" t="str">
+      <c r="C92" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D91" t="str">
+      <c r="D92" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E92" t="str">
         <v>GDZ-20E</v>
       </c>
-      <c r="F91" t="str">
+      <c r="F92" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G92" t="str">
         <v>SECGDZ20-GDZ-20E  Secadora Industrial Electrica 20 Kg..docx</v>
       </c>
-      <c r="H91" t="str">
+      <c r="H92" t="str">
         <v>sí · 640×995 px · 301 ppp</v>
       </c>
-      <c r="I91">
+      <c r="I92">
         <v>124</v>
       </c>
-      <c r="J91" t="str">
+      <c r="J92" t="str">
         <v>NO</v>
       </c>
-      <c r="K91" t="str">
+      <c r="K92" t="str">
         <v>no</v>
       </c>
-      <c r="L91">
+      <c r="L92">
         <v>47</v>
       </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
-      <c r="N91">
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92">
         <v>7999</v>
       </c>
-      <c r="O91" t="str">
+      <c r="O92" t="str">
         <v>activo</v>
       </c>
-      <c r="P91" t="str" xml:space="preserve">
+      <c r="P92" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (124 ppp al tamaño impreso; se amplió a 301)</v>
       </c>
     </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92" t="str">
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str">
         <v>SECGIA10</v>
       </c>
-      <c r="B92" t="str">
+      <c r="B93" t="str">
         <v>SECADORA C., GAS, MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX APILABLE, CAP.:10.2KG, 220V/60/1PH, COD.: CDG27MUCPS</v>
       </c>
-      <c r="C92" t="str">
+      <c r="C93" t="str">
         <v>LG</v>
       </c>
-      <c r="D92" t="str">
+      <c r="D93" t="str">
         <v>LG</v>
       </c>
-      <c r="E92" t="str" xml:space="preserve">
+      <c r="E93" t="str" xml:space="preserve">
         <v xml:space="preserve">GIANT C MAX
 (CDG27MUCPS)</v>
       </c>
-      <c r="F92" t="str">
+      <c r="F93" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G92" t="str">
+      <c r="G93" t="str">
         <v>SECGIA10-Secadora Giant C Max Gas 10.2 kg OPL Apilable.doc</v>
       </c>
-      <c r="H92" t="str">
+      <c r="H93" t="str">
         <v>sí · 503×701 px · 237 ppp</v>
       </c>
-      <c r="I92">
+      <c r="I93">
         <v>250</v>
       </c>
-      <c r="J92" t="str">
+      <c r="J93" t="str">
         <v>NO</v>
       </c>
-      <c r="K92" t="str">
+      <c r="K93" t="str">
         <v>no</v>
       </c>
-      <c r="L92">
+      <c r="L93">
         <v>20</v>
       </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
-      <c r="N92">
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93">
         <v>2090</v>
       </c>
-      <c r="O92" t="str">
+      <c r="O93" t="str">
         <v>activo</v>
       </c>
-      <c r="P92" t="str" xml:space="preserve">
+      <c r="P93" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Trae 1 imagen(es) de más: en la cotización solo entran el logo, el equipo y una vista de complemento</v>
       </c>
     </row>
-    <row r="93" xml:space="preserve">
-      <c r="A93" t="str">
+    <row r="94" xml:space="preserve">
+      <c r="A94" t="str">
         <v>SECGIA102</v>
       </c>
-      <c r="B93" t="str">
+      <c r="B94" t="str">
         <v>SECADORA C., GAS, MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX SINGLE, CAP.:10.2KG, 220V/60/1PH, COD.: CDG27MSCPS</v>
       </c>
-      <c r="C93" t="str">
+      <c r="C94" t="str">
         <v>LG</v>
       </c>
-      <c r="D93" t="str">
+      <c r="D94" t="str">
         <v>LG</v>
       </c>
-      <c r="E93" t="str" xml:space="preserve">
+      <c r="E94" t="str" xml:space="preserve">
         <v xml:space="preserve">GIANT C MAX
 (CDG27MSCPS)</v>
       </c>
-      <c r="F93" t="str">
+      <c r="F94" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G94" t="str">
         <v>SECGIA102-Secadora Giant C Max Gas 10.2 kg OPL.doc</v>
       </c>
-      <c r="H93" t="str">
+      <c r="H94" t="str">
         <v>sí · 637×898 px · 300 ppp</v>
       </c>
-      <c r="I93">
+      <c r="I94">
         <v>151</v>
       </c>
-      <c r="J93" t="str">
+      <c r="J94" t="str">
         <v>NO</v>
       </c>
-      <c r="K93" t="str">
+      <c r="K94" t="str">
         <v>no</v>
       </c>
-      <c r="L93">
+      <c r="L94">
         <v>18</v>
       </c>
-      <c r="M93" t="str">
+      <c r="M94" t="str">
         <v>SECMAX15, SECMAX152</v>
       </c>
-      <c r="N93">
+      <c r="N94">
         <v>2090</v>
       </c>
-      <c r="O93" t="str">
+      <c r="O94" t="str">
         <v>activo</v>
       </c>
-      <c r="P93" t="str" xml:space="preserve">
+      <c r="P94" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que SECMAX15, SECMAX152
@@ -7118,105 +7187,105 @@
 Descripción muy corta (18 líneas; la media de las fichas es 50)</v>
       </c>
     </row>
-    <row r="94" xml:space="preserve">
-      <c r="A94" t="str">
+    <row r="95" xml:space="preserve">
+      <c r="A95" t="str">
         <v>SECGZZ50</v>
       </c>
-      <c r="B94" t="str">
+      <c r="B95" t="str">
         <v>SECADORA A VAPOR SAILSTAR MODELO GZZ-50II CON PANEL DE ACERO INOX, CAP.: 50KG, 200V/3PH/60HZ</v>
       </c>
-      <c r="C94" t="str">
+      <c r="C95" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="D94" t="str">
+      <c r="D95" t="str">
         <v>SAILSTAR</v>
       </c>
-      <c r="E94" t="str">
+      <c r="E95" t="str">
         <v>GZZ-50DII</v>
       </c>
-      <c r="F94" t="str">
+      <c r="F95" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G95" t="str">
         <v>SECGZZ50-GZZ-50DII Secadora Industrial a Vapor  50 Kg. - Panel de Acero inox.docx</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H95" t="str">
         <v>sí · 517×698 px · 243 ppp</v>
       </c>
-      <c r="I94">
+      <c r="I95">
         <v>205</v>
       </c>
-      <c r="J94" t="str">
+      <c r="J95" t="str">
         <v>NO</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K95" t="str">
         <v>no</v>
       </c>
-      <c r="L94">
+      <c r="L95">
         <v>51</v>
       </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94">
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95">
         <v>13500</v>
       </c>
-      <c r="O94" t="str">
+      <c r="O95" t="str">
         <v>activo</v>
       </c>
-      <c r="P94" t="str" xml:space="preserve">
+      <c r="P95" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)</v>
       </c>
     </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95" t="str">
+    <row r="96" xml:space="preserve">
+      <c r="A96" t="str">
         <v>SECMAX15</v>
       </c>
-      <c r="B95" t="str">
+      <c r="B96" t="str">
         <v>SECADORA C., GAS, MARCA: LG, C/S OPL, MOD.: TITAN LIGHT APILABLE, CAP15 KG, 220/60/1PH, COD.: CDT29MUCPS</v>
       </c>
-      <c r="C95" t="str">
+      <c r="C96" t="str">
         <v>LG</v>
       </c>
-      <c r="D95" t="str">
+      <c r="D96" t="str">
         <v>LG</v>
       </c>
-      <c r="E95" t="str" xml:space="preserve">
+      <c r="E96" t="str" xml:space="preserve">
         <v xml:space="preserve">TITAN LIGHT
 CDT29MUCPS</v>
       </c>
-      <c r="F95" t="str">
+      <c r="F96" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G96" t="str">
         <v>SECMAX15-Secadora Titan Light 15 kg OPL A GAS APILABLE.docx</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H96" t="str">
         <v>sí · 637×898 px · 300 ppp</v>
       </c>
-      <c r="I95">
+      <c r="I96">
         <v>142</v>
       </c>
-      <c r="J95" t="str">
+      <c r="J96" t="str">
         <v>NO</v>
       </c>
-      <c r="K95" t="str">
+      <c r="K96" t="str">
         <v>no</v>
       </c>
-      <c r="L95">
+      <c r="L96">
         <v>20</v>
       </c>
-      <c r="M95" t="str">
+      <c r="M96" t="str">
         <v>SECGIA102, SECMAX152</v>
       </c>
-      <c r="N95">
+      <c r="N96">
         <v>3150</v>
       </c>
-      <c r="O95" t="str">
+      <c r="O96" t="str">
         <v>activo</v>
       </c>
-      <c r="P95" t="str" xml:space="preserve">
+      <c r="P96" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (142 ppp al tamaño impreso; se amplió a 300)
@@ -7224,53 +7293,53 @@
 Trae 1 imagen(es) de más: en la cotización solo entran el logo, el equipo y una vista de complemento</v>
       </c>
     </row>
-    <row r="96" xml:space="preserve">
-      <c r="A96" t="str">
+    <row r="97" xml:space="preserve">
+      <c r="A97" t="str">
         <v>SECMAX152</v>
       </c>
-      <c r="B96" t="str">
+      <c r="B97" t="str">
         <v>SECADORA C., GAS, MARCA: LG, C/S OPL, MOD.: TITAN LIGHT SINGLE, CAP. 15 KG, 220/60/1PH, COD.: CDT29MSCPS</v>
       </c>
-      <c r="C96" t="str">
+      <c r="C97" t="str">
         <v>LG</v>
       </c>
-      <c r="D96" t="str">
+      <c r="D97" t="str">
         <v>LG</v>
       </c>
-      <c r="E96" t="str">
+      <c r="E97" t="str">
         <v>TITAN LIGHT</v>
       </c>
-      <c r="F96" t="str">
+      <c r="F97" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G97" t="str">
         <v>SECMAX152-Secadora Titan Light 15 kg OPL A GAS.docx</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H97" t="str">
         <v>sí · 637×898 px · 300 ppp</v>
       </c>
-      <c r="I96">
+      <c r="I97">
         <v>142</v>
       </c>
-      <c r="J96" t="str">
+      <c r="J97" t="str">
         <v>NO</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K97" t="str">
         <v>no</v>
       </c>
-      <c r="L96">
+      <c r="L97">
         <v>24</v>
       </c>
-      <c r="M96" t="str">
+      <c r="M97" t="str">
         <v>SECGIA102, SECMAX15</v>
       </c>
-      <c r="N96">
+      <c r="N97">
         <v>3150</v>
       </c>
-      <c r="O96" t="str">
+      <c r="O97" t="str">
         <v>activo</v>
       </c>
-      <c r="P96" t="str" xml:space="preserve">
+      <c r="P97" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (142 ppp al tamaño impreso; se amplió a 300)
@@ -7278,168 +7347,118 @@
 Trae 1 imagen(es) de más: en la cotización solo entran el logo, el equipo y una vista de complemento</v>
       </c>
     </row>
-    <row r="97" xml:space="preserve">
-      <c r="A97" t="str">
+    <row r="98" xml:space="preserve">
+      <c r="A98" t="str">
         <v>SECNDE</v>
       </c>
-      <c r="B97" t="str">
+      <c r="B98" t="str">
         <v>SECADORA SEMI INDUSTRIAL UNIMAC, MOD: NDENXAGS543MW01, CAP: 10.2 KG, PUERTA SECADORA SOLIDA, CILINDRO GALVANIZADO, CONTROL: QUANTUM H7S-A4 , CALENTAMEINTO: ELÉCTRICO, (220V/60HZ/1PH)</v>
       </c>
-      <c r="C97" t="str">
+      <c r="C98" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D97" t="str">
+      <c r="D98" t="str">
         <v>PRIMUS</v>
       </c>
-      <c r="E97" t="str">
+      <c r="E98" t="str">
         <v>NDE</v>
       </c>
-      <c r="F97" t="str">
+      <c r="F98" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G98" t="str">
         <v>SECNDE-SECADORA ELECTRICA NDE SEMI INDUSTRIAL 13.5 KG.docx</v>
       </c>
-      <c r="H97" t="str">
+      <c r="H98" t="str">
         <v>sí · 636×954 px · 299 ppp</v>
       </c>
-      <c r="I97">
+      <c r="I98">
         <v>133</v>
       </c>
-      <c r="J97" t="str">
+      <c r="J98" t="str">
         <v>NO</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K98" t="str">
         <v>no</v>
       </c>
-      <c r="L97">
+      <c r="L98">
         <v>51</v>
       </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
-      <c r="N97">
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98">
         <v>3150</v>
       </c>
-      <c r="O97" t="str">
+      <c r="O98" t="str">
         <v>activo</v>
       </c>
-      <c r="P97" t="str" xml:space="preserve">
+      <c r="P98" t="str" xml:space="preserve">
         <v xml:space="preserve">La ficha no trae el logo de la marca
 No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (133 ppp al tamaño impreso; se amplió a 299)
 El maestro dice marca UNIMAC y la ficha dice PRIMUS</v>
       </c>
     </row>
-    <row r="98" xml:space="preserve">
-      <c r="A98" t="str">
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str">
         <v>SECPL102</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B99" t="str">
         <v>SECADORA SEMI INDUSTRIAL MARCA LG GAS GIAN C + APILABLE 10.2, 220V/60/1PH</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C99" t="str">
         <v>LG</v>
       </c>
-      <c r="D98" t="str">
+      <c r="D99" t="str">
         <v>LG</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E99" t="str">
         <v>GIANT C +</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F99" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G99" t="str">
         <v>SECPL102-Secadora Giant C + Gas 10.2 kg -apilable.doc</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H99" t="str">
         <v>sí · 636×958 px · 299 ppp</v>
       </c>
-      <c r="I98">
+      <c r="I99">
         <v>132</v>
       </c>
-      <c r="J98" t="str">
+      <c r="J99" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K98" t="str">
+      <c r="K99" t="str">
         <v>no</v>
       </c>
-      <c r="L98">
+      <c r="L99">
         <v>17</v>
       </c>
-      <c r="M98" t="str">
+      <c r="M99" t="str">
         <v>SECEGI10, SEPLU10</v>
       </c>
-      <c r="N98">
+      <c r="N99">
         <v>1850</v>
       </c>
-      <c r="O98" t="str">
+      <c r="O99" t="str">
         <v>activo</v>
       </c>
-      <c r="P98" t="str" xml:space="preserve">
+      <c r="P99" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (132 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que SECEGI10, SEPLU10
 Descripción muy corta (17 líneas; la media de las fichas es 50)</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>SECU120</v>
-      </c>
-      <c r="B99" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: GAS GLP, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
-      </c>
-      <c r="C99" t="str">
-        <v>UNIMAC</v>
-      </c>
-      <c r="D99" t="str">
-        <v>UNIMAC</v>
-      </c>
-      <c r="E99" t="str">
-        <v>UT120</v>
-      </c>
-      <c r="F99" t="str">
-        <v>Cargada con su ficha</v>
-      </c>
-      <c r="G99" t="str">
-        <v>SECU120. SECADORA UT120-DUAL DIGITAL-GALVANIZADO-DOBLE ROTACIÓN-GLP -220V.docx</v>
-      </c>
-      <c r="H99" t="str">
-        <v>sí · 636×1097 px · 299 ppp</v>
-      </c>
-      <c r="I99">
-        <v>165</v>
-      </c>
-      <c r="J99" t="str">
-        <v>sí · 207 ppp</v>
-      </c>
-      <c r="K99" t="str">
-        <v>sí · 250 ppp</v>
-      </c>
-      <c r="L99">
-        <v>54</v>
-      </c>
-      <c r="M99" t="str">
-        <v>SECU120E, SECU120E2</v>
-      </c>
-      <c r="N99">
-        <v>16900</v>
-      </c>
-      <c r="O99" t="str">
-        <v>activo</v>
-      </c>
-      <c r="P99" t="str">
-        <v>Usa la misma foto de equipo que SECU120E, SECU120E2</v>
-      </c>
-    </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SECU1202</v>
+        <v>SECU120</v>
       </c>
       <c r="B100" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: UNLINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CALENTAMIENTO: GAS GLP, PANEL ESTÁNDAR, C/ OPTIDRY, Q(220V/60HZ/ 3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: GAS GLP, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
       </c>
       <c r="C100" t="str">
         <v>UNIMAC</v>
@@ -7454,42 +7473,42 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G100" t="str">
-        <v>SECU1202. SECADORA UT120-UNILIC TOUCH-INOXIDABLE-GLP-DOBLE ROTACION-OPTYDRY-220V.docx</v>
+        <v>SECU120. SECADORA UT120-DUAL DIGITAL-GALVANIZADO-DOBLE ROTACIÓN-GLP -220V.docx</v>
       </c>
       <c r="H100" t="str">
-        <v>sí · 638×1095 px · 300 ppp</v>
+        <v>sí · 636×1097 px · 299 ppp</v>
       </c>
       <c r="I100">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="J100" t="str">
         <v>sí · 207 ppp</v>
       </c>
       <c r="K100" t="str">
-        <v>sí · 427 ppp</v>
+        <v>sí · 250 ppp</v>
       </c>
       <c r="L100">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M100" t="str">
-        <v/>
+        <v>SECU120E, SECU120E2</v>
       </c>
       <c r="N100">
-        <v>21500</v>
+        <v>16900</v>
       </c>
       <c r="O100" t="str">
         <v>activo</v>
       </c>
       <c r="P100" t="str">
-        <v/>
+        <v>Usa la misma foto de equipo que SECU120E, SECU120E2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SECU120E</v>
+        <v>SECU1202</v>
       </c>
       <c r="B101" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: UNLINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CALENTAMIENTO: GAS GLP, PANEL ESTÁNDAR, C/ OPTIDRY, Q(220V/60HZ/ 3PH)</v>
       </c>
       <c r="C101" t="str">
         <v>UNIMAC</v>
@@ -7504,42 +7523,42 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G101" t="str">
-        <v>SECU120E. SECADORA UT120-DUAL DIGITAL-GALVANIZADO- DOBLE ROTACIÓN -ELÉCTRICO-220V.docx</v>
+        <v>SECU1202. SECADORA UT120-UNILIC TOUCH-INOXIDABLE-GLP-DOBLE ROTACION-OPTYDRY-220V.docx</v>
       </c>
       <c r="H101" t="str">
-        <v>sí · 636×1097 px · 299 ppp</v>
+        <v>sí · 638×1095 px · 300 ppp</v>
       </c>
       <c r="I101">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J101" t="str">
         <v>sí · 207 ppp</v>
       </c>
       <c r="K101" t="str">
-        <v>sí · 250 ppp</v>
+        <v>sí · 427 ppp</v>
       </c>
       <c r="L101">
         <v>53</v>
       </c>
       <c r="M101" t="str">
-        <v>SECU120, SECU120E2</v>
+        <v/>
       </c>
       <c r="N101">
-        <v>20500</v>
+        <v>21500</v>
       </c>
       <c r="O101" t="str">
         <v>activo</v>
       </c>
       <c r="P101" t="str">
-        <v>Usa la misma foto de equipo que SECU120, SECU120E2</v>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SECU120E2</v>
+        <v>SECU120E</v>
       </c>
       <c r="B102" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR,P(380V/60HZ/ 3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
       </c>
       <c r="C102" t="str">
         <v>UNIMAC</v>
@@ -7554,7 +7573,7 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G102" t="str">
-        <v>SECU120E2. SECADORA UT120-DUAL DIGITAL-DOBLE ROTACION -GALVANIZADO-ELÉCTRICO-380V.docx</v>
+        <v>SECU120E. SECADORA UT120-DUAL DIGITAL-GALVANIZADO- DOBLE ROTACIÓN -ELÉCTRICO-220V.docx</v>
       </c>
       <c r="H102" t="str">
         <v>sí · 636×1097 px · 299 ppp</v>
@@ -7569,27 +7588,27 @@
         <v>sí · 250 ppp</v>
       </c>
       <c r="L102">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M102" t="str">
-        <v>SECU120, SECU120E</v>
+        <v>SECU120, SECU120E2</v>
       </c>
       <c r="N102">
-        <v>20999</v>
+        <v>20500</v>
       </c>
       <c r="O102" t="str">
         <v>activo</v>
       </c>
       <c r="P102" t="str">
-        <v>Usa la misma foto de equipo que SECU120, SECU120E</v>
+        <v>Usa la misma foto de equipo que SECU120, SECU120E2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SECU1701</v>
+        <v>SECU120E2</v>
       </c>
       <c r="B103" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR,P(380V/60HZ/ 3PH)</v>
       </c>
       <c r="C103" t="str">
         <v>UNIMAC</v>
@@ -7598,48 +7617,48 @@
         <v>UNIMAC</v>
       </c>
       <c r="E103" t="str">
-        <v>UT170</v>
+        <v>UT120</v>
       </c>
       <c r="F103" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G103" t="str">
-        <v>SECU1701-SECADORA UT170-UNILINC TOUCH-DOBLE ROTACION-GN-OPTIDRY-GALVANIZADO-220V.docx</v>
+        <v>SECU120E2. SECADORA UT120-DUAL DIGITAL-DOBLE ROTACION -GALVANIZADO-ELÉCTRICO-380V.docx</v>
       </c>
       <c r="H103" t="str">
-        <v>sí · 639×1098 px · 301 ppp</v>
+        <v>sí · 636×1097 px · 299 ppp</v>
       </c>
       <c r="I103">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J103" t="str">
-        <v>sí · 300 ppp</v>
+        <v>sí · 207 ppp</v>
       </c>
       <c r="K103" t="str">
-        <v>sí · 372 ppp</v>
+        <v>sí · 250 ppp</v>
       </c>
       <c r="L103">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M103" t="str">
-        <v>SECU1702</v>
+        <v>SECU120, SECU120E</v>
       </c>
       <c r="N103">
-        <v>24999</v>
+        <v>20999</v>
       </c>
       <c r="O103" t="str">
         <v>activo</v>
       </c>
       <c r="P103" t="str">
-        <v>Usa la misma foto de equipo que SECU1702</v>
+        <v>Usa la misma foto de equipo que SECU120, SECU120E</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SECU1702</v>
+        <v>SECU1701</v>
       </c>
       <c r="B104" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="C104" t="str">
         <v>UNIMAC</v>
@@ -7654,13 +7673,13 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G104" t="str">
-        <v>SECU1702. SECADORA UT170-UNILINC TOUCH-DOBLE ROTACION-GN-OPTIDRY-INOX-220V.docx</v>
+        <v>SECU1701-SECADORA UT170-UNILINC TOUCH-DOBLE ROTACION-GN-OPTIDRY-GALVANIZADO-220V.docx</v>
       </c>
       <c r="H104" t="str">
         <v>sí · 639×1098 px · 301 ppp</v>
       </c>
       <c r="I104">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J104" t="str">
         <v>sí · 300 ppp</v>
@@ -7672,24 +7691,24 @@
         <v>63</v>
       </c>
       <c r="M104" t="str">
-        <v>SECU1701</v>
+        <v>SECU1702</v>
       </c>
       <c r="N104">
-        <v>23500</v>
+        <v>24999</v>
       </c>
       <c r="O104" t="str">
         <v>activo</v>
       </c>
       <c r="P104" t="str">
-        <v>Usa la misma foto de equipo que SECU1701</v>
-      </c>
-    </row>
-    <row r="105" xml:space="preserve">
+        <v>Usa la misma foto de equipo que SECU1702</v>
+      </c>
+    </row>
+    <row r="105">
       <c r="A105" t="str">
-        <v>SECU200</v>
+        <v>SECU1702</v>
       </c>
       <c r="B105" t="str">
-        <v>SECADORA INDUSTRIAL, MOD.: UT200L, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP. 90 KG, GAS GLP, C/ OPTIDRY, Q(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="C105" t="str">
         <v>UNIMAC</v>
@@ -7698,458 +7717,458 @@
         <v>UNIMAC</v>
       </c>
       <c r="E105" t="str">
-        <v>UT200</v>
+        <v>UT170</v>
       </c>
       <c r="F105" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G105" t="str">
-        <v>SECU200. SECADORA UT200-UNILINC TOUCH-DOBLE ROTACION-INOX-GLP-OPTIDRY-220V.docx</v>
+        <v>SECU1702. SECADORA UT170-UNILINC TOUCH-DOBLE ROTACION-GN-OPTIDRY-INOX-220V.docx</v>
       </c>
       <c r="H105" t="str">
-        <v>sí · 637×1090 px · 300 ppp</v>
+        <v>sí · 639×1098 px · 301 ppp</v>
       </c>
       <c r="I105">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="J105" t="str">
         <v>sí · 300 ppp</v>
       </c>
       <c r="K105" t="str">
-        <v>sí · 235 ppp</v>
+        <v>sí · 372 ppp</v>
       </c>
       <c r="L105">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M105" t="str">
-        <v>SECU2001</v>
+        <v>SECU1701</v>
       </c>
       <c r="N105">
-        <v>31500</v>
+        <v>23500</v>
       </c>
       <c r="O105" t="str">
         <v>activo</v>
       </c>
-      <c r="P105" t="str" xml:space="preserve">
+      <c r="P105" t="str">
+        <v>Usa la misma foto de equipo que SECU1701</v>
+      </c>
+    </row>
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str">
+        <v>SECU200</v>
+      </c>
+      <c r="B106" t="str">
+        <v>SECADORA INDUSTRIAL, MOD.: UT200L, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP. 90 KG, GAS GLP, C/ OPTIDRY, Q(220V/60HZ/1-3PH)</v>
+      </c>
+      <c r="C106" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="D106" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="E106" t="str">
+        <v>UT200</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Cargada con su ficha</v>
+      </c>
+      <c r="G106" t="str">
+        <v>SECU200. SECADORA UT200-UNILINC TOUCH-DOBLE ROTACION-INOX-GLP-OPTIDRY-220V.docx</v>
+      </c>
+      <c r="H106" t="str">
+        <v>sí · 637×1090 px · 300 ppp</v>
+      </c>
+      <c r="I106">
+        <v>186</v>
+      </c>
+      <c r="J106" t="str">
+        <v>sí · 300 ppp</v>
+      </c>
+      <c r="K106" t="str">
+        <v>sí · 235 ppp</v>
+      </c>
+      <c r="L106">
+        <v>52</v>
+      </c>
+      <c r="M106" t="str">
+        <v>SECU2001</v>
+      </c>
+      <c r="N106">
+        <v>31500</v>
+      </c>
+      <c r="O106" t="str">
+        <v>activo</v>
+      </c>
+      <c r="P106" t="str" xml:space="preserve">
         <v xml:space="preserve">Usa la misma foto de equipo que SECU2001
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str">
         <v>SECU2001</v>
       </c>
-      <c r="B106" t="str">
+      <c r="B107" t="str">
         <v>SECADORA INDUSTRIAL, MOD: UT200N, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP: 90KG, GAS NATURAL, C/ OPTIDRY , Q (220V/60HZ/3PH)</v>
       </c>
-      <c r="C106" t="str">
+      <c r="C107" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D106" t="str">
+      <c r="D107" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E106" t="str">
+      <c r="E107" t="str">
         <v>UT200</v>
       </c>
-      <c r="F106" t="str">
+      <c r="F107" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G106" t="str">
+      <c r="G107" t="str">
         <v>SECU2001. SECADORA UT200-UNILINC TOUCH-DOBLE ROTACION-INOX-GN-OPTIDRY-220V.docx</v>
       </c>
-      <c r="H106" t="str">
+      <c r="H107" t="str">
         <v>sí · 637×1090 px · 300 ppp</v>
       </c>
-      <c r="I106">
+      <c r="I107">
         <v>186</v>
       </c>
-      <c r="J106" t="str">
+      <c r="J107" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K106" t="str">
+      <c r="K107" t="str">
         <v>sí · 235 ppp</v>
       </c>
-      <c r="L106">
+      <c r="L107">
         <v>52</v>
       </c>
-      <c r="M106" t="str">
+      <c r="M107" t="str">
         <v>SECU200</v>
       </c>
-      <c r="N106">
+      <c r="N107">
         <v>31500</v>
       </c>
-      <c r="O106" t="str">
+      <c r="O107" t="str">
         <v>activo</v>
       </c>
-      <c r="P106" t="str" xml:space="preserve">
+      <c r="P107" t="str" xml:space="preserve">
         <v xml:space="preserve">Usa la misma foto de equipo que SECU200
 La tabla de cabecera no dice: calentamiento</v>
       </c>
     </row>
-    <row r="107" xml:space="preserve">
-      <c r="A107" t="str">
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str">
         <v>SECU30</v>
       </c>
-      <c r="B107" t="str">
+      <c r="B108" t="str">
         <v>SECADORA INDUSTRIAL, MOD: UT030E, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, G (220V/60Hz/3PH)</v>
       </c>
-      <c r="C107" t="str">
+      <c r="C108" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D107" t="str">
+      <c r="D108" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E107" t="str">
+      <c r="E108" t="str">
         <v>UT030E</v>
       </c>
-      <c r="F107" t="str">
+      <c r="F108" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G107" t="str">
+      <c r="G108" t="str">
         <v>SECU30. SECADORA UT030E-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-ELÉCTRICO-220V.docx</v>
       </c>
-      <c r="H107" t="str">
+      <c r="H108" t="str">
         <v>sí · 638×1117 px · 300 ppp</v>
       </c>
-      <c r="I107">
+      <c r="I108">
         <v>152</v>
       </c>
-      <c r="J107" t="str">
+      <c r="J108" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K107" t="str">
+      <c r="K108" t="str">
         <v>no</v>
       </c>
-      <c r="L107">
+      <c r="L108">
         <v>50</v>
       </c>
-      <c r="M107" t="str">
+      <c r="M108" t="str">
         <v>SECU301, SECU303, SECU502, SECUT055V, SECUT55E</v>
       </c>
-      <c r="N107">
+      <c r="N108">
         <v>7150</v>
       </c>
-      <c r="O107" t="str">
+      <c r="O108" t="str">
         <v>activo</v>
       </c>
-      <c r="P107" t="str" xml:space="preserve">
+      <c r="P108" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que SECU301, SECU303, SECU502, SECUT055V, SECUT55E</v>
       </c>
     </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108" t="str">
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str">
         <v>SECU301</v>
       </c>
-      <c r="B108" t="str">
+      <c r="B109" t="str">
         <v>SECADORA INDUSTRIAL, MOD: UT030E, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, H (380V/60Hz/3PH)</v>
       </c>
-      <c r="C108" t="str">
+      <c r="C109" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D108" t="str">
+      <c r="D109" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E108" t="str">
+      <c r="E109" t="str">
         <v>UT030E</v>
       </c>
-      <c r="F108" t="str">
+      <c r="F109" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G108" t="str">
+      <c r="G109" t="str">
         <v>SECU301. SECADORA UT030E-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-ELÉCTRICO-380V.docx</v>
       </c>
-      <c r="H108" t="str">
+      <c r="H109" t="str">
         <v>sí · 638×1117 px · 300 ppp</v>
       </c>
-      <c r="I108">
+      <c r="I109">
         <v>152</v>
       </c>
-      <c r="J108" t="str">
+      <c r="J109" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K108" t="str">
+      <c r="K109" t="str">
         <v>no</v>
       </c>
-      <c r="L108">
+      <c r="L109">
         <v>50</v>
       </c>
-      <c r="M108" t="str">
+      <c r="M109" t="str">
         <v>SECU30, SECU303, SECU502, SECUT055V, SECUT55E</v>
       </c>
-      <c r="N108">
+      <c r="N109">
         <v>7150</v>
       </c>
-      <c r="O108" t="str">
+      <c r="O109" t="str">
         <v>activo</v>
       </c>
-      <c r="P108" t="str" xml:space="preserve">
+      <c r="P109" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que SECU30, SECU303, SECU502, SECUT055V, SECUT55E</v>
       </c>
     </row>
-    <row r="109" xml:space="preserve">
-      <c r="A109" t="str">
+    <row r="110" xml:space="preserve">
+      <c r="A110" t="str">
         <v>SECU302</v>
       </c>
-      <c r="B109" t="str">
+      <c r="B110" t="str">
         <v>SECADORA INDUSTRIAL, MOD: UT030N, CONTROL: UNILINC TOUCH, GAS NATURAL, DOBLE ROTACION, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO INOXIDABLE, C/ OPTIDRY, CAP 14KG, X (220V/60Hz/1-3PH)</v>
       </c>
-      <c r="C109" t="str">
+      <c r="C110" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D109" t="str">
+      <c r="D110" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E109" t="str">
+      <c r="E110" t="str">
         <v>UT30N</v>
       </c>
-      <c r="F109" t="str">
+      <c r="F110" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G109" t="str">
+      <c r="G110" t="str">
         <v>SECU302. SECADORA UT030-UNILINC TOUCH-DOBLE ROTACION-INOX-OPTYDRY-GN-220V.docx</v>
       </c>
-      <c r="H109" t="str">
+      <c r="H110" t="str">
         <v>sí · 411×735 px · 194 ppp</v>
       </c>
-      <c r="I109">
+      <c r="I110">
         <v>74</v>
       </c>
-      <c r="J109" t="str">
+      <c r="J110" t="str">
         <v>sí · 207 ppp</v>
       </c>
-      <c r="K109" t="str">
+      <c r="K110" t="str">
         <v>sí · 258 ppp</v>
       </c>
-      <c r="L109">
+      <c r="L110">
         <v>56</v>
       </c>
-      <c r="M109" t="str">
+      <c r="M110" t="str">
         <v>SECU55</v>
       </c>
-      <c r="N109">
+      <c r="N110">
         <v>7999</v>
       </c>
-      <c r="O109" t="str">
+      <c r="O110" t="str">
         <v>activo</v>
       </c>
-      <c r="P109" t="str" xml:space="preserve">
+      <c r="P110" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (74 ppp al tamaño impreso; se amplió a 194)
 La foto del equipo queda por debajo de la norma aun ampliada (194 ppp)
 Usa la misma foto de equipo que SECU55</v>
       </c>
     </row>
-    <row r="110" xml:space="preserve">
-      <c r="A110" t="str">
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str">
         <v>SECU303</v>
       </c>
-      <c r="B110" t="str">
+      <c r="B111" t="str">
         <v>SECADORA INDUSTRIAL, MOD: UT030N, CONTROL: DUAL DIGITAL, GAS NATURAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, X (220V/60Hz/1-3PH)</v>
       </c>
-      <c r="C110" t="str">
+      <c r="C111" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D110" t="str">
+      <c r="D111" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E110" t="str">
+      <c r="E111" t="str">
         <v>UT030N</v>
       </c>
-      <c r="F110" t="str">
+      <c r="F111" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G110" t="str">
+      <c r="G111" t="str">
         <v>SECU303. SECADORA UT030N-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GN-220V.docx</v>
       </c>
-      <c r="H110" t="str">
+      <c r="H111" t="str">
         <v>sí · 638×1117 px · 300 ppp</v>
       </c>
-      <c r="I110">
+      <c r="I111">
         <v>152</v>
       </c>
-      <c r="J110" t="str">
+      <c r="J111" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K110" t="str">
+      <c r="K111" t="str">
         <v>no</v>
       </c>
-      <c r="L110">
+      <c r="L111">
         <v>53</v>
       </c>
-      <c r="M110" t="str">
+      <c r="M111" t="str">
         <v>SECU30, SECU301, SECU502, SECUT055V, SECUT55E</v>
       </c>
-      <c r="N110">
+      <c r="N111">
         <v>6800</v>
       </c>
-      <c r="O110" t="str">
+      <c r="O111" t="str">
         <v>activo</v>
       </c>
-      <c r="P110" t="str" xml:space="preserve">
+      <c r="P111" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que SECU30, SECU301, SECU502, SECUT055V, SECUT55E</v>
       </c>
     </row>
-    <row r="111" xml:space="preserve">
-      <c r="A111" t="str">
+    <row r="112" xml:space="preserve">
+      <c r="A112" t="str">
         <v>SECU502</v>
       </c>
-      <c r="B111" t="str">
+      <c r="B112" t="str">
         <v>SECADORA INDUSTRIAL MOD. UT055L, CONTROL: UNILINC TOUCH, A GAS GLP, DOBLE ROTACION, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO INOXIDABLE, C/ OPTIDRY, CAP: 25 KG, X (220V/60HZ/1-3PH)</v>
       </c>
-      <c r="C111" t="str">
+      <c r="C112" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D111" t="str">
+      <c r="D112" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E111" t="str">
+      <c r="E112" t="str">
         <v>UT055</v>
       </c>
-      <c r="F111" t="str">
+      <c r="F112" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G111" t="str">
+      <c r="G112" t="str">
         <v>SECU502. SECADORA UT055-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-220V.docx</v>
       </c>
-      <c r="H111" t="str">
+      <c r="H112" t="str">
         <v>sí · 638×1117 px · 300 ppp</v>
       </c>
-      <c r="I111">
+      <c r="I112">
         <v>166</v>
       </c>
-      <c r="J111" t="str">
+      <c r="J112" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K111" t="str">
+      <c r="K112" t="str">
         <v>no</v>
       </c>
-      <c r="L111">
+      <c r="L112">
         <v>54</v>
       </c>
-      <c r="M111" t="str">
+      <c r="M112" t="str">
         <v>SECU30, SECU301, SECU303, SECUT055V, SECUT55E</v>
       </c>
-      <c r="N111">
+      <c r="N112">
         <v>9500</v>
       </c>
-      <c r="O111" t="str">
+      <c r="O112" t="str">
         <v>activo</v>
       </c>
-      <c r="P111" t="str" xml:space="preserve">
+      <c r="P112" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que SECU30, SECU301, SECU303, SECUT055V, SECUT55E</v>
       </c>
     </row>
-    <row r="112" xml:space="preserve">
-      <c r="A112" t="str">
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str">
         <v>SECU55</v>
       </c>
-      <c r="B112" t="str">
+      <c r="B113" t="str">
         <v>SECADORA INDUSTRIAL MOD. UT055L, CONTROL: DUAL DIGITAL, A GAS GLP, DOBLE ROTACION, CILINDRO GALVANIZADO, PANEL ESTÁNDAR, C/ OPTIDRY, CAP: 25 KG, X (220V/60HZ/1-3PH)</v>
       </c>
-      <c r="C112" t="str">
+      <c r="C113" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D112" t="str">
+      <c r="D113" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="E112" t="str">
+      <c r="E113" t="str">
         <v>UT055L</v>
       </c>
-      <c r="F112" t="str">
+      <c r="F113" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G112" t="str">
+      <c r="G113" t="str">
         <v>SECU55. SECADORA UT055L-UNILINC TOUCH-OPTIDRY-DOBLE ROTACION-INOX-GLP-220V.1-3PH.docx</v>
       </c>
-      <c r="H112" t="str">
+      <c r="H113" t="str">
         <v>sí · 411×735 px · 194 ppp</v>
       </c>
-      <c r="I112">
+      <c r="I113">
         <v>74</v>
       </c>
-      <c r="J112" t="str">
+      <c r="J113" t="str">
         <v>sí · 207 ppp</v>
       </c>
-      <c r="K112" t="str">
+      <c r="K113" t="str">
         <v>sí · 258 ppp</v>
       </c>
-      <c r="L112">
+      <c r="L113">
         <v>59</v>
       </c>
-      <c r="M112" t="str">
+      <c r="M113" t="str">
         <v>SECU302</v>
       </c>
-      <c r="N112">
+      <c r="N113">
         <v>7350</v>
       </c>
-      <c r="O112" t="str">
+      <c r="O113" t="str">
         <v>activo</v>
       </c>
-      <c r="P112" t="str" xml:space="preserve">
+      <c r="P113" t="str" xml:space="preserve">
         <v xml:space="preserve">Foto del equipo de baja resolución (74 ppp al tamaño impreso; se amplió a 194)
 La foto del equipo queda por debajo de la norma aun ampliada (194 ppp)
 Usa la misma foto de equipo que SECU302</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>SECU552</v>
-      </c>
-      <c r="B113" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, OPTIDRY, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
-      </c>
-      <c r="C113" t="str">
-        <v>UNIMAC</v>
-      </c>
-      <c r="D113" t="str">
-        <v>UNIMAC</v>
-      </c>
-      <c r="E113" t="str">
-        <v>UT075</v>
-      </c>
-      <c r="F113" t="str">
-        <v>Cargada con su ficha</v>
-      </c>
-      <c r="G113" t="str">
-        <v>SECU552. SECADORA UT075-UNILICH TOUCH-DOBLE ROTACIÓN-GALVANIZADO-GN-220V OPTIDRY.docx</v>
-      </c>
-      <c r="H113" t="str">
-        <v>sí · 451×824 px · 218 ppp</v>
-      </c>
-      <c r="I113">
-        <v>222</v>
-      </c>
-      <c r="J113" t="str">
-        <v>sí · 208 ppp</v>
-      </c>
-      <c r="K113" t="str">
-        <v>sí · 276 ppp</v>
-      </c>
-      <c r="L113">
-        <v>55</v>
-      </c>
-      <c r="M113" t="str">
-        <v/>
-      </c>
-      <c r="N113">
-        <v>9750</v>
-      </c>
-      <c r="O113" t="str">
-        <v>activo</v>
-      </c>
-      <c r="P113" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SECU553</v>
+        <v>SECU552</v>
       </c>
       <c r="B114" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, OPTIDRY, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="C114" t="str">
         <v>UNIMAC</v>
@@ -8164,42 +8183,42 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G114" t="str">
-        <v>SECU553. SECADORA UT075-DUAL DIGITAL DOBLE ROTACIÓN-GALVANIZADO-GN-220V.docx</v>
+        <v>SECU552. SECADORA UT075-UNILICH TOUCH-DOBLE ROTACIÓN-GALVANIZADO-GN-220V OPTIDRY.docx</v>
       </c>
       <c r="H114" t="str">
-        <v>sí · 639×1063 px · 301 ppp</v>
+        <v>sí · 451×824 px · 218 ppp</v>
       </c>
       <c r="I114">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="J114" t="str">
         <v>sí · 208 ppp</v>
       </c>
       <c r="K114" t="str">
-        <v>sí · 300 ppp</v>
+        <v>sí · 276 ppp</v>
       </c>
       <c r="L114">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M114" t="str">
-        <v>SECU75, SECU75L</v>
+        <v/>
       </c>
       <c r="N114">
-        <v>8500</v>
+        <v>9750</v>
       </c>
       <c r="O114" t="str">
         <v>activo</v>
       </c>
       <c r="P114" t="str">
-        <v>Usa la misma foto de equipo que SECU75, SECU75L</v>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SECU75</v>
+        <v>SECU553</v>
       </c>
       <c r="B115" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, PANEL ESTÁNDAR , CILINDRO GALVANIZADO, GAS GLP, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="C115" t="str">
         <v>UNIMAC</v>
@@ -8214,7 +8233,7 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G115" t="str">
-        <v>SECU75. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-220V.docx</v>
+        <v>SECU553. SECADORA UT075-DUAL DIGITAL DOBLE ROTACIÓN-GALVANIZADO-GN-220V.docx</v>
       </c>
       <c r="H115" t="str">
         <v>sí · 639×1063 px · 301 ppp</v>
@@ -8229,27 +8248,27 @@
         <v>sí · 300 ppp</v>
       </c>
       <c r="L115">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M115" t="str">
-        <v>SECU553, SECU75L</v>
+        <v>SECU75, SECU75L</v>
       </c>
       <c r="N115">
-        <v>7850</v>
+        <v>8500</v>
       </c>
       <c r="O115" t="str">
         <v>activo</v>
       </c>
       <c r="P115" t="str">
-        <v>Usa la misma foto de equipo que SECU553, SECU75L</v>
+        <v>Usa la misma foto de equipo que SECU75, SECU75L</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SECU752</v>
+        <v>SECU75</v>
       </c>
       <c r="B116" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL FRONTAL INOXIDABLE,OPTIDRY, CILINDRO INOXIDABLE, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, PANEL ESTÁNDAR , CILINDRO GALVANIZADO, GAS GLP, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="C116" t="str">
         <v>UNIMAC</v>
@@ -8264,42 +8283,42 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G116" t="str">
-        <v>SECU752. SECADORA UT075-UNILINC TOUCH-DOBLE ROTACION-INOX-C. INOX-GN-220V OPTIDRY.docx</v>
+        <v>SECU75. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-220V.docx</v>
       </c>
       <c r="H116" t="str">
-        <v>sí · 635×1137 px · 301 ppp</v>
+        <v>sí · 639×1063 px · 301 ppp</v>
       </c>
       <c r="I116">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="J116" t="str">
-        <v>sí · 207 ppp</v>
+        <v>sí · 208 ppp</v>
       </c>
       <c r="K116" t="str">
-        <v>sí · 276 ppp</v>
+        <v>sí · 300 ppp</v>
       </c>
       <c r="L116">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M116" t="str">
-        <v/>
+        <v>SECU553, SECU75L</v>
       </c>
       <c r="N116">
-        <v>11950</v>
+        <v>7850</v>
       </c>
       <c r="O116" t="str">
         <v>activo</v>
       </c>
       <c r="P116" t="str">
-        <v/>
+        <v>Usa la misma foto de equipo que SECU553, SECU75L</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SECU755</v>
+        <v>SECU752</v>
       </c>
       <c r="B117" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL ESTÁNDAR , OPTIDRY, CILINDRO INOXIDABLE, GAS GLP, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL FRONTAL INOXIDABLE,OPTIDRY, CILINDRO INOXIDABLE, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="C117" t="str">
         <v>UNIMAC</v>
@@ -8308,34 +8327,34 @@
         <v>UNIMAC</v>
       </c>
       <c r="E117" t="str">
-        <v>UT075L</v>
+        <v>UT075</v>
       </c>
       <c r="F117" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G117" t="str">
-        <v>SECU755. SECADORA UT075-UNILICH TOUCH -DOBLE ROTACION-INOXIDABLE-GLP-220V OPTIDRY.docx</v>
+        <v>SECU752. SECADORA UT075-UNILINC TOUCH-DOBLE ROTACION-INOX-C. INOX-GN-220V OPTIDRY.docx</v>
       </c>
       <c r="H117" t="str">
-        <v>sí · 457×749 px · 215 ppp</v>
+        <v>sí · 635×1137 px · 301 ppp</v>
       </c>
       <c r="I117">
-        <v>222</v>
+        <v>150</v>
       </c>
       <c r="J117" t="str">
-        <v>sí · 208 ppp</v>
+        <v>sí · 207 ppp</v>
       </c>
       <c r="K117" t="str">
-        <v>sí · 258 ppp</v>
+        <v>sí · 276 ppp</v>
       </c>
       <c r="L117">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M117" t="str">
         <v/>
       </c>
       <c r="N117">
-        <v>9900</v>
+        <v>11950</v>
       </c>
       <c r="O117" t="str">
         <v>activo</v>
@@ -8346,10 +8365,10 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SECU75L</v>
+        <v>SECU755</v>
       </c>
       <c r="B118" t="str">
-        <v>SECADORA INDUSTRIAL MOD. UT075, CONTROL: DUAL DIGITAL , DOBLE ROTACION, CILINDRO GALVANIZADO , PANEL ESTANDAR , CAP: 34 KG, A GAS GLP, (380V/60HZ/3PH), BLANCO</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL ESTÁNDAR , OPTIDRY, CILINDRO INOXIDABLE, GAS GLP, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="C118" t="str">
         <v>UNIMAC</v>
@@ -8358,48 +8377,48 @@
         <v>UNIMAC</v>
       </c>
       <c r="E118" t="str">
-        <v>UT075</v>
+        <v>UT075L</v>
       </c>
       <c r="F118" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G118" t="str">
-        <v>SECU75L. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-380V.docx</v>
+        <v>SECU755. SECADORA UT075-UNILICH TOUCH -DOBLE ROTACION-INOXIDABLE-GLP-220V OPTIDRY.docx</v>
       </c>
       <c r="H118" t="str">
-        <v>sí · 639×1063 px · 301 ppp</v>
+        <v>sí · 457×749 px · 215 ppp</v>
       </c>
       <c r="I118">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="J118" t="str">
         <v>sí · 208 ppp</v>
       </c>
       <c r="K118" t="str">
-        <v>sí · 300 ppp</v>
+        <v>sí · 258 ppp</v>
       </c>
       <c r="L118">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M118" t="str">
-        <v>SECU553, SECU75</v>
+        <v/>
       </c>
       <c r="N118">
-        <v>7999</v>
+        <v>9900</v>
       </c>
       <c r="O118" t="str">
         <v>activo</v>
       </c>
       <c r="P118" t="str">
-        <v>Usa la misma foto de equipo que SECU553, SECU75</v>
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SECUT055V</v>
+        <v>SECU75L</v>
       </c>
       <c r="B119" t="str">
-        <v>SECADORA INDUSTRIAL MOD. UT055, CAP. 25 KG, DUAL DIGITAL, VAPOR , TAMBOR GALVANIZADO, DOBLE ROTACION, 220V/60HZ/1-3PH</v>
+        <v>SECADORA INDUSTRIAL MOD. UT075, CONTROL: DUAL DIGITAL , DOBLE ROTACION, CILINDRO GALVANIZADO , PANEL ESTANDAR , CAP: 34 KG, A GAS GLP, (380V/60HZ/3PH), BLANCO</v>
       </c>
       <c r="C119" t="str">
         <v>UNIMAC</v>
@@ -8408,48 +8427,48 @@
         <v>UNIMAC</v>
       </c>
       <c r="E119" t="str">
-        <v>UT055</v>
+        <v>UT075</v>
       </c>
       <c r="F119" t="str">
         <v>Cargada con su ficha</v>
       </c>
       <c r="G119" t="str">
-        <v>SECUT055V-SECADORA UT055-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-VAPOR-220V.docx</v>
+        <v>SECU75L. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-380V.docx</v>
       </c>
       <c r="H119" t="str">
-        <v>sí · 638×1117 px · 300 ppp</v>
+        <v>sí · 639×1063 px · 301 ppp</v>
       </c>
       <c r="I119">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="J119" t="str">
+        <v>sí · 208 ppp</v>
+      </c>
+      <c r="K119" t="str">
         <v>sí · 300 ppp</v>
-      </c>
-      <c r="K119" t="str">
-        <v>sí · 237 ppp</v>
       </c>
       <c r="L119">
         <v>52</v>
       </c>
       <c r="M119" t="str">
-        <v>SECU30, SECU301, SECU303, SECU502, SECUT55E</v>
+        <v>SECU553, SECU75</v>
       </c>
       <c r="N119">
-        <v>10750</v>
+        <v>7999</v>
       </c>
       <c r="O119" t="str">
         <v>activo</v>
       </c>
       <c r="P119" t="str">
-        <v>Usa la misma foto de equipo que SECU30, SECU301, SECU303, SECU502, SECUT55E</v>
-      </c>
-    </row>
-    <row r="120" xml:space="preserve">
+        <v>Usa la misma foto de equipo que SECU553, SECU75</v>
+      </c>
+    </row>
+    <row r="120">
       <c r="A120" t="str">
-        <v>SECUT55E</v>
+        <v>SECUT055V</v>
       </c>
       <c r="B120" t="str">
-        <v>SECADORAINDUSTRIAL ELECTRICA MOD. UT055, CAP. 25 KG, DUAL DIGITAL, 220V/60HZ/3PH</v>
+        <v>SECADORA INDUSTRIAL MOD. UT055, CAP. 25 KG, DUAL DIGITAL, VAPOR , TAMBOR GALVANIZADO, DOBLE ROTACION, 220V/60HZ/1-3PH</v>
       </c>
       <c r="C120" t="str">
         <v>UNIMAC</v>
@@ -8464,7 +8483,7 @@
         <v>Cargada con su ficha</v>
       </c>
       <c r="G120" t="str">
-        <v>SECUT55E-SECADORA UT055-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-ELECTRICA-220V.docx</v>
+        <v>SECUT055V-SECADORA UT055-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-VAPOR-220V.docx</v>
       </c>
       <c r="H120" t="str">
         <v>sí · 638×1117 px · 300 ppp</v>
@@ -8476,651 +8495,651 @@
         <v>sí · 300 ppp</v>
       </c>
       <c r="K120" t="str">
-        <v>no</v>
+        <v>sí · 237 ppp</v>
       </c>
       <c r="L120">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M120" t="str">
-        <v>SECU30, SECU301, SECU303, SECU502, SECUT055V</v>
+        <v>SECU30, SECU301, SECU303, SECU502, SECUT55E</v>
       </c>
       <c r="N120">
-        <v>8250</v>
+        <v>10750</v>
       </c>
       <c r="O120" t="str">
         <v>activo</v>
       </c>
-      <c r="P120" t="str" xml:space="preserve">
+      <c r="P120" t="str">
+        <v>Usa la misma foto de equipo que SECU30, SECU301, SECU303, SECU502, SECUT55E</v>
+      </c>
+    </row>
+    <row r="121" xml:space="preserve">
+      <c r="A121" t="str">
+        <v>SECUT55E</v>
+      </c>
+      <c r="B121" t="str">
+        <v>SECADORAINDUSTRIAL ELECTRICA MOD. UT055, CAP. 25 KG, DUAL DIGITAL, 220V/60HZ/3PH</v>
+      </c>
+      <c r="C121" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="D121" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="E121" t="str">
+        <v>UT055</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Cargada con su ficha</v>
+      </c>
+      <c r="G121" t="str">
+        <v>SECUT55E-SECADORA UT055-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-ELECTRICA-220V.docx</v>
+      </c>
+      <c r="H121" t="str">
+        <v>sí · 638×1117 px · 300 ppp</v>
+      </c>
+      <c r="I121">
+        <v>152</v>
+      </c>
+      <c r="J121" t="str">
+        <v>sí · 300 ppp</v>
+      </c>
+      <c r="K121" t="str">
+        <v>no</v>
+      </c>
+      <c r="L121">
+        <v>51</v>
+      </c>
+      <c r="M121" t="str">
+        <v>SECU30, SECU301, SECU303, SECU502, SECUT055V</v>
+      </c>
+      <c r="N121">
+        <v>8250</v>
+      </c>
+      <c r="O121" t="str">
+        <v>activo</v>
+      </c>
+      <c r="P121" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Usa la misma foto de equipo que SECU30, SECU301, SECU303, SECU502, SECUT055V</v>
       </c>
     </row>
-    <row r="121" xml:space="preserve">
-      <c r="A121" t="str">
+    <row r="122" xml:space="preserve">
+      <c r="A122" t="str">
         <v>SEPLU10</v>
       </c>
-      <c r="B121" t="str">
+      <c r="B122" t="str">
         <v>SECADORA SEMI INDUSTRIAL MARCA LG GAS GIAN C + 10.2, 220V/60/1PH</v>
       </c>
-      <c r="C121" t="str">
+      <c r="C122" t="str">
         <v>LG</v>
       </c>
-      <c r="D121" t="str">
+      <c r="D122" t="str">
         <v>LG</v>
       </c>
-      <c r="E121" t="str">
+      <c r="E122" t="str">
         <v>GIANT C</v>
       </c>
-      <c r="F121" t="str">
+      <c r="F122" t="str">
         <v>Cargada con su ficha</v>
       </c>
-      <c r="G121" t="str">
+      <c r="G122" t="str">
         <v>SEPLU10-Secadora Giant C + Gas 10.2 kg.doc</v>
       </c>
-      <c r="H121" t="str">
+      <c r="H122" t="str">
         <v>sí · 636×958 px · 299 ppp</v>
       </c>
-      <c r="I121">
+      <c r="I122">
         <v>132</v>
       </c>
-      <c r="J121" t="str">
+      <c r="J122" t="str">
         <v>sí · 300 ppp</v>
       </c>
-      <c r="K121" t="str">
+      <c r="K122" t="str">
         <v>no</v>
       </c>
-      <c r="L121">
+      <c r="L122">
         <v>17</v>
       </c>
-      <c r="M121" t="str">
+      <c r="M122" t="str">
         <v>SECEGI10, SECPL102</v>
       </c>
-      <c r="N121">
+      <c r="N122">
         <v>1850</v>
       </c>
-      <c r="O121" t="str">
+      <c r="O122" t="str">
         <v>activo</v>
       </c>
-      <c r="P121" t="str" xml:space="preserve">
+      <c r="P122" t="str" xml:space="preserve">
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (132 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que SECEGI10, SECPL102
 Descripción muy corta (17 líneas; la media de las fichas es 50)</v>
       </c>
     </row>
-    <row r="122" xml:space="preserve">
-      <c r="A122" t="str">
+    <row r="123" xml:space="preserve">
+      <c r="A123" t="str">
         <v>1SECU1701</v>
       </c>
-      <c r="B122" t="str">
+      <c r="B123" t="str">
         <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
       </c>
-      <c r="C122" t="str">
+      <c r="C123" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D122" t="str">
-        <v/>
-      </c>
-      <c r="E122" t="str">
-        <v/>
-      </c>
-      <c r="F122" t="str">
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G122" t="str">
+      <c r="G123" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H122" t="str">
+      <c r="H123" t="str">
         <v>NO</v>
       </c>
-      <c r="I122" t="str">
-        <v/>
-      </c>
-      <c r="J122" t="str">
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
         <v>NO</v>
       </c>
-      <c r="K122" t="str">
+      <c r="K123" t="str">
         <v>no</v>
       </c>
-      <c r="L122" t="str">
-        <v/>
-      </c>
-      <c r="M122" t="str">
-        <v/>
-      </c>
-      <c r="N122">
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123">
         <v>24999</v>
       </c>
-      <c r="O122" t="str">
+      <c r="O123" t="str">
         <v>retirado</v>
       </c>
-      <c r="P122" t="str" xml:space="preserve">
+      <c r="P123" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: EL MISMO EQUIPO ESTA CODIFICADO TAMBIEN COMO SECU1701 y ESE SI TIENE FICHA | SE ESCRIBE CASI IGUAL (SECU1701): SECU1701-SECADORA UT170-UNILINC TOUCH-DOBLE ROTACION-GN-OPTIDRY-GALVANIZADO-220V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT170\SECU1701-SECADORA UT170-UNILINC TOUCH-DOBLE ROTACION-GN-OPTIDRY-GALVANIZADO-220V.docx</v>
       </c>
     </row>
-    <row r="123" xml:space="preserve">
-      <c r="A123" t="str">
+    <row r="124" xml:space="preserve">
+      <c r="A124" t="str">
         <v>CALM23</v>
       </c>
-      <c r="B123" t="str">
+      <c r="B124" t="str">
         <v>CALDERIN CON PLANCHA 2.3L MO. MINI 230/1/60HZ MOD. ARIES</v>
       </c>
-      <c r="C123" t="str">
+      <c r="C124" t="str">
         <v>SIMI MONDIAL</v>
       </c>
-      <c r="D123" t="str">
-        <v/>
-      </c>
-      <c r="E123" t="str">
-        <v/>
-      </c>
-      <c r="F123" t="str">
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G123" t="str">
+      <c r="G124" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H123" t="str">
+      <c r="H124" t="str">
         <v>NO</v>
       </c>
-      <c r="I123" t="str">
-        <v/>
-      </c>
-      <c r="J123" t="str">
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
         <v>NO</v>
       </c>
-      <c r="K123" t="str">
+      <c r="K124" t="str">
         <v>no</v>
       </c>
-      <c r="L123" t="str">
-        <v/>
-      </c>
-      <c r="M123" t="str">
-        <v/>
-      </c>
-      <c r="N123">
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124">
         <v>950</v>
       </c>
-      <c r="O123" t="str">
+      <c r="O124" t="str">
         <v>retirado</v>
       </c>
-      <c r="P123" t="str" xml:space="preserve">
+      <c r="P124" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: EL MISMO EQUIPO ESTA CODIFICADO TAMBIEN COMO CALMI23 y ESE SI TIENE FICHA | LLEVA EL CODIGO DENTRO DE OTRO: CALM231-Mesa de planchado con calderin incporado 2.3 litros.doc → V:\LESLY\SIDI MONDIAL\ESPECIFICACIONES TECNICAS\CALM231-Mesa de planchado con calderin incporado 2.3 litros.doc | SE ESCRIBE CASI IGUAL (CALMI23): CALMI23-Calderin Aries electrico 2.3 litros.doc → V:\LESLY\SIDI MONDIAL\ESPECIFICACIONES TECNICAS\CALMI23-Calderin Aries electrico 2.3 litros.doc
 En V: hay archivos que empiezan con ese código: CALM231-Mesa de planchado con calderin incporado 2.3 litros.doc</v>
       </c>
     </row>
-    <row r="124" xml:space="preserve">
-      <c r="A124" t="str">
+    <row r="125" xml:space="preserve">
+      <c r="A125" t="str">
         <v>CO401</v>
       </c>
-      <c r="B124" t="str">
+      <c r="B125" t="str">
         <v>COCHE UTILITARIO DE PLASTICO MOD. HM-401, 5" LLANTAS, 130*80*88 CM , 2 RUEDAS FIJAS , 2 RUEDAS GIRATORIAS, CAPACIDAD 35 KG, COLOR: BLUE, POLIETILENO VIRGEN (PE)</v>
       </c>
-      <c r="C124" t="str">
+      <c r="C125" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="D124" t="str">
-        <v/>
-      </c>
-      <c r="E124" t="str">
-        <v/>
-      </c>
-      <c r="F124" t="str">
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G124" t="str">
+      <c r="G125" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H124" t="str">
+      <c r="H125" t="str">
         <v>NO</v>
       </c>
-      <c r="I124" t="str">
-        <v/>
-      </c>
-      <c r="J124" t="str">
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
         <v>NO</v>
       </c>
-      <c r="K124" t="str">
+      <c r="K125" t="str">
         <v>no</v>
       </c>
-      <c r="L124" t="str">
-        <v/>
-      </c>
-      <c r="M124" t="str">
-        <v/>
-      </c>
-      <c r="N124">
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125">
         <v>899</v>
       </c>
-      <c r="O124" t="str">
+      <c r="O125" t="str">
         <v>retirado</v>
       </c>
-      <c r="P124" t="str" xml:space="preserve">
+      <c r="P125" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: EL MISMO EQUIPO ESTA CODIFICADO TAMBIEN COMO CO401A y ESE SI TIENE FICHA | LLEVA EL CODIGO DENTRO DE OTRO: CO401A-COCHE DE TRANSPORTE DE ROPA HM 401 AZUL.docx → V:\LESLY\COCHES\ESPECIFICACIONES\CO401A-COCHE DE TRANSPORTE DE ROPA HM 401 AZUL.docx
 En V: hay archivos que empiezan con ese código: CO401A-COCHE DE TRANSPORTE DE ROPA  HM 401 AZUL.docx</v>
       </c>
     </row>
-    <row r="125" xml:space="preserve">
-      <c r="A125" t="str">
+    <row r="126" xml:space="preserve">
+      <c r="A126" t="str">
         <v>CO402</v>
       </c>
-      <c r="B125" t="str">
+      <c r="B126" t="str">
         <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402, 5" LLANTAS, 120*80*80 CM , 2 RUEDAS FIJAS , 2 RUEDAS GIRATORIAS, CAPACIDAD 31 KG, COLOR: AZUL/WHITE/ GREY, POLIETILENO VIRGEN (PE)</v>
       </c>
-      <c r="C125" t="str">
+      <c r="C126" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="D125" t="str">
-        <v/>
-      </c>
-      <c r="E125" t="str">
-        <v/>
-      </c>
-      <c r="F125" t="str">
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G125" t="str">
+      <c r="G126" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H125" t="str">
+      <c r="H126" t="str">
         <v>NO</v>
       </c>
-      <c r="I125" t="str">
-        <v/>
-      </c>
-      <c r="J125" t="str">
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
         <v>NO</v>
       </c>
-      <c r="K125" t="str">
+      <c r="K126" t="str">
         <v>no</v>
       </c>
-      <c r="L125" t="str">
-        <v/>
-      </c>
-      <c r="M125" t="str">
-        <v/>
-      </c>
-      <c r="N125">
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126">
         <v>825</v>
       </c>
-      <c r="O125" t="str">
+      <c r="O126" t="str">
         <v>retirado</v>
       </c>
-      <c r="P125" t="str" xml:space="preserve">
+      <c r="P126" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: LLEVA EL CODIGO DENTRO DE OTRO: CO402A-COCHE DE TRANSPORTE DE ROPA - HM 402 AZUL.docx → V:\LESLY\COCHES\ESPECIFICACIONES\CO402A-COCHE DE TRANSPORTE DE ROPA - HM 402 AZUL.docx | LLEVA EL CODIGO DENTRO DE OTRO: CO402B-COCHE DE TRANSPORTE DE ROPA - HM 402 BLANCO.docx → V:\LESLY\COCHES\ESPECIFICACIONES\CO402B-COCHE DE TRANSPORTE DE ROPA - HM 402 BLANCO.docx | LLEVA EL CODIGO DENTRO DE OTRO: CO402G-COCHE DE TRANSPORTE DE ROPA - HM 402 GRIS.docx → V:\LESLY\COCHES\ESPECIFICACIONES\CO402G-COCHE DE TRANSPORTE DE ROPA - HM 402 GRIS.docx
 En V: hay archivos que empiezan con ese código: CO402A-COCHE DE TRANSPORTE DE ROPA - HM 402 AZUL.docx · CO402B-COCHE DE TRANSPORTE DE ROPA - HM 402 BLANCO.docx · CO402G-COCHE DE TRANSPORTE DE ROPA - HM 402 GRIS.docx</v>
       </c>
     </row>
-    <row r="126" xml:space="preserve">
-      <c r="A126" t="str">
+    <row r="127" xml:space="preserve">
+      <c r="A127" t="str">
         <v>CO408</v>
       </c>
-      <c r="B126" t="str">
+      <c r="B127" t="str">
         <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408, 5" LLANTAS, 110*79*84 CM , 2 RUEDAS FIJAS , 2 RUEDAS GIRATORIAS,CAPACIDAD 26 KG, COLOR: BLUE/WHITE, POLIETILENO VIRGEN (PE)</v>
       </c>
-      <c r="C126" t="str">
+      <c r="C127" t="str">
         <v>EFAMEIN</v>
       </c>
-      <c r="D126" t="str">
-        <v/>
-      </c>
-      <c r="E126" t="str">
-        <v/>
-      </c>
-      <c r="F126" t="str">
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G126" t="str">
+      <c r="G127" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H126" t="str">
+      <c r="H127" t="str">
         <v>NO</v>
       </c>
-      <c r="I126" t="str">
-        <v/>
-      </c>
-      <c r="J126" t="str">
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
         <v>NO</v>
       </c>
-      <c r="K126" t="str">
+      <c r="K127" t="str">
         <v>no</v>
       </c>
-      <c r="L126" t="str">
-        <v/>
-      </c>
-      <c r="M126" t="str">
-        <v/>
-      </c>
-      <c r="N126">
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127">
         <v>799</v>
       </c>
-      <c r="O126" t="str">
+      <c r="O127" t="str">
         <v>retirado</v>
       </c>
-      <c r="P126" t="str" xml:space="preserve">
+      <c r="P127" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: LLEVA EL CODIGO DENTRO DE OTRO: CO408A-COCHE DE TRANSPORTE DE ROPA HM 408 AZUL.docx → V:\LESLY\COCHES\ESPECIFICACIONES\CO408A-COCHE DE TRANSPORTE DE ROPA HM 408 AZUL.docx | LLEVA EL CODIGO DENTRO DE OTRO: CO408B-COCHE DE TRANSPORTE DE ROPA HM 408 BLANCO.docx → V:\LESLY\COCHES\ESPECIFICACIONES\CO408B-COCHE DE TRANSPORTE DE ROPA HM 408 BLANCO.docx
 En V: hay archivos que empiezan con ese código: CO408A-COCHE DE TRANSPORTE DE ROPA  HM 408 AZUL.docx · CO408B-COCHE DE TRANSPORTE DE ROPA  HM 408 BLANCO.docx</v>
       </c>
     </row>
-    <row r="127" xml:space="preserve">
-      <c r="A127" t="str">
+    <row r="128" xml:space="preserve">
+      <c r="A128" t="str">
         <v>LAV135S</v>
       </c>
-      <c r="B127" t="str">
+      <c r="B128" t="str">
         <v>LAVADORA INDUST. FLOT. SOFTWASH MOD. FX135, FUERZA 400G, CONTROL X +, PANEL FRONTAL, LATERAL Y CILINDRO INOX, CAP. 13.5KG, RPM: 1,075, X (220/60Hz/1PH)</v>
       </c>
-      <c r="C127" t="str">
+      <c r="C128" t="str">
         <v>PRIMUS</v>
       </c>
-      <c r="D127" t="str">
-        <v/>
-      </c>
-      <c r="E127" t="str">
-        <v/>
-      </c>
-      <c r="F127" t="str">
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G127" t="str">
+      <c r="G128" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H127" t="str">
+      <c r="H128" t="str">
         <v>NO</v>
       </c>
-      <c r="I127" t="str">
-        <v/>
-      </c>
-      <c r="J127" t="str">
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
         <v>NO</v>
       </c>
-      <c r="K127" t="str">
+      <c r="K128" t="str">
         <v>no</v>
       </c>
-      <c r="L127" t="str">
-        <v/>
-      </c>
-      <c r="M127" t="str">
-        <v/>
-      </c>
-      <c r="N127">
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128">
         <v>14500</v>
       </c>
-      <c r="O127" t="str">
+      <c r="O128" t="str">
         <v>retirado</v>
       </c>
-      <c r="P127" t="str" xml:space="preserve">
+      <c r="P128" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: EL MISMO EQUIPO ESTA CODIFICADO TAMBIEN COMO LAV1355 y ESE SI TIENE FICHA | SE ESCRIBE CASI IGUAL (LAV135): LAV135-LAVADORA RX135-X CONTROL-200G-GRIS-220V-1PH.docx → V:\LESLY\ALLIANCE ok\ESPECIFICACIONES TECNICAS\LAV135-LAVADORA RX135-X CONTROL-200G-GRIS-220V-1PH.docx | SE ESCRIBE CASI IGUAL (LAV1351): LAV1351 -LAVADORA RX135-X CONTROL PLUS-100G-INOX-220V-1PH.docx → V:\LESLY\ALLIANCE ok\ESPECIFICACIONES TECNICAS\LAV1351 -LAVADORA RX135-X CONTROL PLUS-100G-INOX-220V-1PH.docx | SE ESCRIBE CASI IGUAL (LAV1355): LAV1355-LAVADORA FX135-XCONTROL PLUS-SOFTWASH-400G-INOX-220V-1PH.docx → V:\LESLY\ALLIANCE ok\ESPECIFICACIONES TECNICAS\LAV1355-LAVADORA FX135-XCONTROL PLUS-SOFTWASH-400G-INOX-220V-1PH.docx</v>
       </c>
     </row>
-    <row r="128" xml:space="preserve">
-      <c r="A128" t="str">
+    <row r="129" xml:space="preserve">
+      <c r="A129" t="str">
         <v>LAVA060</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B129" t="str">
         <v>LAVADORA INDUSTRIAL, MOD. UCT060, CONTROL: M9, FUERZA: 100G, PANEL FRONTAL, SUPERIOR, LATERAL INOX, CILINDRO INOXIDABLE, CALENTAMIENTO PREPARADO A VAPOR, 27KG, X(220V/60HZ/1-3PH)</v>
       </c>
-      <c r="C128" t="str">
+      <c r="C129" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D128" t="str">
-        <v/>
-      </c>
-      <c r="E128" t="str">
-        <v/>
-      </c>
-      <c r="F128" t="str">
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G128" t="str">
+      <c r="G129" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H128" t="str">
+      <c r="H129" t="str">
         <v>NO</v>
       </c>
-      <c r="I128" t="str">
-        <v/>
-      </c>
-      <c r="J128" t="str">
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
         <v>NO</v>
       </c>
-      <c r="K128" t="str">
+      <c r="K129" t="str">
         <v>no</v>
       </c>
-      <c r="L128" t="str">
-        <v/>
-      </c>
-      <c r="M128" t="str">
-        <v/>
-      </c>
-      <c r="N128">
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129">
         <v>15500</v>
       </c>
-      <c r="O128" t="str">
+      <c r="O129" t="str">
         <v>retirado</v>
       </c>
-      <c r="P128" t="str" xml:space="preserve">
+      <c r="P129" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: EL MISMO EQUIPO ESTA CODIFICADO TAMBIEN COMO LAV0601 y ESE SI TIENE FICHA | SE ESCRIBE CASI IGUAL (LAV060): LAV060-LAVADORA UCT060-M30-INOX-200G-220V.docx → V:\LESLY\ALLIANCE ok\ESPECIFICACIONES TECNICAS\LAV060-LAVADORA UCT060-M30-INOX-200G-220V.docx</v>
       </c>
     </row>
-    <row r="129" xml:space="preserve">
-      <c r="A129" t="str">
+    <row r="130" xml:space="preserve">
+      <c r="A130" t="str">
         <v>SEC75E</v>
       </c>
-      <c r="B129" t="str">
+      <c r="B130" t="str">
         <v>SECADORA INDUSTRIAL, MOD. UT075E, CONTROL: DUAL DIGITAL, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, CALENTAMIENTO: ELÉCTRICO, CAP:34KG, G (220V/60HZ/3PH)</v>
       </c>
-      <c r="C129" t="str">
+      <c r="C130" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D129" t="str">
-        <v/>
-      </c>
-      <c r="E129" t="str">
-        <v/>
-      </c>
-      <c r="F129" t="str">
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G129" t="str">
+      <c r="G130" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H129" t="str">
+      <c r="H130" t="str">
         <v>NO</v>
       </c>
-      <c r="I129" t="str">
-        <v/>
-      </c>
-      <c r="J129" t="str">
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
         <v>NO</v>
       </c>
-      <c r="K129" t="str">
+      <c r="K130" t="str">
         <v>no</v>
       </c>
-      <c r="L129" t="str">
-        <v/>
-      </c>
-      <c r="M129" t="str">
-        <v/>
-      </c>
-      <c r="N129">
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130">
         <v>9300</v>
       </c>
-      <c r="O129" t="str">
+      <c r="O130" t="str">
         <v>retirado</v>
       </c>
-      <c r="P129" t="str" xml:space="preserve">
+      <c r="P130" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: SE ESCRIBE CASI IGUAL (SECU75E): SECU75E. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACIÓN -GALVANIZADO-ELECTRICO-220V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU75E. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACIÓN -GALVANIZADO-ELECTRICO-220V.docx</v>
       </c>
     </row>
-    <row r="130" xml:space="preserve">
-      <c r="A130" t="str">
+    <row r="131" xml:space="preserve">
+      <c r="A131" t="str">
         <v>SEC75E2</v>
       </c>
-      <c r="B130" t="str">
+      <c r="B131" t="str">
         <v>SECADORA INDUSTRIAL, MOD. UT075E, CONTROL: DUAL DIGITAL, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, CALENTAMIENTO: ELÉCTRICO, CAP:34KG, H (380V/60HZ/3PH)</v>
       </c>
-      <c r="C130" t="str">
+      <c r="C131" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D130" t="str">
-        <v/>
-      </c>
-      <c r="E130" t="str">
-        <v/>
-      </c>
-      <c r="F130" t="str">
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G130" t="str">
+      <c r="G131" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H130" t="str">
+      <c r="H131" t="str">
         <v>NO</v>
       </c>
-      <c r="I130" t="str">
-        <v/>
-      </c>
-      <c r="J130" t="str">
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
         <v>NO</v>
       </c>
-      <c r="K130" t="str">
+      <c r="K131" t="str">
         <v>no</v>
       </c>
-      <c r="L130" t="str">
-        <v/>
-      </c>
-      <c r="M130" t="str">
-        <v/>
-      </c>
-      <c r="N130">
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131">
         <v>9500</v>
       </c>
-      <c r="O130" t="str">
+      <c r="O131" t="str">
         <v>retirado</v>
       </c>
-      <c r="P130" t="str" xml:space="preserve">
+      <c r="P131" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: SE ESCRIBE CASI IGUAL (SECU75E2): SECU75E2. SECADORA UT075-DUAL DIGITAL-GALVANIZADO-DOBLE ROTACION-ELECTRICO-380V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU75E2. SECADORA UT075-DUAL DIGITAL-GALVANIZADO-DOBLE ROTACION-ELECTRICO-380V.docx</v>
       </c>
     </row>
-    <row r="131" xml:space="preserve">
-      <c r="A131" t="str">
+    <row r="132" xml:space="preserve">
+      <c r="A132" t="str">
         <v>SEC75E3</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>SECADORA INDUSTRIAL, MOD. UT075E, CONTROL: DUAL DIGITAL, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, CALENTAMIENTO: ELÉCTRICO, CAP:34KG, G (220V/60HZ/3PH)</v>
       </c>
-      <c r="C131" t="str">
+      <c r="C132" t="str">
         <v>UNIMAC</v>
       </c>
-      <c r="D131" t="str">
-        <v/>
-      </c>
-      <c r="E131" t="str">
-        <v/>
-      </c>
-      <c r="F131" t="str">
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
         <v>Sin ficha en V:</v>
       </c>
-      <c r="G131" t="str">
+      <c r="G132" t="str">
         <v>El archivo existe pero con OTRO codigo</v>
       </c>
-      <c r="H131" t="str">
+      <c r="H132" t="str">
         <v>NO</v>
       </c>
-      <c r="I131" t="str">
-        <v/>
-      </c>
-      <c r="J131" t="str">
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
         <v>NO</v>
       </c>
-      <c r="K131" t="str">
+      <c r="K132" t="str">
         <v>no</v>
       </c>
-      <c r="L131" t="str">
-        <v/>
-      </c>
-      <c r="M131" t="str">
-        <v/>
-      </c>
-      <c r="N131">
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132">
         <v>9150</v>
       </c>
-      <c r="O131" t="str">
+      <c r="O132" t="str">
         <v>retirado</v>
       </c>
-      <c r="P131" t="str" xml:space="preserve">
+      <c r="P132" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: SE ESCRIBE CASI IGUAL (SECU75E3): SECU75E3. SECADORA UT075-DUAL DIGITAL -GALVANIZADO-ELECTRICO-220V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU75E3. SECADORA UT075-DUAL DIGITAL -GALVANIZADO-ELECTRICO-220V.docx</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="str">
+    <row r="133">
+      <c r="A133" t="str">
         <v>SECNSEN</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B133" t="str">
         <v>SECADORA SEMI INDUSTRIAL APILABLE ELECTRICO, PRIMUS, MOD: NSENXAGS173NW01, CAP: 13.5 KG, TAMBOR GALVANIZADO, CONTROL: QUANTUM GOLD, (220V/60HZ/3PH), 26A, 5400W</v>
       </c>
-      <c r="C132" t="str">
+      <c r="C133" t="str">
         <v>PRIMUS</v>
-      </c>
-      <c r="D132" t="str">
-        <v/>
-      </c>
-      <c r="E132" t="str">
-        <v/>
-      </c>
-      <c r="F132" t="str">
-        <v>Sin ficha en V:</v>
-      </c>
-      <c r="G132" t="str">
-        <v>No hay ningun archivo con ese codigo</v>
-      </c>
-      <c r="H132" t="str">
-        <v>NO</v>
-      </c>
-      <c r="I132" t="str">
-        <v/>
-      </c>
-      <c r="J132" t="str">
-        <v>NO</v>
-      </c>
-      <c r="K132" t="str">
-        <v>no</v>
-      </c>
-      <c r="L132" t="str">
-        <v/>
-      </c>
-      <c r="M132" t="str">
-        <v/>
-      </c>
-      <c r="N132">
-        <v>4500</v>
-      </c>
-      <c r="O132" t="str">
-        <v>retirado</v>
-      </c>
-      <c r="P132" t="str">
-        <v>El maestro lo marca en rojo: «No hay ningun archivo con ese codigo»</v>
-      </c>
-    </row>
-    <row r="133" xml:space="preserve">
-      <c r="A133" t="str">
-        <v>SECU754</v>
-      </c>
-      <c r="B133" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
-      </c>
-      <c r="C133" t="str">
-        <v>UNIMAC</v>
       </c>
       <c r="D133" t="str">
         <v/>
@@ -9132,7 +9151,7 @@
         <v>Sin ficha en V:</v>
       </c>
       <c r="G133" t="str">
-        <v>El archivo existe pero con OTRO codigo</v>
+        <v>No hay ningun archivo con ese codigo</v>
       </c>
       <c r="H133" t="str">
         <v>NO</v>
@@ -9153,26 +9172,76 @@
         <v/>
       </c>
       <c r="N133">
-        <v>11150</v>
+        <v>4500</v>
       </c>
       <c r="O133" t="str">
         <v>retirado</v>
       </c>
-      <c r="P133" t="str" xml:space="preserve">
+      <c r="P133" t="str">
+        <v>El maestro lo marca en rojo: «No hay ningun archivo con ese codigo»</v>
+      </c>
+    </row>
+    <row r="134" xml:space="preserve">
+      <c r="A134" t="str">
+        <v>SECU754</v>
+      </c>
+      <c r="B134" t="str">
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: UNILICH TOUCH, DOBLE ROTACION, PANEL FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+      </c>
+      <c r="C134" t="str">
+        <v>UNIMAC</v>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v>Sin ficha en V:</v>
+      </c>
+      <c r="G134" t="str">
+        <v>El archivo existe pero con OTRO codigo</v>
+      </c>
+      <c r="H134" t="str">
+        <v>NO</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K134" t="str">
+        <v>no</v>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134">
+        <v>11150</v>
+      </c>
+      <c r="O134" t="str">
+        <v>retirado</v>
+      </c>
+      <c r="P134" t="str" xml:space="preserve">
         <v xml:space="preserve">El maestro lo marca en rojo: «El archivo existe pero con OTRO codigo»
 El maestro apunta: EL MISMO EQUIPO ESTA CODIFICADO TAMBIEN COMO SECU752 y ESE SI TIENE FICHA | SE ESCRIBE CASI IGUAL (SECU75): SECU75. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-220V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU75. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-220V.docx | SE ESCRIBE CASI IGUAL (SECU752): SECU752. SECADORA UT075-UNILINC TOUCH-DOBLE ROTACION-INOX-C. INOX-GN-220V OPTIDRY.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU752. SECADORA UT075-UNILINC TOUCH-DOBLE ROTACION-INOX-C. INOX-GN-220V OPTIDRY.docx | SE ESCRIBE CASI IGUAL (SECU755): SECU755. SECADORA UT075-UNILICH TOUCH -DOBLE ROTACION-INOXIDABLE-GLP-220V OPTIDRY.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU755. SECADORA UT075-UNILICH TOUCH -DOBLE ROTACION-INOXIDABLE-GLP-220V OPTIDRY.docx | SE ESCRIBE CASI IGUAL (SECU75E): SECU75E. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACIÓN -GALVANIZADO-ELECTRICO-220V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU75E. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACIÓN -GALVANIZADO-ELECTRICO-220V.docx | SE ESCRIBE CASI IGUAL (SECU75L): SECU75L. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-380V.docx → V:\PROYECTO ASIGNADO - JEAN PAUL\FICHAS TECNICAS\UT075\SECU75L. SECADORA UT075-DUAL DIGITAL-DOBLE ROTACION-GALVANIZADO-GLP-380V.docx</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P134"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -9319,19 +9388,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Precio actualizado</v>
+        <v>Producto nuevo</v>
       </c>
       <c r="B9" t="str">
-        <v>CALM18</v>
+        <v>LAV2801</v>
       </c>
       <c r="C9" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 1.8 LITROS CALENTAMIENTO ELECTRICO</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D9" t="str">
-        <v>2250.00</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
+        <v>Figura en el maestro v2 con ficha y no existía en el CRM</v>
       </c>
     </row>
     <row r="10">
@@ -9339,13 +9408,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B10" t="str">
-        <v>CALM231</v>
+        <v>CALM18</v>
       </c>
       <c r="C10" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 2.3 LITROS CALENTAMIENTO ELECTRICO</v>
+        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 1.8 LITROS CALENTAMIENTO ELECTRICO</v>
       </c>
       <c r="D10" t="str">
-        <v>2350.00</v>
+        <v>2250.00</v>
       </c>
       <c r="E10" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9356,13 +9425,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B11" t="str">
-        <v>CALM4</v>
+        <v>CALM231</v>
       </c>
       <c r="C11" t="str">
-        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 4 LITROS CALENTAMIENTO ELECTRICO</v>
+        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 2.3 LITROS CALENTAMIENTO ELECTRICO</v>
       </c>
       <c r="D11" t="str">
-        <v>2500.00</v>
+        <v>2350.00</v>
       </c>
       <c r="E11" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9373,13 +9442,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B12" t="str">
-        <v>CO401A</v>
+        <v>CALM4</v>
       </c>
       <c r="C12" t="str">
-        <v>COCHE UTILITARIO DE PLASTICO MOD. HM-401 Azul</v>
+        <v>MESA DE PLANCHADO ASPIRANTE MOD. FENIX SEMI INDUSTRIAL CON CALDERIN INCORPORADA 4 LITROS CALENTAMIENTO ELECTRICO</v>
       </c>
       <c r="D12" t="str">
-        <v>1050.00</v>
+        <v>2500.00</v>
       </c>
       <c r="E12" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9390,13 +9459,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B13" t="str">
-        <v>CO402A</v>
+        <v>CO401A</v>
       </c>
       <c r="C13" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Azul</v>
+        <v>COCHE UTILITARIO DE PLASTICO MOD. HM-401 Azul</v>
       </c>
       <c r="D13" t="str">
-        <v>999.00</v>
+        <v>1050.00</v>
       </c>
       <c r="E13" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9407,10 +9476,10 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B14" t="str">
-        <v>CO402B</v>
+        <v>CO402A</v>
       </c>
       <c r="C14" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Blanco</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Azul</v>
       </c>
       <c r="D14" t="str">
         <v>999.00</v>
@@ -9424,10 +9493,10 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B15" t="str">
-        <v>CO402G</v>
+        <v>CO402B</v>
       </c>
       <c r="C15" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Gris</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Blanco</v>
       </c>
       <c r="D15" t="str">
         <v>999.00</v>
@@ -9441,13 +9510,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B16" t="str">
-        <v>CO408A</v>
+        <v>CO402G</v>
       </c>
       <c r="C16" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Azul</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-402 Gris</v>
       </c>
       <c r="D16" t="str">
-        <v>899.00</v>
+        <v>999.00</v>
       </c>
       <c r="E16" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9458,10 +9527,10 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B17" t="str">
-        <v>CO408B</v>
+        <v>CO408A</v>
       </c>
       <c r="C17" t="str">
-        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Blanco</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Azul</v>
       </c>
       <c r="D17" t="str">
         <v>899.00</v>
@@ -9475,13 +9544,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B18" t="str">
-        <v>LAV040</v>
+        <v>CO408B</v>
       </c>
       <c r="C18" t="str">
-        <v>LAVADORA INDUSTRIAL</v>
+        <v>CARRO DE LVANDERIA DE PLASTICO MOD. HM-408 Blanco</v>
       </c>
       <c r="D18" t="str">
-        <v>14500.00</v>
+        <v>899.00</v>
       </c>
       <c r="E18" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9492,13 +9561,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B19" t="str">
-        <v>LAV060</v>
+        <v>LAV040</v>
       </c>
       <c r="C19" t="str">
         <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D19" t="str">
-        <v>16500.00</v>
+        <v>14500.00</v>
       </c>
       <c r="E19" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9509,13 +9578,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B20" t="str">
-        <v>SECU752</v>
+        <v>LAV060</v>
       </c>
       <c r="C20" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D20" t="str">
-        <v>11950.00</v>
+        <v>16500.00</v>
       </c>
       <c r="E20" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9526,13 +9595,13 @@
         <v>Precio actualizado</v>
       </c>
       <c r="B21" t="str">
-        <v>SECU755</v>
+        <v>LAV280</v>
       </c>
       <c r="C21" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D21" t="str">
-        <v>9900.00</v>
+        <v>14900.00</v>
       </c>
       <c r="E21" t="str">
         <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
@@ -9540,53 +9609,53 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Retirado del catálogo</v>
+        <v>Precio actualizado</v>
       </c>
       <c r="B22" t="str">
-        <v>1SECU1701</v>
+        <v>LAV2801</v>
       </c>
       <c r="C22" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>15200.00</v>
       </c>
       <c r="E22" t="str">
-        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Retirado del catálogo</v>
+        <v>Precio actualizado</v>
       </c>
       <c r="B23" t="str">
-        <v>CALM23</v>
+        <v>SECU752</v>
       </c>
       <c r="C23" t="str">
-        <v>CALDERÍN CON PLANCHA</v>
+        <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>11950.00</v>
       </c>
       <c r="E23" t="str">
-        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Retirado del catálogo</v>
+        <v>Precio actualizado</v>
       </c>
       <c r="B24" t="str">
-        <v>CO401</v>
+        <v>SECU755</v>
       </c>
       <c r="C24" t="str">
-        <v>COCHE DE TRANSPORTE DE ROPA</v>
+        <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>9900.00</v>
       </c>
       <c r="E24" t="str">
-        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
+        <v>El libro más nuevo de Lesly (MODIF. UT120 26-08) trae este precio</v>
       </c>
     </row>
     <row r="25">
@@ -9594,16 +9663,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B25" t="str">
-        <v>CO402</v>
+        <v>1SECU1701</v>
       </c>
       <c r="C25" t="str">
-        <v>COCHE DE TRANSPORTE DE ROPA</v>
+        <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="26">
@@ -9611,16 +9680,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B26" t="str">
-        <v>CO408</v>
+        <v>CALM23</v>
       </c>
       <c r="C26" t="str">
-        <v>COCHE DE TRANSPORTE DE ROPA</v>
+        <v>CALDERÍN CON PLANCHA</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="27">
@@ -9628,16 +9697,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B27" t="str">
-        <v>LAV135S</v>
+        <v>CO401</v>
       </c>
       <c r="C27" t="str">
-        <v>LAVADORA INDUST. FLOT. SOFTWASH</v>
+        <v>COCHE DE TRANSPORTE DE ROPA</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
       </c>
     </row>
     <row r="28">
@@ -9645,16 +9714,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B28" t="str">
-        <v>LAVA060</v>
+        <v>CO402</v>
       </c>
       <c r="C28" t="str">
-        <v>LAVADORA INDUSTRIAL</v>
+        <v>COCHE DE TRANSPORTE DE ROPA</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
       </c>
     </row>
     <row r="29">
@@ -9662,16 +9731,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B29" t="str">
-        <v>SEC75E</v>
+        <v>CO408</v>
       </c>
       <c r="C29" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>COCHE DE TRANSPORTE DE ROPA</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+        <v>Su equipo ahora está codificado por color (CO401A, CO402A/B/G, CO408A/B)</v>
       </c>
     </row>
     <row r="30">
@@ -9679,10 +9748,10 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B30" t="str">
-        <v>SEC75E2</v>
+        <v>LAV135S</v>
       </c>
       <c r="C30" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUST. FLOT. SOFTWASH</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -9696,10 +9765,10 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B31" t="str">
-        <v>SEC75E3</v>
+        <v>LAVA060</v>
       </c>
       <c r="C31" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>LAVADORA INDUSTRIAL</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -9713,10 +9782,10 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B32" t="str">
-        <v>SECNSEN</v>
+        <v>SEC75E</v>
       </c>
       <c r="C32" t="str">
-        <v>SECADORA SEMI INDUSTRIAL APILABLE ELÉCTRICA</v>
+        <v>SECADORA INDUSTRIAL</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -9730,7 +9799,7 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B33" t="str">
-        <v>SECU754</v>
+        <v>SEC75E2</v>
       </c>
       <c r="C33" t="str">
         <v>SECADORA INDUSTRIAL</v>
@@ -9747,7 +9816,7 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B34" t="str">
-        <v>SECU75E</v>
+        <v>SEC75E3</v>
       </c>
       <c r="C34" t="str">
         <v>SECADORA INDUSTRIAL</v>
@@ -9756,7 +9825,7 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="35">
@@ -9764,16 +9833,16 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B35" t="str">
-        <v>SECU75E2</v>
+        <v>SECNSEN</v>
       </c>
       <c r="C35" t="str">
-        <v>SECADORA INDUSTRIAL</v>
+        <v>SECADORA SEMI INDUSTRIAL APILABLE ELÉCTRICA</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
       </c>
     </row>
     <row r="36">
@@ -9781,7 +9850,7 @@
         <v>Retirado del catálogo</v>
       </c>
       <c r="B36" t="str">
-        <v>SECU75E3</v>
+        <v>SECU754</v>
       </c>
       <c r="C36" t="str">
         <v>SECADORA INDUSTRIAL</v>
@@ -9790,12 +9859,63 @@
         <v/>
       </c>
       <c r="E36" t="str">
+        <v>Está en el maestro pero sin ficha: al sistema solo suben los que tienen su Word</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B37" t="str">
+        <v>SECU75E</v>
+      </c>
+      <c r="C37" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SECU75E2</v>
+      </c>
+      <c r="C38" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Retirado del catálogo</v>
+      </c>
+      <c r="B39" t="str">
+        <v>SECU75E3</v>
+      </c>
+      <c r="C39" t="str">
+        <v>SECADORA INDUSTRIAL</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
         <v>El maestro v2 ya no lo lista; el mismo equipo figura con otro código</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E39"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11300,7 +11420,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -11604,7 +11724,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>LAV1355 + LAV2402 + LAV280</v>
+        <v>LAV1355 + LAV2402 + LAV280 + LAV2801</v>
       </c>
       <c r="B22" t="str">
         <v>LAV1355</v>
@@ -11618,7 +11738,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>LAV1355 + LAV2402 + LAV280</v>
+        <v>LAV1355 + LAV2402 + LAV280 + LAV2801</v>
       </c>
       <c r="B23" t="str">
         <v>LAV2402</v>
@@ -11632,13 +11752,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LAV1355 + LAV2402 + LAV280</v>
+        <v>LAV1355 + LAV2402 + LAV280 + LAV2801</v>
       </c>
       <c r="B24" t="str">
         <v>LAV280</v>
       </c>
       <c r="C24" t="str">
-        <v>LAVADORA INDUST. FLOT. MOD. FX280, FUERZA 400G, CONTROL X, PANEL FRONTAL INOX., PANEL LATERAL GRIS, CILINDRO INOX., CALENTAMIENTO BOILER FED, CAP.: 28KG, Q (220/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIDIGA, MOD. RX280, CAP: 28 KG, FUERZA 100G, CONTROL X + , PANEL SUPERIOR, FRONTAL LATERAL INOXIDABLE, CIL. INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, P(220V/60HZ/3PH)</v>
       </c>
       <c r="D24" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11646,13 +11766,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LAV180 + LAV240</v>
+        <v>LAV1355 + LAV2402 + LAV280 + LAV2801</v>
       </c>
       <c r="B25" t="str">
-        <v>LAV180</v>
+        <v>LAV2801</v>
       </c>
       <c r="C25" t="str">
-        <v>LAVADORA INDUST. FLOT. MOD. FX180, FUERZA 400G, CONTROL X +, PANEL SUPERIOR, FRONTAL, LATERAL Y CILINDRO INOX, CALENTAMIENTO BOILER FED, CAP.: 18KG, X (220/60HZ/1PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIDIGA, MOD. RX280, CAP: 28 KG, FUERZA 100G, CONTROL X + , PANEL SUPERIOR, FRONTAL LATERAL INOXIDABLE, CIL. INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, P(380V/60HZ/3PH)</v>
       </c>
       <c r="D25" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11663,10 +11783,10 @@
         <v>LAV180 + LAV240</v>
       </c>
       <c r="B26" t="str">
-        <v>LAV240</v>
+        <v>LAV180</v>
       </c>
       <c r="C26" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD. RX240, CAP: 24 KG, CONTROL: X CONTROL, FUERZA 100G, CILINDRO INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, X(220V/60HZ/1PH)</v>
+        <v>LAVADORA INDUST. FLOT. MOD. FX180, FUERZA 400G, CONTROL X +, PANEL SUPERIOR, FRONTAL, LATERAL Y CILINDRO INOX, CALENTAMIENTO BOILER FED, CAP.: 18KG, X (220/60HZ/1PH)</v>
       </c>
       <c r="D26" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11674,13 +11794,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>LAV2401 + LAV3501</v>
+        <v>LAV180 + LAV240</v>
       </c>
       <c r="B27" t="str">
-        <v>LAV2401</v>
+        <v>LAV240</v>
       </c>
       <c r="C27" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD. RX240, CAP: 24 KG, CONTROL: X CONTROL, FUERZA 200G, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., CILINDRO INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, X(220V/60HZ/1PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD. RX240, CAP: 24 KG, CONTROL: X CONTROL, FUERZA 100G, CILINDRO INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, X(220V/60HZ/1PH)</v>
       </c>
       <c r="D27" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11691,10 +11811,10 @@
         <v>LAV2401 + LAV3501</v>
       </c>
       <c r="B28" t="str">
-        <v>LAV3501</v>
+        <v>LAV2401</v>
       </c>
       <c r="C28" t="str">
-        <v>LAVADORA IND. RIGIDA MOD.RX350, CONTROL X +, FUERZA:100G, CAP.: 35KG, BOILER FED + PREPARADO VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX, CILNDRO INOX., P (380V/60/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD. RX240, CAP: 24 KG, CONTROL: X CONTROL, FUERZA 200G, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., CILINDRO INOX., BOILER FED + PREPARADO A VAPOR, CON PUERTO USB, X(220V/60HZ/1PH)</v>
       </c>
       <c r="D28" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11702,13 +11822,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LAVG080 + LAVT080 + LAVUC100</v>
+        <v>LAV2401 + LAV3501</v>
       </c>
       <c r="B29" t="str">
-        <v>LAVG080</v>
+        <v>LAV3501</v>
       </c>
       <c r="C29" t="str">
-        <v>LAVADORA INDUSTRIAL RÍGIDA, MOD: UCG080, FUERZA: 200G, CONTROL M9, PANEL LATERAL,FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, CAP: 36 KG, (220V/60HZ/1-3PH)</v>
+        <v>LAVADORA IND. RIGIDA MOD.RX350, CONTROL X +, FUERZA:100G, CAP.: 35KG, BOILER FED + PREPARADO VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX, CILNDRO INOX., P (380V/60/3PH)</v>
       </c>
       <c r="D29" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11719,10 +11839,10 @@
         <v>LAVG080 + LAVT080 + LAVUC100</v>
       </c>
       <c r="B30" t="str">
-        <v>LAVT080</v>
+        <v>LAVG080</v>
       </c>
       <c r="C30" t="str">
-        <v>LAVADORA IND. RIGIDA MOD:UCT080 CAP: 36 KG, FUERZA 100G OPL, CONTROL M9, CILINDRO INOX, PREPARADO A VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., (220V/60HZ/1-3PH), 15 AMP</v>
+        <v>LAVADORA INDUSTRIAL RÍGIDA, MOD: UCG080, FUERZA: 200G, CONTROL M9, PANEL LATERAL,FRONTAL INOXIDABLE, CILINDRO INOXIDABLE, CAP: 36 KG, (220V/60HZ/1-3PH)</v>
       </c>
       <c r="D30" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11733,10 +11853,10 @@
         <v>LAVG080 + LAVT080 + LAVUC100</v>
       </c>
       <c r="B31" t="str">
-        <v>LAVUC100</v>
+        <v>LAVT080</v>
       </c>
       <c r="C31" t="str">
-        <v>LAV.IND,RIG,MOD.UC100,OPL,200G,M9,X,220V/60HZ/1-3PH,CAP.45KG,PAN.ACER.CILN.STAND.PREP.VAP.</v>
+        <v>LAVADORA IND. RIGIDA MOD:UCT080 CAP: 36 KG, FUERZA 100G OPL, CONTROL M9, CILINDRO INOX, PREPARADO A VAPOR, PANEL SUPERIOR, FRONTAL Y LATERAL INOX., (220V/60HZ/1-3PH), 15 AMP</v>
       </c>
       <c r="D31" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11744,13 +11864,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LAVG50 + LAVG70 + LAVGP100</v>
+        <v>LAVG080 + LAVT080 + LAVUC100</v>
       </c>
       <c r="B32" t="str">
-        <v>LAVG50</v>
+        <v>LAVUC100</v>
       </c>
       <c r="C32" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP50, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 50 KG, (220V/60HZ/3PH)</v>
+        <v>LAV.IND,RIG,MOD.UC100,OPL,200G,M9,X,220V/60HZ/1-3PH,CAP.45KG,PAN.ACER.CILN.STAND.PREP.VAP.</v>
       </c>
       <c r="D32" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11761,10 +11881,10 @@
         <v>LAVG50 + LAVG70 + LAVGP100</v>
       </c>
       <c r="B33" t="str">
-        <v>LAVG70</v>
+        <v>LAVG50</v>
       </c>
       <c r="C33" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP70, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 70 KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP50, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 50 KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D33" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11775,10 +11895,10 @@
         <v>LAVG50 + LAVG70 + LAVGP100</v>
       </c>
       <c r="B34" t="str">
-        <v>LAVGP100</v>
+        <v>LAVG70</v>
       </c>
       <c r="C34" t="str">
-        <v>LAVADORA IND. EXTRACTORA SAILSTAR MOD.GP100 CAP.100KG C/CALENTAMIENTO A VAPOR 220V/60HZ/3PH</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: GP70, CON CALENTAMIENTO A VAPOR, CONTROL: TOUCH, FUERZA: 350G, CAP: 70 KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D34" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11786,13 +11906,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LAVGIA13 + LAVMA17</v>
+        <v>LAVG50 + LAVG70 + LAVGP100</v>
       </c>
       <c r="B35" t="str">
-        <v>LAVGIA13</v>
+        <v>LAVGP100</v>
       </c>
       <c r="C35" t="str">
-        <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX APILABLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MDCRS</v>
+        <v>LAVADORA IND. EXTRACTORA SAILSTAR MOD.GP100 CAP.100KG C/CALENTAMIENTO A VAPOR 220V/60HZ/3PH</v>
       </c>
       <c r="D35" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11803,10 +11923,10 @@
         <v>LAVGIA13 + LAVMA17</v>
       </c>
       <c r="B36" t="str">
-        <v>LAVMA17</v>
+        <v>LAVGIA13</v>
       </c>
       <c r="C36" t="str">
-        <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX APILABLE, CAP:17KG, 220/60/1PH, COD:CWT29MDCRS</v>
+        <v>LAVADORA C., FLOT., MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX APILABLE, CAP.: 13KG, 220/60/1PH, COD.: CWG27MDCRS</v>
       </c>
       <c r="D36" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11814,13 +11934,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LAVS17 + LAVS17E</v>
+        <v>LAVGIA13 + LAVMA17</v>
       </c>
       <c r="B37" t="str">
-        <v>LAVS17</v>
+        <v>LAVMA17</v>
       </c>
       <c r="C37" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA C., FLOT., MARCA: LG, MOD.: TITAN MAX APILABLE, CAP:17KG, 220/60/1PH, COD:CWT29MDCRS</v>
       </c>
       <c r="D37" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11831,10 +11951,10 @@
         <v>LAVS17 + LAVS17E</v>
       </c>
       <c r="B38" t="str">
-        <v>LAVS17E</v>
+        <v>LAVS17</v>
       </c>
       <c r="C38" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D38" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11842,13 +11962,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>LAVS23 + LAVS23E</v>
+        <v>LAVS17 + LAVS17E</v>
       </c>
       <c r="B39" t="str">
-        <v>LAVS23</v>
+        <v>LAVS17E</v>
       </c>
       <c r="C39" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS17-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D39" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11859,10 +11979,10 @@
         <v>LAVS23 + LAVS23E</v>
       </c>
       <c r="B40" t="str">
-        <v>LAVS23E</v>
+        <v>LAVS23</v>
       </c>
       <c r="C40" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D40" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11870,13 +11990,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>LAVUS030 + LAVUS050</v>
+        <v>LAVS23 + LAVS23E</v>
       </c>
       <c r="B41" t="str">
-        <v>LAVUS030</v>
+        <v>LAVS23E</v>
       </c>
       <c r="C41" t="str">
-        <v>LAVADORA - SECADORA INDUSTRIAL, MOD. UST030, UNILIC TOUCH, PANEL FRONTAL, LATERAL y CILINDRO INOXIDABLE, DOBLE ROTACION, GAS NATURAL, CAP.: 2*14 KG, X(220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: SS23-E, CON CALEFACCION ELECTRICA, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, 320G, CAP 23KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D41" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11887,10 +12007,10 @@
         <v>LAVUS030 + LAVUS050</v>
       </c>
       <c r="B42" t="str">
-        <v>LAVUS050</v>
+        <v>LAVUS030</v>
       </c>
       <c r="C42" t="str">
-        <v>LAVADORA - SECADORA INDUSTRIAL, MOD. UST050, UNILIC TOUCH, PANEL FRONTAL, LATERAL y CILINDRO INOXIDABLE, DOBLE ROTACION, GAS NATURAL, CAP.: 2*23 KG, X(220V/60HZ/3PH)</v>
+        <v>LAVADORA - SECADORA INDUSTRIAL, MOD. UST030, UNILIC TOUCH, PANEL FRONTAL, LATERAL y CILINDRO INOXIDABLE, DOBLE ROTACION, GAS NATURAL, CAP.: 2*14 KG, X(220V/60HZ/3PH)</v>
       </c>
       <c r="D42" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11898,13 +12018,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
+        <v>LAVUS030 + LAVUS050</v>
       </c>
       <c r="B43" t="str">
-        <v>LAVUW045</v>
+        <v>LAVUS050</v>
       </c>
       <c r="C43" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, X (220V/60HZ/1-3 PH)</v>
+        <v>LAVADORA - SECADORA INDUSTRIAL, MOD. UST050, UNILIC TOUCH, PANEL FRONTAL, LATERAL y CILINDRO INOXIDABLE, DOBLE ROTACION, GAS NATURAL, CAP.: 2*23 KG, X(220V/60HZ/3PH)</v>
       </c>
       <c r="D43" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11915,10 +12035,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B44" t="str">
-        <v>LAVW045</v>
+        <v>LAVUW045</v>
       </c>
       <c r="C44" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, P (380V/60HZ/3 PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, X (220V/60HZ/1-3 PH)</v>
       </c>
       <c r="D44" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11929,10 +12049,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B45" t="str">
-        <v>LAVW065</v>
+        <v>LAVW045</v>
       </c>
       <c r="C45" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UWT065, FUERZA: 400 G, CONTROL UNILINC TOUCH, CAP. 29.5 KG, SIS. OPL, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., C/ DOSIFICADOR MANUAL, C/ OTISPRAY, (220V/60HZ/1-3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD: UWT045, FUERZA 400G, CONTROL: UNILINC TOUCH, CAP:20KG, SIS. OPL, PANEL LATERAL, FRONTAL Y CILINDRO INOX., PREPARADA PARA VAPOR, CON DOSIFICADOR MANUAL, C/ OPTISPRAY, P (380V/60HZ/3 PH)</v>
       </c>
       <c r="D45" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11943,10 +12063,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B46" t="str">
-        <v>LAVW0851</v>
+        <v>LAVW065</v>
       </c>
       <c r="C46" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (380V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UWT065, FUERZA: 400 G, CONTROL UNILINC TOUCH, CAP. 29.5 KG, SIS. OPL, PREPARADO PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., C/ DOSIFICADOR MANUAL, C/ OTISPRAY, (220V/60HZ/1-3PH)</v>
       </c>
       <c r="D46" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11957,10 +12077,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B47" t="str">
-        <v>LAVW0852</v>
+        <v>LAVW0851</v>
       </c>
       <c r="C47" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (380V/60HZ/3PH)</v>
       </c>
       <c r="D47" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11971,10 +12091,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B48" t="str">
-        <v>LAVW105</v>
+        <v>LAVW0852</v>
       </c>
       <c r="C48" t="str">
-        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, MOD: UW085, FUERZA: 300 G, CONTROL UNILINC TOUCH, CAP. 38.5 KG, M. RÍGIDO, SIS. OPL, PREP. PARA VAPOR, PANEL LATERAL, FRONTAL Y CILINDRO INOX., CON DOSIFICADOR MANUAL, C/ OPTISPRAY, (220V/60HZ/3PH)</v>
       </c>
       <c r="D48" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11985,10 +12105,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B49" t="str">
-        <v>LAVW1051</v>
+        <v>LAVW105</v>
       </c>
       <c r="C49" t="str">
-        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD:UWT105, FUERZA 300G, CAP: 47.6KG, OPL, CONTROL: UNILINC TOUCH, PANEL LATERAL, FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(220V/60HZ/3PH)</v>
       </c>
       <c r="D49" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -11999,10 +12119,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B50" t="str">
-        <v>LAVW1301</v>
+        <v>LAVW1051</v>
       </c>
       <c r="C50" t="str">
-        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL RIGIDA, UNIMAC, MOD:UWT105, FUERZA 300G, CAP: 47.6KG, OPL, CONTROL: UNILINC TOUCH, PANEL LATERAL, FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
       </c>
       <c r="D50" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12013,10 +12133,10 @@
         <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B51" t="str">
-        <v>LAVW1302</v>
+        <v>LAVW1301</v>
       </c>
       <c r="C51" t="str">
-        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL: UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, Q(220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, P(380V/60HZ/3PH)</v>
       </c>
       <c r="D51" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12024,13 +12144,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LAVW17 + LAVW23</v>
+        <v>LAVUW045 + LAVW045 + LAVW065 + LAVW0851 + LAVW0852 + LAVW105 + LAVW1051 + LAVW1301 + LAVW1302</v>
       </c>
       <c r="B52" t="str">
-        <v>LAVW17</v>
+        <v>LAVW1302</v>
       </c>
       <c r="C52" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: WET 17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, CONTROL: TOUCH, CON SEÑALES DE ALIMENTACIÓN, 300G, CAP 17KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA INDUSTRIAL, RIGIDA MOD: UWT130, FUERZA 300G, CAP:58KG, CONTROL: UNILINC TOUCH, PANEL LATERAL / FRONTAL Y CILINDRO INOX, PREPARADO PARA VAPOR, DOSIFICADOR MANUAL, C/ OPTISPRAY, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="D52" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12041,10 +12161,10 @@
         <v>LAVW17 + LAVW23</v>
       </c>
       <c r="B53" t="str">
-        <v>LAVW23</v>
+        <v>LAVW17</v>
       </c>
       <c r="C53" t="str">
-        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: WET 23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, CONTROL: TOUCH, CON SEÑALES DE ALIMENTACIÓN, 300G, CAP 17KG, (220V/60HZ/3PH)</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: WET 17, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, CONTROL: TOUCH, CON SEÑALES DE ALIMENTACIÓN, 300G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D53" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12052,13 +12172,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SECEFG125 + SECEFV125</v>
+        <v>LAVW17 + LAVW23</v>
       </c>
       <c r="B54" t="str">
-        <v>SECEFG125</v>
+        <v>LAVW23</v>
       </c>
       <c r="C54" t="str">
-        <v>SECADORA INDUSTRIAL A GAS EFAMEIN MODELO EFAS125, CAP. 125 KG, 10 HP, 220V/60HZ/TRIFASICO</v>
+        <v>LAVADORA EXTRACTORA SAILSTAR, MOD.: WET 23, CON CALENTAMIENTO A VAPOR, PANEL SUPERIOR, FRONTAL Y CILINDRO INOXIDABLE, CONTROL: TOUCH, CON SEÑALES DE ALIMENTACIÓN, 300G, CAP 17KG, (220V/60HZ/3PH)</v>
       </c>
       <c r="D54" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12069,10 +12189,10 @@
         <v>SECEFG125 + SECEFV125</v>
       </c>
       <c r="B55" t="str">
-        <v>SECEFV125</v>
+        <v>SECEFG125</v>
       </c>
       <c r="C55" t="str">
-        <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS125, CAP. 125 KG, 10 HP, 220V/60HZ/TRIFASICO</v>
+        <v>SECADORA INDUSTRIAL A GAS EFAMEIN MODELO EFAS125, CAP. 125 KG, 10 HP, 220V/60HZ/TRIFASICO</v>
       </c>
       <c r="D55" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12080,13 +12200,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SECEGI10 + SECPL102 + SEPLU10</v>
+        <v>SECEFG125 + SECEFV125</v>
       </c>
       <c r="B56" t="str">
-        <v>SECEGI10</v>
+        <v>SECEFV125</v>
       </c>
       <c r="C56" t="str">
-        <v>SECADORA SEMI INDUSTRIAL MARCA LG ELECTRICO GIANT C 10.2 KG, 220/60/1PH</v>
+        <v>SECADORA INDUSTRIAL A VAPOR EFAMEIN MODELO EFAS125, CAP. 125 KG, 10 HP, 220V/60HZ/TRIFASICO</v>
       </c>
       <c r="D56" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12097,10 +12217,10 @@
         <v>SECEGI10 + SECPL102 + SEPLU10</v>
       </c>
       <c r="B57" t="str">
-        <v>SECPL102</v>
+        <v>SECEGI10</v>
       </c>
       <c r="C57" t="str">
-        <v>SECADORA SEMI INDUSTRIAL MARCA LG GAS GIAN C + APILABLE 10.2, 220V/60/1PH</v>
+        <v>SECADORA SEMI INDUSTRIAL MARCA LG ELECTRICO GIANT C 10.2 KG, 220/60/1PH</v>
       </c>
       <c r="D57" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12111,10 +12231,10 @@
         <v>SECEGI10 + SECPL102 + SEPLU10</v>
       </c>
       <c r="B58" t="str">
-        <v>SEPLU10</v>
+        <v>SECPL102</v>
       </c>
       <c r="C58" t="str">
-        <v>SECADORA SEMI INDUSTRIAL MARCA LG GAS GIAN C + 10.2, 220V/60/1PH</v>
+        <v>SECADORA SEMI INDUSTRIAL MARCA LG GAS GIAN C + APILABLE 10.2, 220V/60/1PH</v>
       </c>
       <c r="D58" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12122,13 +12242,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SECGIA102 + SECMAX15 + SECMAX152</v>
+        <v>SECEGI10 + SECPL102 + SEPLU10</v>
       </c>
       <c r="B59" t="str">
-        <v>SECGIA102</v>
+        <v>SEPLU10</v>
       </c>
       <c r="C59" t="str">
-        <v>SECADORA C., GAS, MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX SINGLE, CAP.:10.2KG, 220V/60/1PH, COD.: CDG27MSCPS</v>
+        <v>SECADORA SEMI INDUSTRIAL MARCA LG GAS GIAN C + 10.2, 220V/60/1PH</v>
       </c>
       <c r="D59" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12139,10 +12259,10 @@
         <v>SECGIA102 + SECMAX15 + SECMAX152</v>
       </c>
       <c r="B60" t="str">
-        <v>SECMAX15</v>
+        <v>SECGIA102</v>
       </c>
       <c r="C60" t="str">
-        <v>SECADORA C., GAS, MARCA: LG, C/S OPL, MOD.: TITAN LIGHT APILABLE, CAP15 KG, 220/60/1PH, COD.: CDT29MUCPS</v>
+        <v>SECADORA C., GAS, MARCA: LG, C/SIS OPL, MOD.: GIANT-C MAX SINGLE, CAP.:10.2KG, 220V/60/1PH, COD.: CDG27MSCPS</v>
       </c>
       <c r="D60" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12153,10 +12273,10 @@
         <v>SECGIA102 + SECMAX15 + SECMAX152</v>
       </c>
       <c r="B61" t="str">
-        <v>SECMAX152</v>
+        <v>SECMAX15</v>
       </c>
       <c r="C61" t="str">
-        <v>SECADORA C., GAS, MARCA: LG, C/S OPL, MOD.: TITAN LIGHT SINGLE, CAP. 15 KG, 220/60/1PH, COD.: CDT29MSCPS</v>
+        <v>SECADORA C., GAS, MARCA: LG, C/S OPL, MOD.: TITAN LIGHT APILABLE, CAP15 KG, 220/60/1PH, COD.: CDT29MUCPS</v>
       </c>
       <c r="D61" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12164,13 +12284,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SECU120 + SECU120E + SECU120E2</v>
+        <v>SECGIA102 + SECMAX15 + SECMAX152</v>
       </c>
       <c r="B62" t="str">
-        <v>SECU120</v>
+        <v>SECMAX152</v>
       </c>
       <c r="C62" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: GAS GLP, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
+        <v>SECADORA C., GAS, MARCA: LG, C/S OPL, MOD.: TITAN LIGHT SINGLE, CAP. 15 KG, 220/60/1PH, COD.: CDT29MSCPS</v>
       </c>
       <c r="D62" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12181,10 +12301,10 @@
         <v>SECU120 + SECU120E + SECU120E2</v>
       </c>
       <c r="B63" t="str">
-        <v>SECU120E</v>
+        <v>SECU120</v>
       </c>
       <c r="C63" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: GAS GLP, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
       </c>
       <c r="D63" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12195,10 +12315,10 @@
         <v>SECU120 + SECU120E + SECU120E2</v>
       </c>
       <c r="B64" t="str">
-        <v>SECU120E2</v>
+        <v>SECU120E</v>
       </c>
       <c r="C64" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR,P(380V/60HZ/ 3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR, Q(220V/60HZ/ 3PH)</v>
       </c>
       <c r="D64" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12206,13 +12326,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SECU1701 + SECU1702</v>
+        <v>SECU120 + SECU120E + SECU120E2</v>
       </c>
       <c r="B65" t="str">
-        <v>SECU1701</v>
+        <v>SECU120E2</v>
       </c>
       <c r="C65" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT120L, CAP: 55KG, CONTROL: DUAL DIGITAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CALENTAMIENTO: ELECTRICO, PANEL ESTÁNDAR,P(380V/60HZ/ 3PH)</v>
       </c>
       <c r="D65" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12223,10 +12343,10 @@
         <v>SECU1701 + SECU1702</v>
       </c>
       <c r="B66" t="str">
-        <v>SECU1702</v>
+        <v>SECU1701</v>
       </c>
       <c r="C66" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="D66" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12234,13 +12354,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SECU200 + SECU2001</v>
+        <v>SECU1701 + SECU1702</v>
       </c>
       <c r="B67" t="str">
-        <v>SECU200</v>
+        <v>SECU1702</v>
       </c>
       <c r="C67" t="str">
-        <v>SECADORA INDUSTRIAL, MOD.: UT200L, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP. 90 KG, GAS GLP, C/ OPTIDRY, Q(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT170, CONTROL: UNILIC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP.77KG, GAS NATURAL, C/ OPTIDRY, Q(220V/60HZ/3PH)</v>
       </c>
       <c r="D67" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12251,10 +12371,10 @@
         <v>SECU200 + SECU2001</v>
       </c>
       <c r="B68" t="str">
-        <v>SECU2001</v>
+        <v>SECU200</v>
       </c>
       <c r="C68" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT200N, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP: 90KG, GAS NATURAL, C/ OPTIDRY , Q (220V/60HZ/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD.: UT200L, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP. 90 KG, GAS GLP, C/ OPTIDRY, Q(220V/60HZ/1-3PH)</v>
       </c>
       <c r="D68" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12262,13 +12382,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
+        <v>SECU200 + SECU2001</v>
       </c>
       <c r="B69" t="str">
-        <v>SECU30</v>
+        <v>SECU2001</v>
       </c>
       <c r="C69" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT030E, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, G (220V/60Hz/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT200N, CONTROL: UNILINC TOUCH, DOBLE ROTACION, CILINDRO INOXIDABLE, CAP: 90KG, GAS NATURAL, C/ OPTIDRY , Q (220V/60HZ/3PH)</v>
       </c>
       <c r="D69" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12279,10 +12399,10 @@
         <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
       </c>
       <c r="B70" t="str">
-        <v>SECU301</v>
+        <v>SECU30</v>
       </c>
       <c r="C70" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT030E, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, H (380V/60Hz/3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT030E, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, G (220V/60Hz/3PH)</v>
       </c>
       <c r="D70" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12293,10 +12413,10 @@
         <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
       </c>
       <c r="B71" t="str">
-        <v>SECU303</v>
+        <v>SECU301</v>
       </c>
       <c r="C71" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT030N, CONTROL: DUAL DIGITAL, GAS NATURAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, X (220V/60Hz/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT030E, CONTROL: DUAL DIGITAL, ELECTRICO, 30KW, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, H (380V/60Hz/3PH)</v>
       </c>
       <c r="D71" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12307,10 +12427,10 @@
         <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
       </c>
       <c r="B72" t="str">
-        <v>SECU502</v>
+        <v>SECU303</v>
       </c>
       <c r="C72" t="str">
-        <v>SECADORA INDUSTRIAL MOD. UT055L, CONTROL: UNILINC TOUCH, A GAS GLP, DOBLE ROTACION, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO INOXIDABLE, C/ OPTIDRY, CAP: 25 KG, X (220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT030N, CONTROL: DUAL DIGITAL, GAS NATURAL, DOBLE ROTACION, CILINDRO GALVANIZADO, CAP 14KG, X (220V/60Hz/1-3PH)</v>
       </c>
       <c r="D72" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12321,10 +12441,10 @@
         <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
       </c>
       <c r="B73" t="str">
-        <v>SECUT055V</v>
+        <v>SECU502</v>
       </c>
       <c r="C73" t="str">
-        <v>SECADORA INDUSTRIAL MOD. UT055, CAP. 25 KG, DUAL DIGITAL, VAPOR , TAMBOR GALVANIZADO, DOBLE ROTACION, 220V/60HZ/1-3PH</v>
+        <v>SECADORA INDUSTRIAL MOD. UT055L, CONTROL: UNILINC TOUCH, A GAS GLP, DOBLE ROTACION, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO INOXIDABLE, C/ OPTIDRY, CAP: 25 KG, X (220V/60HZ/1-3PH)</v>
       </c>
       <c r="D73" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12335,10 +12455,10 @@
         <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
       </c>
       <c r="B74" t="str">
-        <v>SECUT55E</v>
+        <v>SECUT055V</v>
       </c>
       <c r="C74" t="str">
-        <v>SECADORAINDUSTRIAL ELECTRICA MOD. UT055, CAP. 25 KG, DUAL DIGITAL, 220V/60HZ/3PH</v>
+        <v>SECADORA INDUSTRIAL MOD. UT055, CAP. 25 KG, DUAL DIGITAL, VAPOR , TAMBOR GALVANIZADO, DOBLE ROTACION, 220V/60HZ/1-3PH</v>
       </c>
       <c r="D74" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12346,13 +12466,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SECU302 + SECU55</v>
+        <v>SECU30 + SECU301 + SECU303 + SECU502 + SECUT055V + SECUT55E</v>
       </c>
       <c r="B75" t="str">
-        <v>SECU302</v>
+        <v>SECUT55E</v>
       </c>
       <c r="C75" t="str">
-        <v>SECADORA INDUSTRIAL, MOD: UT030N, CONTROL: UNILINC TOUCH, GAS NATURAL, DOBLE ROTACION, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO INOXIDABLE, C/ OPTIDRY, CAP 14KG, X (220V/60Hz/1-3PH)</v>
+        <v>SECADORAINDUSTRIAL ELECTRICA MOD. UT055, CAP. 25 KG, DUAL DIGITAL, 220V/60HZ/3PH</v>
       </c>
       <c r="D75" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12363,10 +12483,10 @@
         <v>SECU302 + SECU55</v>
       </c>
       <c r="B76" t="str">
-        <v>SECU55</v>
+        <v>SECU302</v>
       </c>
       <c r="C76" t="str">
-        <v>SECADORA INDUSTRIAL MOD. UT055L, CONTROL: DUAL DIGITAL, A GAS GLP, DOBLE ROTACION, CILINDRO GALVANIZADO, PANEL ESTÁNDAR, C/ OPTIDRY, CAP: 25 KG, X (220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD: UT030N, CONTROL: UNILINC TOUCH, GAS NATURAL, DOBLE ROTACION, CILINDRO INOXIDABLE, PANEL FRONTAL DE ACERO INOXIDABLE, C/ OPTIDRY, CAP 14KG, X (220V/60Hz/1-3PH)</v>
       </c>
       <c r="D76" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12374,13 +12494,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SECU553 + SECU75 + SECU75L</v>
+        <v>SECU302 + SECU55</v>
       </c>
       <c r="B77" t="str">
-        <v>SECU553</v>
+        <v>SECU55</v>
       </c>
       <c r="C77" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL MOD. UT055L, CONTROL: DUAL DIGITAL, A GAS GLP, DOBLE ROTACION, CILINDRO GALVANIZADO, PANEL ESTÁNDAR, C/ OPTIDRY, CAP: 25 KG, X (220V/60HZ/1-3PH)</v>
       </c>
       <c r="D77" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12391,10 +12511,10 @@
         <v>SECU553 + SECU75 + SECU75L</v>
       </c>
       <c r="B78" t="str">
-        <v>SECU75</v>
+        <v>SECU553</v>
       </c>
       <c r="C78" t="str">
-        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, PANEL ESTÁNDAR , CILINDRO GALVANIZADO, GAS GLP, CAP:34KG, X(220V/60HZ/1-3PH)</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, DOBLE ROTACION, PANEL ESTÁNDAR, CILINDRO GALVANIZADO, GAS NATURAL, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="D78" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
@@ -12405,18 +12525,32 @@
         <v>SECU553 + SECU75 + SECU75L</v>
       </c>
       <c r="B79" t="str">
-        <v>SECU75L</v>
+        <v>SECU75</v>
       </c>
       <c r="C79" t="str">
-        <v>SECADORA INDUSTRIAL MOD. UT075, CONTROL: DUAL DIGITAL , DOBLE ROTACION, CILINDRO GALVANIZADO , PANEL ESTANDAR , CAP: 34 KG, A GAS GLP, (380V/60HZ/3PH), BLANCO</v>
+        <v>SECADORA INDUSTRIAL, MOD. UT075, CONTROL: DUAL DIGITAL, PANEL ESTÁNDAR , CILINDRO GALVANIZADO, GAS GLP, CAP:34KG, X(220V/60HZ/1-3PH)</v>
       </c>
       <c r="D79" t="str">
         <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>SECU553 + SECU75 + SECU75L</v>
+      </c>
+      <c r="B80" t="str">
+        <v>SECU75L</v>
+      </c>
+      <c r="C80" t="str">
+        <v>SECADORA INDUSTRIAL MOD. UT075, CONTROL: DUAL DIGITAL , DOBLE ROTACION, CILINDRO GALVANIZADO , PANEL ESTANDAR , CAP: 34 KG, A GAS GLP, (380V/60HZ/3PH), BLANCO</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Que todos estos equipos se vean realmente igual; si no, cada ficha necesita su propia foto</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D80"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
+++ b/docs/Fichas tecnicas cargadas al CRM - revision 28-08.xlsx
@@ -6922,7 +6922,8 @@
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (132 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que SECPL102, SEPLU10
-Descripción muy corta (19 líneas; la media de las fichas es 50)</v>
+Descripción muy corta (19 líneas; la media de las fichas es 50)
+No dice si es apilable o no (en LG la misma máquina viene de las dos formas)</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -8614,7 +8615,8 @@
         <v xml:space="preserve">No trae vista de complemento (panel o botonera)
 Foto del equipo de baja resolución (132 ppp al tamaño impreso; se amplió a 299)
 Usa la misma foto de equipo que SECEGI10, SECPL102
-Descripción muy corta (17 líneas; la media de las fichas es 50)</v>
+Descripción muy corta (17 líneas; la media de las fichas es 50)
+No dice si es apilable o no (en LG la misma máquina viene de las dos formas)</v>
       </c>
     </row>
     <row r="123" xml:space="preserve">
